--- a/test/斷詞結果檢查.xlsx
+++ b/test/斷詞結果檢查.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pytest\NLP\final\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F02B4D5A-1A11-4C89-993A-0B343815D8F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87C266C4-9335-4C16-8EDF-FFFB6682AA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="302">
   <si>
     <t>欄位 A (text)</t>
   </si>
@@ -36,847 +36,901 @@
     <t>第一輪前先決定座位及起始發牌位置。洗牌並切牌。本次輪到擔任盲注的玩家們下盲注。為每位玩家發兩張底牌。翻牌前（preflop）喊注。</t>
   </si>
   <si>
-    <t>第一 輪前 先 決定 座位 及 起始 發牌 位置 。 洗牌 並切 牌 。 本次 輪到 擔任 盲注 的 玩家 們 下 盲注 。 為 每位 玩家 發兩張 底牌 。 翻牌前 （ preflop ） 喊注 。</t>
+    <t>第一 輪前 先 決定 座位 及 起始 發牌 位置 洗牌 並 切牌 本次 輪到 擔任 盲注 玩家 們 下 盲注 為 每位 玩家 發兩張 底牌 翻牌前 preflop 喊注</t>
   </si>
   <si>
     <t>消一張牌後發出三張公共牌。翻牌圈（flop）喊注。</t>
   </si>
   <si>
-    <t>消一張 牌後發 出三張 公共牌 。 翻牌圈 （ flop ） 喊注 。</t>
+    <t>消一張 牌後發 出三張 公共牌 翻牌圈 flop 喊注</t>
   </si>
   <si>
     <t>消一張牌後發出一張公共牌（轉牌）。轉牌圈（turn）喊注。</t>
   </si>
   <si>
-    <t>消一 張牌 後 發出 一張 公共牌 （ 轉牌 ） 。 轉牌圈 （ turn ） 喊注 。</t>
+    <t>消一 張牌 後 發出 一張 公共牌 轉牌 轉牌圈 turn 喊注</t>
   </si>
   <si>
     <t>消一張牌後發出一張公共牌（河牌）。河牌圈（river）喊注。</t>
   </si>
   <si>
-    <t>消一 張牌 後 發出 一張 公共牌 （ 河牌 ） 。 河牌圈 （ river ） 喊注 。</t>
+    <t>消一 張牌 後 發出 一張 公共牌 河牌 河牌圈 river 喊注</t>
   </si>
   <si>
     <t>若有兩家或以上未蓋牌則攤牌比大小，依勝負分配總彩金。結束本回合，莊家位置依順時鐘次序移動至下一家進行下一輪。</t>
   </si>
   <si>
-    <t>若有 兩家 或 以上 未蓋 牌則 攤牌 比 大小 ， 依勝負 分配 總彩金 。 結束 本 回合 ， 莊家 位置 依順 時鐘 次序 移動 至 下 一家 進行 下 一輪 。</t>
+    <t>若有 兩家 或 以上 未蓋 牌則 攤牌 比 大小 依勝負 分配 總彩金 結束 本 回合 莊家 位置 依順 時鐘 次序 移動 至 下 一家 進行 下 一輪</t>
   </si>
   <si>
     <t>座位分配方式與發牌次序。一般撲克錦標賽的座位均採取隨機分配，私人遊戲多以抽牌比大小決定起始座位順序及第一個發牌者位置。抽牌選位的方法為每人發一張牌，抽到最大牌者為莊位(button)，同大小則比花色。每一輪結束後，莊家依順時針方向由玩家依序輪流擔任。</t>
   </si>
   <si>
-    <t>座位 分配 方式 與 發牌 次序 。 一般 撲克錦標賽 的 座位 均 採取 隨機 分配 ， 私人 遊戲 多 以 抽牌 比 大小 決定 起始 座位 順序 及 第一 個 發牌 者 位置 。 抽牌 選位 的 方法 為 每人 發一 張牌 ， 抽到 最大 牌者 為 莊位 ( button ) ， 同 大小 則比 花色 。 每一輪 結束 後 ， 莊家 依順 時針 方向 由 玩家 依序 輪流 擔任 。</t>
+    <t>座位 分配 方式 發牌 次序 一般 撲克錦標賽 座位 均 採取 隨機 分配 私人 遊戲 多 以 抽牌 比 大小 決定 起始 座位 順序 及 第一 個 發牌 者 位置 抽牌 選位 方法 為 每人 發一 張牌 抽到 最大 牌者 為 莊位 ( button ) 同 大小 則比 花色 每一輪 結束 後 莊家 依 順時針 方向 由 玩家 依序 輪流 擔任</t>
   </si>
   <si>
     <t>下盲注（blinds）及切牌後進行發牌。在三人桌(含)以上皆由莊位（dealer button）位置的下家(小盲注，Small Bind)開始，依順時鐘方向派發，每輪一張共兩輪。每一個參加的玩家都會得到兩張底牌。</t>
   </si>
   <si>
-    <t>下 盲注 （ blinds ） 及切 牌後進行 發牌 。 在 三人桌 ( 含 ) 以上 皆 由 莊位 （ dealer button ） 位置 的 下家 ( 小盲注 ， Small Bind ) 開始 ， 依順 時鐘 方向 派發 ， 每輪 一張 共 兩輪 。 每一個 參加 的 玩家 都 會 得到 兩張 底牌 。</t>
+    <t>下 盲注 blinds 及 切牌 後 進行 發牌 三人桌 ( 含 ) 以上 皆 由 莊位 dealer button 位置 下家 ( 小盲注 Small Bind ) 開始 依順 時鐘 方向 派發 每輪 一張 共 兩輪 每一個 參加 玩家 會 得到 兩張 底牌</t>
   </si>
   <si>
     <t>若為兩人桌(單挑，head up)的話，由莊位為小盲、另一位為大盲，由大盲開始發牌。</t>
   </si>
   <si>
-    <t>若為 兩人桌 ( 單挑 ， head up ) 的 話 ， 由 莊位 為 小盲 、 另 一位 為大盲 ， 由大盲 開始 發牌 。</t>
+    <t>若為 兩人桌 ( 單挑 head up ) 話 由 莊位 為 小盲 另 一位 為大盲 由大盲 開始 發牌</t>
   </si>
   <si>
     <t>Howard Lederer於其教學DVD中建議，由玩家擔任發牌者進行發牌時，由發牌者之上上家進行洗牌，由發牌者之上家(CO位子，Cut-off)進行切牌，以降低作弊風險。</t>
   </si>
   <si>
-    <t>Howard Lederer 於 其 教學 DVD 中建 議 ， 由 玩家 擔任 發牌 者 進行 發牌 時 ， 由 發牌 者 之上 上家 進行 洗牌 ， 由 發牌 者 之上 家 ( CO 位子 ， Cut - off ) 進行 切牌 ， 以 降低 作弊 風險 。</t>
+    <t>Howard Lederer 於 其 教學 DVD 中建 議 由 玩家 擔任 發牌 者 進行 發牌 時 由 發牌 者 之上 上家 進行 洗牌 由 發牌 者 之上 家 ( CO 位子 Cut - off ) 進行 切牌 以 降低 作弊 風險</t>
   </si>
   <si>
     <t>標準德州撲克遊戲盲注的位置，小盲注與大盲注緊接於發牌者之後。坐在發牌人（dealer）位置的玩家，前面有按鈕（button）作標示。位於發牌人順時針方向次一位置的玩家須下小盲注（small blind），金額等於大盲注（big blind）的一半。小盲注玩家的下一家的玩家須下大盲注，金額等於最低下注額。每局以順時針方向輪流。</t>
   </si>
   <si>
-    <t>標準 德州 撲克遊戲 盲注 的 位置 ， 小盲注 與 大盲注 緊接 於 發牌 者 之 後 。 坐在 發牌 人 （ dealer ） 位置 的 玩家 ， 前面 有 按鈕 （ button ） 作標示 。 位 於 發牌 人順 時針 方向 次 一 位置 的 玩家 須下 小盲注 （ small blind ） ， 金額 等 於 大盲注 （ big blind ） 的 一半 。 小盲注 玩家 的 下 一家 的 玩家 須下 大盲注 ， 金額 等 於 最低 下注 額 。 每局 以順 時針 方向 輪流 。</t>
+    <t>標準 德州撲克 遊戲 盲注 位置 小盲注 大盲注 緊接 於 發牌 者 之 後 坐在 發牌 人 dealer 位置 玩家 前面 有 按鈕 button 作標示 位 於 發牌 人 順時針 方向 次 一 位置 玩家 須下 小盲注 small blind 金額 等 於 大盲注 big blind 一半 小盲注 玩家 下 一家 玩家 須下 大盲注 金額 等 於 最低 下注 額 每局 以 順時針 方向 輪流</t>
   </si>
   <si>
     <t>在撲克比賽中，盲注/底注（ante）的金額會隨時間逐漸提高。有時大小盲注有不同比例，例如大小盲注分別為15元和10元也十分正常。</t>
   </si>
   <si>
-    <t>在 撲克 比賽 中 ， 盲注 / 底注 （ ante ） 的 金額會 隨時間 逐漸 提高 。 有時 大 小盲注 有 不同 比例 ， 例如 大 小盲注 分別 為 15 元 和 10 元 也 十分 正常 。</t>
+    <t>撲克 比賽 中 盲注 底注 ante 金額會 隨時間 逐漸 提高 有時 大 小盲注 有 不同 比例 例如 大 小盲注 分別 為 15 元 和 10 元 十分 正常</t>
   </si>
   <si>
     <t>如只剩兩名玩家，「一對一」（heads-up）特別規則會生效。在這個情況下，莊位下小盲注，而他的對手須下大盲注。第一輪由莊位先叫注，翻牌後的各輪皆由大盲注先行叫注。</t>
   </si>
   <si>
-    <t>如 只 剩 兩名 玩家 ， 「 一對 一 」 （ heads - up ） 特別 規則 會 生效 。 在 這個 情況 下 ， 莊位 下 小盲注 ， 而 他 的 對 手須 下 大盲注 。 第一 輪 由 莊位 先 叫 注 ， 翻牌後 的 各輪 皆 由 大盲注 先行 叫注 。</t>
+    <t>如 只 剩 兩名 玩家 一對 一 heads - up 特別 規則 會 生效 這個 情況 下 莊位 下 小盲注 他 對手 須下 大盲注 第一 輪 由 莊位 先 叫注 翻牌後 各輪 皆 由 大盲注 先行 叫注</t>
   </si>
   <si>
     <t>德州撲克最常見的三個變種為限注（limit）、無限注（no-limit）和彩池限注（pot-limit）。</t>
   </si>
   <si>
-    <t>德州 撲克 最常見 的 三個 變種 為 限注 （ limit ） 、 無限注 （ no - limit ） 和 彩池限注 （ pot - limit ） 。</t>
+    <t>德州撲克 最常見 三個 變種 為 限注 limit 無限注 no - limit 和 彩池限注 pot - limit</t>
   </si>
   <si>
     <t>最低加注(min-raise)金額限制：在翻牌前(pre-flop)想第一位加注的玩家需至少為大盲的兩倍。其餘時候若該圈尚未有玩家加注，則想加注的玩家需大於大盲注。若該圈有兩位以上玩家加注或下注(bet)，則需至少大於或等於該圈最後一個下注玩家的金額，加上最後兩個下注玩家的差額。若該圈只有一位玩家下注，則需大於下注玩家的兩倍。</t>
   </si>
   <si>
-    <t>最低 加注 ( min - raise ) 金額 限制 ： 在 翻牌前 ( pre - flop ) 想 第一位 加注 的 玩家 需 至少 為大盲 的 兩倍 。 其餘 時候 若 該 圈 尚未 有 玩家 加注 ， 則想 加注 的 玩家 需大 於 大盲注 。 若該 圈 有 兩位 以上 玩家 加注 或 下注 ( bet ) ， 則需 至少 大 於 或 等 於 該 圈 最後一個 下注 玩家 的 金額 ， 加上 最後兩個 下注 玩家 的 差額 。 若該 圈 只有 一位 玩家 下注 ， 則需 大 於 下注 玩家 的 兩倍 。</t>
+    <t>最低 加注 ( min - raise ) 金額 限制 翻牌前 ( pre - flop ) 想 第一位 加注 玩家 需 至少 為大盲 兩倍 其餘 時候 若 該 圈 尚未 有 玩家 加注 則想 加注 玩家 需大 於 大盲注 若該 圈 有 兩位 以上 玩家 加注 或 下注 ( bet ) 則需 至少 大 於 或 等 於 該 圈 最後一個 下注 玩家 金額 加上 最後兩個 下注 玩家 差額 若該 圈 只有 一位 玩家 下注 則需 大 於 下注 玩家 兩倍</t>
   </si>
   <si>
     <t>德州撲克的基礎行動選項：蓋牌（Fold）與過牌（Check）。蓋牌指玩家放棄繼續這局牌，將底牌交還給發牌者，並失去已投入彩池的籌碼。過牌指在當前下注圈尚未有任何人下注的情況下，玩家選擇不投入籌碼，並將行動權順時針交給下一位玩家。</t>
   </si>
   <si>
-    <t>德州 撲克 的 基礎 行動 選項 ： 蓋牌 （ Fold ） 與 過牌 （ Check ） 。 蓋牌 指 玩家 放棄 繼續 這局 牌 ， 將 底牌 交還給 發牌 者 ， 並 失去 已 投入 彩池 的 籌碼 。 過牌 指在 當前 下注 圈 尚未 有 任何人 下注 的 情況 下 ， 玩家 選擇 不 投入 籌碼 ， 並將 行動權 順時 針交給 下 一位 玩家 。</t>
+    <t>德州撲克 基礎 行動 選項 蓋牌 Fold 過牌 Check 蓋牌 指 玩家 放棄 繼續 這局 牌 將 底牌 交還給 發牌 者 並 失去 已 投入 彩池 籌碼 過牌 指在 當前 下注圈 尚未 有 任何人 下注 情況 下 玩家 選擇 不 投入 籌碼 並將 行動 權 順時針 交給 下 一位 玩家</t>
   </si>
   <si>
     <t>德州撲克的基礎行動選項：跟注（Call）與加注（Raise）。跟注指玩家投入與當前最高下注額相等的籌碼，以獲得繼續參與遊戲的權利。加注指玩家在當前最高下注額的基礎上，進一步提高下注金額，迫使後面的玩家必須跟進更高的金額才能繼續遊戲。</t>
   </si>
   <si>
-    <t>德州 撲克 的 基礎 行動 選項 ： 跟注 （ Call ） 與 加注 （ Raise ） 。 跟注 指 玩家 投入 與 當前 最高 下注 額 相等 的 籌碼 ， 以 獲得 繼續 參與 遊戲 的 權利 。 加注 指 玩家 在 當前 最高 下注 額 的 基礎 上 ， 進 一步 提高 下注 金額 ， 迫使 後 面 的 玩家 必須 跟 進 更 高 的 金額 才能 繼續 遊戲 。</t>
+    <t>德州撲克 基礎 行動 選項 跟注 Call 加注 Raise 跟注 指 玩家 投入 當前 最高 下注 額 相等 籌碼 以 獲得 繼續 參與 遊戲 權利 加注 指 玩家 當前 最高 下注 額 基礎 上 進 一步 提高 下注 金額 迫使 後 面 玩家 必須 跟 進 更 高 金額 才能 繼續 遊戲</t>
   </si>
   <si>
     <t>All-in後未達最低加注額時的限制：若玩家所餘籌碼All-in後仍低於最低加注金額，則此注僅視為跟注（call）而不能被當成加注（raise）。在該圈若未有其他人再加注的情況下，原先已經行動過的加注者僅可選擇跟注補齊或蓋牌，於此圈不可再行加注。</t>
   </si>
   <si>
-    <t>All - in 後 未 達 最低 加注 額時 的 限制 ： 若 玩家 所餘籌碼 All - in 後 仍 低 於 最低 加注 金額 ， 則此 注僅視 為 跟注 （ call ） 而 不能 被 當成 加注 （ raise ） 。 在 該 圈 若 未有 其他人 再 加注 的 情況 下 ， 原先 已經 行動過 的 加注 者 僅可選擇 跟注 補齊 或 蓋牌 ， 於 此圈 不可 再行 加注 。</t>
+    <t>All - in 後 未 達 最低 加注 額時 限制 若 玩家 所餘籌碼 All - in 後 仍 低 於 最低 加注 金額 則此 注僅視 為 跟注 call 不能 當成 加注 raise 該 圈 若 未有 其他人 再 加注 情況 下 原先 已經 行動 過的 加注 者 僅可選擇 跟注 補齊 或 蓋牌 於 此圈 不可 再行 加注</t>
   </si>
   <si>
     <t>All-in後未達最低加注額的特殊變種規則：依少部份賭場規定，若All-in的籌碼量大於最低加注額的一半以上，原加注者即可重新加注。或是規定當連續多個All-in累積的籌碼量，加總已經超過了最小加注額後，原加注者即可重新加注。</t>
   </si>
   <si>
-    <t>All - in 後 未 達 最低 加注 額 的 特殊 變種 規則 ： 依少 部份 賭場 規定 ， 若 All - in 的 籌碼量 大 於 最低 加注 額 的 一半 以上 ， 原 加注 者 即可 重新 加注 。 或是 規定 當連續 多個 All - in 累積 的 籌碼量 ， 加總 已經 超過 了 最小 加注 額 後 ， 原 加注 者 即可 重新 加注 。</t>
+    <t>All - in 後 未 達 最低 加注 額 特殊 變種 規則 依少 部份 賭場 規定 若 All - in 籌碼量 大 於 最低 加注 額 一半 以上 原 加注 者 即可 重新 加注 或是 規定 當連續 多個 All - in 累積 籌碼量 加總 已經 超過 最小 加注 額 後 原 加注 者 即可 重新 加注</t>
   </si>
   <si>
     <t>攤牌(Show down)方式：如有兩名以上的玩家在最後一輪下注結束時仍未蓋牌，則須進行攤牌。每名玩家以自己的兩張底牌，加上桌面五張公共牌，共七張牌中，取最大的五張牌組合決定勝負。當中可包括兩張或一張底牌，甚至只有公共牌，其餘的兩張不列入比較範圍。若一名玩家加注而其他所有玩家均蓋牌，則無需開牌即可贏得彩池。</t>
   </si>
   <si>
-    <t>攤牌 ( Show down ) 方式 ： 如有 兩名 以上 的 玩家 在 最後一輪 下注 結束 時 仍 未蓋牌 ， 則須 進行 攤牌 。 每名 玩家 以 自己 的 兩張 底牌 ， 加上 桌面 五張 公共牌 ， 共七 張牌 中 ， 取 最大 的 五 張牌 組合 決定 勝負 。 當中 可 包括 兩張 或 一張 底牌 ， 甚至 只有 公共牌 ， 其餘 的 兩張 不 列入 比較 範圍 。 若 一名 玩家 加注 而 其他 所有 玩家 均 蓋牌 ， 則無需 開牌 即可 贏得 彩池 。</t>
+    <t>攤牌 ( Show down ) 方式 如有 兩名 以上 玩家 最後一輪 下注 結束 時 仍 未蓋牌 則須 進行 攤牌 每名 玩家 以 自己 兩張 底牌 加上 桌面 五張 公共牌 共七 張牌 中 取 最大 五 張牌 組合 決定 勝負 當中 可 包括 兩張 或 一張 底牌 甚至 只有 公共牌 其餘 兩張 不 列入 比較 範圍 若 一名 玩家 加注 其他 所有 玩家 均 蓋牌 則無需 開牌 即可 贏得 彩池</t>
   </si>
   <si>
     <t>最佳手牌（nut hand）：某五張公用牌翻開後，可判定該局能夠組成的最大可能牌型，即為該局的最佳手牌。</t>
   </si>
   <si>
-    <t>最佳手牌 （ nut hand ） ： 某五張 公用 牌 翻開 後 ， 可 判定 該局 能夠 組成 的 最大 可能 牌型 ， 即為 該局 的 最佳手牌 。</t>
+    <t>最佳手牌 nut hand 某五張 公用 牌 翻開 後 可 判定 該局 能夠 組成 最大 可能 牌型 即為 該局 最佳手牌</t>
   </si>
   <si>
     <t>攤牌平手與次大牌（kicker）規則：如多於一名玩家擁有最大的手牌，彩池由他們平等均分，不能平分的零頭由發牌者順時針方向尚未蓋牌的第一個玩家獲得。若玩家牌型大小相若，須以次大牌（kicker）決定勝負，若次大牌相同則依序比到使用的五張為止。攤牌時只計算數字大小，花色在德州撲克中無分大小。</t>
   </si>
   <si>
-    <t>攤牌 平手 與 次大牌 （ kicker ） 規則 ： 如多 於 一名 玩家 擁有 最大 的 手牌 ， 彩池 由 他們 平等 均分 ， 不能 平分 的 零頭 由 發牌 者 順時針 方向 尚未 蓋牌 的 第一 個 玩家 獲得 。 若 玩家 牌型 大小 相若 ， 須以 次大牌 （ kicker ） 決定 勝負 ， 若 次大牌 相同 則 依序 比 到 使用 的 五張 為止 。 攤牌 時 只 計算數 字 大小 ， 花色 在 德州 撲克中 無分 大小 。</t>
+    <t>攤牌 平手 次大牌 kicker 規則 如多 於 一名 玩家 擁有 最大 手牌 彩池 由 他們 平等 均分 不能 平分 零頭 由 發牌 者 順時針 方向 尚未 蓋牌 第一 個 玩家 獲得 若 玩家 牌型 大小 相若 須以 次大牌 kicker 決定 勝負 若 次大牌 相同 則 依序 比 到 使用 五張 為止 攤牌 時 只 計算 數字 大小 花色 德州撲克 中無分 大小</t>
   </si>
   <si>
     <t>開牌次序與自行蓋牌（muck）：通常未蓋牌玩家可依序自行決定是否開牌。開牌順序為最後一圈的最後加注者為第一開牌者；若全數All-in，由第一個All-in玩家先開；若無人加注，以按鈕位置順時針第一家未蓋牌者先開。決定開牌需兩張底牌全翻，玩家亦可選擇不開牌直接放棄，稱為muck。</t>
   </si>
   <si>
-    <t>開牌 次序 與 自行 蓋牌 （ muck ） ： 通常 未蓋牌 玩家 可 依序 自行 決定 是否 開牌 。 開牌 順序 為 最 後 一圈 的 最 後 加注 者 為 第一 開牌 者 ； 若 全數 All - in ， 由 第一 個 All - in 玩家 先開 ； 若無人 加注 ， 以 按鈕 位置 順時針 第一家 未蓋 牌者 先開 。 決定 開牌 需 兩張 底牌 全翻 ， 玩家 亦可 選擇 不 開牌 直接 放棄 ， 稱為 muck 。</t>
+    <t>開牌 次序 自行 蓋牌 muck 通常 未蓋牌 玩家 可 依序 自行 決定 是否 開牌 開牌 順序 為 最 後 一圈 最 後 加注 者 為 第一 開牌 者 若 全數 All - in 由 第一 個 All - in 玩家 先開 若無人 加注 以 按鈕位 置 順時針 第一家 未蓋 牌者 先開 決定 開牌 需 兩張 底牌 全翻 玩家 亦可 選擇 不 開牌 直接 放棄 稱為 muck</t>
   </si>
   <si>
     <t>主彩池(Main pot)分配規則：當沒有玩家全押(all-in)時，彩池由最後一輪下注結束時，未蓋牌的玩家中牌型最大的者獨得。</t>
   </si>
   <si>
-    <t>主彩池 ( Main pot ) 分配 規則 ： 當沒有 玩家 全押 ( all - in ) 時 ， 彩池 由 最後一輪 下注 結束 時 ， 未蓋牌 的 玩家 中牌 型 最大 的 者 獨得 。</t>
+    <t>主彩池 ( Main pot ) 分配 規則 當沒有 玩家 全押 ( all - in ) 時 彩池 由 最後一輪 下注 結束 時 未蓋牌 玩家 中 牌型 最大 者 獨得</t>
   </si>
   <si>
     <t>邊池(Side pot)形成與分配規則：當有一或多個玩家全押時，超過全押玩家押注金額的部份將會形成一或多個邊池。已全押之玩家無法贏取全押後形成之彩池，最多只能自其他跟牌之玩家處，取得相當於本身全押之總籌碼數。各個邊池由參與該邊池投注中，持有最大牌面的玩家贏得。</t>
   </si>
   <si>
-    <t>邊池 ( Side pot ) 形成 與 分配 規則 ： 當有 一 或 多個 玩家 全押 時 ， 超過 全押 玩家 押注 金額 的 部份 將會 形成 一 或 多個 邊池 。 已 全押 之 玩家 無法 贏取 全押 後 形成 之彩池 ， 最 多 只能 自 其他 跟牌 之 玩家 處 ， 取得 相當 於 本身 全押 之 總籌 碼數 。 各個 邊池 由 參 與 該 邊池 投注 中 ， 持有 最大 牌面 的 玩家 贏得 。</t>
+    <t>邊池 ( Side pot ) 形成 分配 規則 當有 一 或 多個 玩家 全押 時 超過 全押 玩家 押注 金額 部份 將會 形成 一 或 多個 邊池 已 全押 之 玩家 無法 贏取 全押 後 形成 之彩池 最 多 只能 自 其他 跟牌 之 玩家 處 取得 相當 於 本身 全押 之 總籌 碼數 各個 邊池 由 參 該 邊池 投注 中 持有 最大 牌面 玩家 贏得</t>
   </si>
   <si>
     <t>無人跟注的邊池處理：無人跟注的邊池（僅有一位玩家下注，剩下其他玩家都蓋牌）將會由該下注玩家直接贏得，形同退還下注於該邊池之籌碼。</t>
   </si>
   <si>
-    <t>無人 跟注 的 邊池 處理 ： 無人 跟注 的 邊池 （ 僅有 一位 玩家 下注 ， 剩下 其他 玩家 都 蓋牌 ） 將會 由 該 下注 玩家 直接 贏得 ， 形同 退還 下注 於 該 邊池 之 籌碼 。</t>
+    <t>無人 跟注 邊池 處理 無人 跟注 邊池 僅有 一位 玩家 下注 剩下 其他 玩家 蓋牌 將會 由 該 下注 玩家 直接 贏得 形同 退還 下注 於 該 邊池 之 籌碼</t>
   </si>
   <si>
     <t>彩池無法均分時的小額籌碼分配：當彩池由兩個以上玩家平分時，若有無法平分之小額籌碼（零頭），將由順時鐘方向算過去，最靠近發牌者(Dealer)的贏家取得。</t>
   </si>
   <si>
-    <t>彩池 無法 均分 時 的 小額 籌碼 分配 ： 當彩池 由 兩個 以上 玩家 平分 時 ， 若有 無法 平分 之小額 籌碼 （ 零頭 ） ， 將由順 時鐘 方向 算過 去 ， 最靠近 發牌 者 ( Dealer ) 的 贏家 取得 。</t>
+    <t>彩池 無法 均分 時 小額 籌碼 分配 當彩池 由 兩個 以上 玩家 平分 時 若有 無法 平分 之小額 籌碼 零頭 將由順 時鐘 方向 算過 去 最靠近 發牌 者 ( Dealer ) 贏家 取得</t>
   </si>
   <si>
     <t>牌型大小通用規則：德州撲克的牌型大小不分花色，有可能平手，從大到小比牌。若五張比完大小相同，則均分彩池內的籌碼。一般大小依序為：皇家同花順 &gt; 同花順 &gt; 四條（鐵支） &gt; 葫蘆 &gt; 同花 &gt; 順子 &gt; 三條 &gt; 兩對 &gt; 對子 &gt; 散牌（烏龍）。</t>
   </si>
   <si>
-    <t>牌型 大小 通用 規則 ： 德州 撲克 的 牌型 大小 不 分 花色 ， 有 可能 平手 ， 從大到 小比牌 。 若五張 比 完 大小 相同 ， 則 均分 彩池 內 的 籌碼 。 一般 大小 依序 為 ： 皇家同花順 &gt; 同花順 &gt; 四條 （ 鐵支 ） &gt; 葫蘆 &gt; 同花 &gt; 順子 &gt; 三條 &gt; 兩對 &gt; 對子 &gt; 散牌 （ 烏龍 ） 。</t>
+    <t>牌型 大小 通用 規則 德州撲克 牌型 大小 不 分 花色 有 可能 平手 從大到 小比牌 若五張 比 完 大小 相同 則 均分 彩池 內 籌碼 一般 大小 依序 為 皇家同花順 同花順 四條 鐵支 葫蘆 同花 順子 三條 兩對 對子 散牌 烏龍</t>
   </si>
   <si>
     <t>皇家同花順（Royal Straight Flush）與同花順（Straight Flush）：同花順為五張同花色的連續數字牌，數字最大者為贏家。皇家同花順為最大的同花順，由同花色的A、K、Q、J和10組成。若公牌開出最大同花順，則未蓋牌玩家平分籌碼。</t>
   </si>
   <si>
-    <t>皇家同花順 （ Royal Straight Flush ） 與 同花順 （ Straight Flush ） ： 同花順 為 五 張同 花色 的 連續數 字牌 ， 數字 最大者 為 贏家 。 皇家同花順 為 最大 的 同花順 ， 由同 花色 的 A 、 K 、 Q 、 J 和 10 組成 。 若公牌 開出 最大 同花順 ， 則未蓋牌 玩家 平分 籌碼 。</t>
+    <t>皇家同花順 Royal Straight Flush 同花順 Straight Flush 同花順 為 五 張同 花色 連續 數字 牌 數字 最大者 為 贏家 皇家同花順 為 最大 同花順 由同 花色 A K Q J 和 10 組成 若公牌 開出 最大 同花順 則未蓋牌 玩家 平分 籌碼</t>
   </si>
   <si>
     <t>四條（鐵支，Four of a kind）：其中四張是相同數字的牌，第五張是剩下牌組中最大的一張牌。若有一家以上持有四條，則比較第五張起腳牌（kicker），最大者為贏家；若第五張也相同則平分彩池。</t>
   </si>
   <si>
-    <t>四條 （ 鐵支 ， Four of a kind ） ： 其中 四張 是 相同 數字 的 牌 ， 第五 張是 剩下 牌組 中 最大 的 一 張牌 。 若有 一家 以上 持有 四條 ， 則比較 第五 張起 腳牌 （ kicker ） ， 最大者 為 贏家 ； 若 第五 張 也 相同 則 平分 彩池 。</t>
+    <t>四條 鐵支 Four of a kind 其中 四張 相同 數字 牌 第五 張是 剩下 牌組 中 最大 一 張牌 若有 一家 以上 持有 四條 則比較 第五 張起 腳牌 kicker 最大者 為 贏家 若 第五 張 相同 則 平分 彩池</t>
   </si>
   <si>
     <t>葫蘆（滿堂紅，Full house）：由三張相同數字及任何兩張其他相同數字的牌組成。如果同時有多人拿到葫蘆，三張相同數字中較大者為贏家；若三張數字相同，則再比剩下兩張牌中數字較大者。</t>
   </si>
   <si>
-    <t>葫蘆 （ 滿堂紅 ， Full house ） ： 由三張 相同 數字 及 任何 兩張 其他 相同 數字 的 牌 組成 。 如果 同時 有 多 人 拿到 葫蘆 ， 三張 相同 數字 中較 大者 為 贏家 ； 若三張 數字 相同 ， 則再 比 剩下 兩張牌 中數 字 較 大者 。</t>
+    <t>葫蘆 滿堂紅 Full house 由三張 相同 數字 及 任何 兩張 其他 相同 數字 牌 組成 如果 同時 有 多 人 拿到 葫蘆 三張 相同 數字 中較 大者 為 贏家 若三張 數字 相同 則再 比 剩下 兩張牌 中 數字 較大者</t>
   </si>
   <si>
     <t>同花（Flush）：由五張不按順序但相同花色的牌組成。如果不只一人有此牌組，則牌面數字最大的人贏得該局；如果最大數字相同，則依序由第二、第三、第四或者第五張牌來決定勝負。</t>
   </si>
   <si>
-    <t>同花 （ Flush ） ： 由五張 不 按 順序 但 相同 花色 的 牌 組成 。 如果 不 只 一人 有 此牌 組 ， 則牌 面數 字 最大 的 人 贏得 該局 ； 如果 最大 數字 相同 ， 則 依序 由 第二 、 第三 、 第四 或者 第五 張牌 來 決定 勝負 。</t>
+    <t>同花 Flush 由五張 不 按 順序 但 相同 花色 牌 組成 如果 不 只 一人 有 此牌 組 則牌面 數字 最大 人 贏得 該局 如果 最大 數字 相同 則 依序 由 第二 第三 第四 或者 第五 張牌 來 決定 勝負</t>
   </si>
   <si>
     <t>順子（Straight）：由五張連續數字的牌組成。如果不只一人有此牌組，則五張牌中數字最大的贏得此局。其中 10-J-Q-K-A 為最大的順子，A-2-3-4-5 為最小的順子。</t>
   </si>
   <si>
-    <t>順子 （ Straight ） ： 由五張 連續 數字 的 牌 組成 。 如果 不 只 一人 有 此牌 組 ， 則五 張牌 中數 字 最大 的 贏得 此局 。 其中 10 - J - Q - K - A 為 最大 的 順子 ， A - 2 - 3 - 4 - 5 為 最小 的 順子 。</t>
+    <t>順子 Straight 由五張 連續 數字 牌 組成 如果 不 只 一人 有 此牌 組 則五 張牌 中 數字 最大 贏得 此局 其中 10 - J - Q - K - A 為 最大 順子 A - 2 - 3 - 4 - 5 為 最小 順子</t>
   </si>
   <si>
     <t>三條（Three of a kind）：由三張相同數字和兩張不同數字的雜牌組成。如果不只一人有此牌組，則三張牌中數字最大者贏得該局。若三張數字相同，則依序比較剩下的兩張雜牌。</t>
   </si>
   <si>
-    <t>三條 （ Three of a kind ） ： 由三張 相同 數字 和 兩張 不同 數字 的 雜牌 組成 。 如果 不 只 一人 有 此牌 組 ， 則三 張牌 中數 字 最大者 贏得 該局 。 若三張 數字 相同 ， 則 依序 比較 剩下 的 兩張 雜牌 。</t>
+    <t>三條 Three of a kind 由三張 相同 數字 和 兩張 不同 數字 雜牌 組成 如果 不 只 一人 有 此牌 組 則三 張牌 中 數字 最大者 贏得 該局 若三張 數字 相同 則 依序 比較 剩下 兩張 雜牌</t>
   </si>
   <si>
     <t>兩對（Two pair）、對子（Pair）與散牌（高牌，High card）：兩對由兩組同數字對子加一張雜牌組成；對子由兩張同數字加三張雜牌組成；散牌為無法組成牌型的五張雜牌。比牌時皆由持有的最大對子先比，若相同則依序比較剩下的雜牌（kicker），數字大者勝。</t>
   </si>
   <si>
-    <t>兩對 （ Two pair ） 、 對子 （ Pair ） 與 散牌 （ 高牌 ， High card ） ： 兩對 由 兩 組同 數字 對子 加一張 雜牌 組成 ； 對子 由 兩張 同數 字 加三張 雜牌 組成 ； 散牌 為 無法 組成 牌型 的 五張 雜牌 。 比牌 時 皆 由 持有 的 最大 對子 先比 ， 若 相同 則 依序 比較 剩下 的 雜牌 （ kicker ） ， 數字 大者勝 。</t>
+    <t>兩對 Two pair 對子 Pair 散牌 高牌 High card 兩對 由 兩 組同 數字 對子 加一張 雜牌 組成 對子 由 兩 張同 數字 加三張 雜牌 組成 散牌 為 無法 組成 牌型 五張 雜牌 比牌 時 皆 由 持有 最大 對子 先比 若 相同 則 依序 比較 剩下 雜牌 kicker 數字 大者勝</t>
   </si>
   <si>
     <t>限注式德州撲克（Limit Texas Hold'em）：下注金額是固定的。首兩輪（即翻牌前和翻牌）的下注和加注須與大盲注相同，稱為「小注」。其後兩輪（即轉牌和河牌）的下注和加注須等於大盲注的兩倍，稱為「大注」。每一個押注圈只允許最多四次動作，即一次下注與三次加注（下注、加注、再加注、最後加注），達到上限後任何人皆不能再加注。</t>
   </si>
   <si>
-    <t>限注 式 德州 撲克 （ Limit Texas Hold ' em ） ： 下注 金額 是 固定 的 。 首兩輪 （ 即 翻牌前 和 翻牌 ） 的 下注 和 加注 須與 大盲注 相同 ， 稱為 「 小注 」 。 其後兩輪 （ 即 轉牌 和 河牌 ） 的 下注 和 加注 須等 於 大盲注 的 兩倍 ， 稱為 「 大注 」 。 每一個 押注 圈 只 允許 最多 四次 動作 ， 即 一次 下注 與 三次 加注 （ 下注 、 加注 、 再 加注 、 最 後 加注 ） ， 達到 上限 後 任何人 皆 不能 再 加注 。</t>
+    <t>限注式 德州撲克 Limit Texas Hold ' em 下注 金額 固定 首兩輪 即 翻牌前 和 翻牌 下注 和 加注 須與 大盲注 相同 稱為 小注 其後兩輪 即 轉牌 和 河牌 下注 和 加注 須等 於 大盲注 兩倍 稱為 大注 每一個 押注 圈 只 允許 最多 四次 動作 即 一次 下注 三次 加注 下注 加注 再 加注 最 後 加注 達到 上限 後 任何人 皆 不能 再 加注</t>
   </si>
   <si>
     <t>彩池限注德州撲克（Pot-limit Texas Hold'em）：每輪下注過程中，下注金額最低須等於大盲注金額。加注額設有上限限制，玩家最大可加注與目前底池金額相等的籌碼。計算可加注的最大彩池上限時，需先包含本次自己必須跟注（call）的籌碼量。每輪加注次數並沒有限制。</t>
   </si>
   <si>
-    <t>彩池限注 德州 撲克 （ Pot - limit Texas Hold ' em ） ： 每輪 下注 過程 中 ， 下注 金額 最低 須等 於 大盲注 金額 。 加注 額設 有 上限 限制 ， 玩家 最大 可 加注 與 目前 底池 金額 相等 的 籌碼 。 計算 可 加注 的 最大 彩池 上限 時 ， 需先 包含 本次 自己 必須 跟注 （ call ） 的 籌碼量 。 每輪 加注 次數 並沒有 限制 。</t>
+    <t>彩池限注 德州撲克 Pot - limit Texas Hold ' em 每輪 下注 過程 中 下注 金額 最低 須等 於 大盲注 金額 加注 額設 有 上限 限制 玩家 最大 可 加注 目前 底池 金額 相等 籌碼 計算 可 加注 最大 彩池 上限 時 需先 包含 本次 自己 必須 跟注 call 籌碼量 每輪 加注 次數 並沒有 限制</t>
   </si>
   <si>
     <t>無限注德州撲克（No-limit Texas Hold'em）：為最受歡迎的變種玩法。玩家在輪到自己下注時，可下注檯面上任何下限以上的籌碼，最大可下注當時持有的全部籌碼，即為「全押」（All-in）。下注金額最低須等於大盲注金額；若要加注，最小加注額為大盲注或該輪最後一次加注額之較大者（加注幅度至少需等於前次的加注額）。每一輪可加注的籌碼和次數均無上限。</t>
   </si>
   <si>
-    <t>無限注 德州 撲克 （ No - limit Texas Hold ' em ） ： 為 最受 歡迎 的 變種 玩法 。 玩家 在 輪 到 自己 下注 時 ， 可 下注 檯 面上 任何 下限 以上 的 籌碼 ， 最大 可 下注 當時 持有 的 全部 籌碼 ， 即為 「 全押 」 （ All - in ） 。 下注 金額 最低 須等 於 大盲注 金額 ； 若 要 加注 ， 最小 加注 額為 大盲注 或 該 輪 最 後 一次 加注 額之較 大者 （ 加注 幅度 至少 需等 於 前次 的 加注 額 ） 。 每一輪 可 加注 的 籌碼 和 次 數均 無 上限 。</t>
+    <t>無限注 德州撲克 No - limit Texas Hold ' em 為 最受 歡迎 變種 玩法 玩家 輪 到 自己 下注 時 可 下注 檯 面上 任何 下限 以上 籌碼 最大 可 下注 當時 持有 全部 籌碼 即為 全押 All - in 下注 金額 最低 須等 於 大盲注 金額 若 要 加注 最小 加注 額為 大盲注 或 該 輪 最 後 一次 加注 額之較 大者 加注 幅度 至少 需等 於 前次 加注 額 每一輪 可 加注 籌碼 和 次 數均 無 上限</t>
   </si>
   <si>
     <t>德州撲克的位置策略：位置往往比牌力更關鍵，行動越晚資訊越多。SB與BB（盲注位）翻牌後最先行動，資訊最少，應打得更保守。UTG與MP（前中位）起手牌範圍要嚴格，避免邊緣牌。CO與BTN（後位）可以主動偷盲、控制底池。同一手牌在後位是賺錢牌，在前位可能是陷阱。</t>
   </si>
   <si>
-    <t>德州 撲克 的 位置 策略 ： 位置 往往 比牌力 更 關鍵 ， 行動 越晚 資訊越 多 。 SB 與 BB （ 盲注位 ） 翻牌後 最 先行 動 ， 資訊 最少 ， 應打 得 更 保守 。 UTG 與 MP （ 前中位 ） 起手 牌範圍 要 嚴格 ， 避免 邊緣牌 。 CO 與 BTN （ 後位 ） 可以 主動 偷盲 、 控制 底池 。 同一 手牌 在 後位 是 賺 錢牌 ， 在 前位 可能 是 陷阱 。</t>
+    <t>德州撲克 位置 策略 位置 往往 比牌力 更 關鍵 行動 越晚 資訊越 多 SB BB 盲注位 翻牌後 最先 行動 資訊 最少 應打 得 更 保守 UTG MP 前中位 起手 牌範圍 要 嚴格 避免 邊緣牌 CO BTN 後位 可以 主動 偷盲 控制 底池 同一 手牌 後位 賺 錢牌 前位 可能 陷阱</t>
   </si>
   <si>
     <t>起手牌選擇範圍：早位應以強牌（如AA至TT對子、AK、AQs）為主；中位可加入AQo、KQs及中等對子；後位可放寬到ATo以上、同花連張及小對子來偷盲或看翻牌。同花牌價值通常大於雜色牌，因為帶有順子、同花與阻斷牌的操作潛力。</t>
   </si>
   <si>
-    <t>起手牌 選擇 範圍 ： 早位 應以 強牌 （ 如 AA 至 TT 對子 、 AK 、 AQs ） 為主 ； 中位 可 加入 AQo 、 KQs 及 中等 對子 ； 後位 可放 寬 到 ATo 以上 、 同花 連張 及 小 對子 來 偷 盲 或 看 翻牌 。 同花 牌價值 通常 大 於 雜色牌 ， 因為 帶 有 順子 、 同花 與 阻斷 牌 的 操作 潛力 。</t>
+    <t>起手牌 選擇 範圍 早位 應以 強牌 如 AA 至 TT 對子 AK AQs 為主 中位 可 加入 AQo KQs 及 中等 對子 後位 可放 寬 到 ATo 以上 同花 連張 及 小 對子 來 偷 盲 或 看 翻牌 同花 牌價值 通常 大 於 雜色牌 因為 帶 有 順子 同花 阻斷 牌 操作 潛力</t>
   </si>
   <si>
     <t>翻牌後數學與2與4法則：Pot Odds（底池賠率）公式為「要跟的籌碼 ÷（底池＋要跟）」。快速估算聽牌成功率可使用「2與4法則」：剩一張牌可看時，成功率約為 outs（出路）乘上 2%；剩兩張牌可看時，約為 outs 乘上 4%。若計算出的聽牌成功率大於或等於 Pot Odds，跟注通常是正期望值（EV+）。</t>
   </si>
   <si>
-    <t>翻牌後 數學 與 2 與 4 法則 ： Pot Odds （ 底池 賠率 ） 公式 為 「 要 跟 的 籌碼 ÷ （ 底池 ＋ 要 跟 ） 」 。 快速 估算 聽牌 成功率 可 使用 「 2 與 4 法則 」 ： 剩一 張牌 可 看時 ， 成功率 約 為 outs （ 出路 ） 乘 上 2% ； 剩兩 張牌 可 看時 ， 約 為 outs 乘 上 4% 。 若計算出 的 聽牌 成功率 大 於 或 等 於 Pot Odds ， 跟注 通常 是 正 期望值 （ EV + ） 。</t>
+    <t>翻牌後 數學 2 4 法則 Pot Odds 底池 賠率 公式 為 要 跟 籌碼 ÷ 底池 ＋ 要 跟 快速 估算 聽牌 成功率 可 使用 2 4 法則 剩一 張牌 可 看時 成功率 約 為 outs 出路 乘 上 2% 剩兩 張牌 可 看時 約 為 outs 乘 上 4% 若計算出 聽牌 成功率 大 於 或 等 於 Pot Odds 跟注 通常 正 期望值 EV +</t>
   </si>
   <si>
     <t>常見聽牌機率與賠率：同花聽牌（Flush Draw）有9張outs，翻牌到河牌成功率約35%，賠率約1.9比1。開口順子聽牌（OESD）有8張outs，成功率約31.5%，賠率約2.1比1。內聽順子（Gutshot）有4張outs，成功率約16.5%，賠率約5比1。</t>
   </si>
   <si>
-    <t>常見 聽牌 機率 與 賠率 ： 同花 聽牌 （ Flush Draw ） 有 9 張 outs ， 翻牌 到 河牌 成功率 約 35% ， 賠率 約 1.9 比 1 。 開口 順子 聽牌 （ OESD ） 有 8 張 outs ， 成功率 約 31.5% ， 賠率 約 2.1 比 1 。 內 聽 順子 （ Gutshot ） 有 4 張 outs ， 成功率 約 16.5% ， 賠率 約 5 比 1 。</t>
+    <t>常見 聽牌 機率 賠率 同花 聽牌 Flush Draw 有 9 張 outs 翻牌 到 河牌 成功率 約 35% 賠率 約 1.9 比 1 開口 順子 聽牌 OESD 有 8 張 outs 成功率 約 31.5% 賠率 約 2.1 比 1 內 聽 順子 Gutshot 有 4 張 outs 成功率 約 16.5% 賠率 約 5 比 1</t>
   </si>
   <si>
     <t>遊戲人數與牌局組成：德州撲克一般支援 2 到 10 名玩家，現金局（Cash Game）通常以 6 到 9 人最為普遍。遊戲中每位玩家會獲發 2 張隱藏的「手牌（Hole cards）」。桌面會發出 5 張所有人共用的「公共牌（Community cards）」，分為前三張的「翻牌（Flop）」、第四張的「轉牌（Turn）」與第五張的「河牌（River）」。</t>
   </si>
   <si>
-    <t>遊戲 人數 與 牌局 組成 ： 德州 撲克 一般 支援 2 到 10 名 玩家 ， 現金局 （ Cash Game ） 通常 以 6 到 9 人 最 為 普遍 。 遊戲 中 每位 玩家 會 獲發 2 張隱藏 的 「 手牌 （ Hole cards ） 」 。 桌面 會 發出 5 張 所有人 共用 的 「 公共牌 （ Community cards ） 」 ， 分為 前三張 的 「 翻牌 （ Flop ） 」 、 第四 張 的 「 轉牌 （ Turn ） 」 與 第五 張 的 「 河牌 （ River ） 」 。</t>
+    <t>遊戲 人數 牌局 組成 德州撲克 一般 支援 2 到 10 名 玩家 現金局 Cash Game 通常 以 6 到 9 人 最 為 普遍 遊戲 中 每位 玩家 會 獲發 2 張隱藏 手牌 Hole cards 桌面 會 發出 5 張 所有人 共用 公共牌 Community cards 分為 前三張 翻牌 Flop 第四 張 轉牌 Turn 第五 張 河牌 River</t>
   </si>
   <si>
     <t>最佳五張牌組合與打公牌（Play the board）：玩家需從手裡的 2 張手牌，加上桌面的 5 張公共牌，共 7 張牌中選出任意 5 張，做出最大的牌型組合。這 5 張牌可以是手裡 2 張加桌面 3 張，或是手裡 1 張加桌面 4 張；若桌面 5 張公共牌已是最大組合，也可以完全不使用手牌，稱為「打公牌（Play the board）」。</t>
   </si>
   <si>
-    <t>最佳 五張牌 組合 與 打公牌 （ Play the board ） ： 玩家 需從 手裡 的 2 張手牌 ， 加上 桌面 的 5 張 公共牌 ， 共 7 張牌 中選出 任意 5 張 ， 做出 最大 的 牌型 組合 。 這 5 張牌 可以 是 手裡 2 張加 桌面 3 張 ， 或是 手裡 1 張加 桌面 4 張 ； 若 桌面 5 張 公共牌 已 是 最大 組合 ， 也 可以 完全 不 使用 手牌 ， 稱為 「 打公牌 （ Play the board ） 」 。</t>
+    <t>最佳 五張牌 組合 打公牌 Play the board 玩家 需從 手裡 2 張手牌 加上 桌面 5 張 公共牌 共 7 張牌 中選出 任意 5 張 做出 最大 牌型 組合 這 5 張牌 可以 手裡 2 張加 桌面 3 張 或是 手裡 1 張加 桌面 4 張 若 桌面 5 張 公共牌 已 最大 組合 可以 完全 不 使用 手牌 稱為 打公牌 Play the board</t>
   </si>
   <si>
     <t>盲注與發牌順序：發牌前，小盲位（Small Blind, SB）與大盲位（Big Blind, BB）玩家必須強制支付盲注籌碼。發牌時由小盲位開始，接著是大盲、槍口位（Under the Gun, UTG），依順時針方向輪流，最後發給莊家按鈕位（Button）。每位玩家共會獲發兩張手牌。</t>
   </si>
   <si>
-    <t>盲注 與 發牌 順序 ： 發牌 前 ， 小盲位 （ Small Blind , SB ） 與 大盲位 （ Big Blind , BB ） 玩家 必須 強制 支付 盲注 籌碼 。 發牌 時 由 小盲位 開始 ， 接著 是 大盲 、 槍口位 （ Under the Gun , UTG ） ， 依順 時針 方向 輪流 ， 最後發給 莊家按鈕位 （ Button ） 。 每位 玩家 共會 獲發 兩張 手牌 。</t>
+    <t>盲注 發牌 順序 發牌 前 小盲位 Small Blind , SB 大盲位 Big Blind , BB 玩家 必須 強制 支付 盲注 籌碼 發牌 時 由 小盲位 開始 接著 大盲 槍口位 Under the Gun , UTG 依 順時針 方向 輪流 最後發給 莊家 按鈕位 Button 每位 玩家 共會 獲發 兩張 手牌</t>
   </si>
   <si>
     <t>翻牌前後行動順序與選項：翻牌前（Pre-flop）因為盲注已下注，由大盲注左側的槍口位（UTG）第一個行動，可選擇棄牌（Fold）、跟注（Call）或加注（Raise）。翻牌後（Post-flop）則由小盲位開始行動；若該下注圈尚未有人下注，玩家多出「過牌（Check）」的選擇。若前方已經有人下注或加注，則後方玩家不能選擇過牌。</t>
   </si>
   <si>
-    <t>翻牌前 後 行動 順序 與 選項 ： 翻牌前 （ Pre - flop ） 因為 盲注 已 下注 ， 由 大盲注 左側 的 槍口位 （ UTG ） 第一 個 行動 ， 可選擇 棄牌 （ Fold ） 、 跟注 （ Call ） 或 加注 （ Raise ） 。 翻牌後 （ Post - flop ） 則由 小盲位 開 始行 動 ； 若該 下注 圈 尚未 有人 下注 ， 玩家 多出 「 過牌 （ Check ） 」 的 選擇 。 若 前方 已經 有人 下注 或 加注 ， 則後方 玩家 不能 選擇 過牌 。</t>
+    <t>翻牌前 後 行動 順序 選項 翻牌前 Pre - flop 因為 盲注 已 下注 由 大盲注 左側 槍口位 UTG 第一 個 行動 可選擇 棄牌 Fold 跟注 Call 或 加注 Raise 翻牌後 Post - flop 則由 小盲位 開始 行動 若該 下注圈 尚未 有人 下注 玩家 多出 過牌 Check 選擇 若 前方 已經 有人 下注 或 加注 則後方 玩家 不能 選擇 過牌</t>
   </si>
   <si>
     <t>下注圈結束的標誌：每一輪下注（Betting round）結束的標誌是，所有決定繼續參與該局的玩家，最終都投入了一樣多的籌碼於彩池中。如果玩家不想再投入與其他人同等的籌碼，就必須選擇棄牌（Fold）。</t>
   </si>
   <si>
-    <t>下注 圈 結束 的 標誌 ： 每一輪 下注 （ Betting round ） 結束 的 標誌 是 ， 所有 決定 繼續 參與 該局 的 玩家 ， 最終 都 投入 了 一樣 多 的 籌碼 於 彩池 中 。 如果 玩家 不想 再 投入 與 其他人 同等 的 籌碼 ， 就 必須 選擇 棄牌 （ Fold ） 。</t>
+    <t>下注圈 結束 標誌 每一輪 下注 Betting round 結束 標誌 所有 決定 繼續 參與 該局 玩家 最終 投入 一樣 多 籌碼 於 彩池 中 如果 玩家 不想 再 投入 其他人 同等 籌碼 必須 選擇 棄牌 Fold</t>
   </si>
   <si>
     <t>銷牌（Burn card）規則：在發出任何公共牌（翻牌、轉牌、河牌）之前，發牌員都必須先「銷牌（Burn）」，即捨棄牌堆頂端的第一張牌（不予使用）。銷牌後才發出公共牌（翻牌發 3 張，轉牌與河牌各發 1 張），此機制的目的是為了防止作弊或作號。</t>
   </si>
   <si>
-    <t>銷牌 （ Burn card ） 規則 ： 在 發出 任何 公共牌 （ 翻牌 、 轉牌 、 河牌 ） 之前 ， 發牌員 都 必須 先 「 銷牌 （ Burn ） 」 ， 即 捨 棄牌 堆頂 端的 第一 張牌 （ 不予 使用 ） 。 銷牌 後 才 發出 公共牌 （ 翻牌 發 3 張 ， 轉牌 與 河牌 各發 1 張 ） ， 此機制 的 目的 是 為 了 防止 作弊 或 作號 。</t>
+    <t>銷牌 Burn card 規則 發出 任何 公共牌 翻牌 轉牌 河牌 之前 發牌員 必須 先 銷牌 Burn 即 捨 棄牌 堆頂 端的 第一 張牌 不予 使用 銷牌 後 才 發出 公共牌 翻牌 發 3 張 轉牌 河牌 各發 1 張 此機制 目的 為 防止 作弊 或 作號</t>
   </si>
   <si>
     <t>翻牌後行動順序與棄牌遞延：翻牌後的各個下注圈，標準順序是由小盲位開始順時針行動，按鈕位（Button）通常是最後一個行動的優勢位置。若前方的盲注位玩家已棄牌，則由按鈕位左側「剩下未棄牌的第一位玩家」開始行動。</t>
   </si>
   <si>
-    <t>翻牌後 行動 順序 與 棄牌 遞延 ： 翻牌後 的 各個 下注 圈 ， 標準 順序 是 由 小盲位 開始 順時 針行動 ， 按 鈕位 （ Button ） 通常 是 最後一個 行動 的 優勢 位置 。 若 前方 的 盲注位 玩家 已 棄牌 ， 則由 按 鈕位 左側 「 剩下 未 棄牌 的 第一位 玩家 」 開 始行 動 。</t>
+    <t>翻牌後 行動 順序 棄牌 遞延 翻牌後 各個 下注圈 標準 順序 由 小盲位 開始 順時針 行動 按鈕位 Button 通常 最後一個 行動 優勢 位置 若 前方 盲注位 玩家 已 棄牌 則由 按鈕位 左側 剩下 未 棄牌 第一位 玩家 開始 行動</t>
   </si>
   <si>
     <t>攤牌與下注逼退（Bluffing 概念）：在最後一圈行動中，若所有玩家皆選擇過牌（Check）或跟注至金額相同，則進入攤牌（Showdown）比大小。若玩家不想攤牌比牌力，可以選擇下注或加注更多的籌碼，利用下注壓力迫使跟不下的對手棄牌（Fold），藉此直接贏得底池。</t>
   </si>
   <si>
-    <t>攤牌 與 下注 逼退 （ Bluffing 概念 ） ： 在 最 後 一圈 行動 中 ， 若 所有 玩家 皆 選擇 過牌 （ Check ） 或 跟注 至金額 相同 ， 則進入 攤牌 （ Showdown ） 比 大小 。 若 玩家 不想 攤牌 比牌力 ， 可以 選擇 下注 或 加注 更 多 的 籌碼 ， 利用 下注 壓力 迫使 跟 不下 的 對 手 棄牌 （ Fold ） ， 藉此 直接 贏得 底池 。</t>
+    <t>攤牌 下注 逼退 Bluffing 概念 最 後 一圈 行動 中 若 所有 玩家 皆 選擇 過牌 Check 或 跟注 至金額 相同 則進入 攤牌 Showdown 比 大小 若 玩家 不想 攤牌 比牌力 可以 選擇 下注 或 加注 更 多 籌碼 利用 下注 壓力 迫使 跟 不下 對手 棄牌 Fold 藉此 直接 贏得 底池</t>
   </si>
   <si>
     <t>新加入牌桌的觀察策略與玩家分類：加入新牌桌時不應急於入局，應優先觀察對手打法。特別是透過對手攤牌（Showdown）時秀出的底牌，回溯其下注邏輯。這有助於快速將玩家分類，辨識出高手、激進型玩家、保守型玩家、喜歡詐唬（Bluff）的玩家，以及情緒失控（上頭 / Tilt）的玩家。</t>
   </si>
   <si>
-    <t>新 加入 牌桌 的 觀察 策略 與 玩家 分類 ： 加入 新 牌桌 時不應 急 於 入局 ， 應 優先 觀察 對 手 打法 。 特別 是 透過 對手 攤牌 （ Showdown ） 時秀出 的 底牌 ， 回溯 其 下注 邏輯 。 這 有助 於 快速 將 玩家 分類 ， 辨識出 高手 、 激進型 玩家 、 保守 型 玩家 、 喜歡 詐 唬 （ Bluff ） 的 玩家 ， 以及 情緒 失控 （ 上頭 / Tilt ） 的 玩家 。</t>
+    <t>新 加入 牌桌 觀察 策略 玩家 分類 加入 新 牌桌 時不應 急 於 入局 應 優先 觀察 對手 打法 特別 透過 對手 攤牌 Showdown 時秀出 底牌 回溯 其 下注 邏輯 這 有助 於 快速 將 玩家 分類 辨識出 高手 激進型 玩家 保守 型 玩家 喜歡 詐唬 Bluff 玩家 情緒 失控 上頭 Tilt 玩家</t>
   </si>
   <si>
     <t>翻牌前的看牌時機與肢體語言（Tells）：翻牌前（Pre-flop）不應一拿到手牌就立刻查看，以免下意識的表情或肢體動作洩漏自身的牌力意圖給對手。正確的做法是先觀察其他玩家看牌時的反應來搜集資訊，直到輪到自己行動時才查看底牌，以確保透露給對手的資訊降至最低。</t>
   </si>
   <si>
-    <t>翻牌前 的 看牌 時機 與 肢體 語言 （ Tells ） ： 翻牌前 （ Pre - flop ） 不應 一 拿到 手牌 就 立刻 查看 ， 以免 下意識 的 表情 或肢 體動作 洩漏 自身 的 牌力意 圖給 對 手 。 正確 的 做法 是 先 觀察 其他 玩家 看牌 時 的 反應 來 搜集 資訊 ， 直到 輪到 自己 行動時 才 查看 底牌 ， 以確 保 透露 給對 手 的 資訊降 至 最低 。</t>
-  </si>
-  <si>
-    <t>Step.1 坐下：您可以在賭場的空位中自由選擇座位，但是在德州撲克中與座位是一個非常重要的因素，因此在賽事或與牌友玩時通常，座位的順序由規定好的座位表或撲克牌確定。</t>
-  </si>
-  <si>
-    <t>Step.1 坐下 ： 您 可以 在 賭場 的 空位 中 自由 選擇 座位 ， 但是 在 德州 撲克中 與 座位 是 一個 非常 重要 的 因素 ， 因此 在 賽事 或 與 牌友 玩時 通常 ， 座位 的 順序 由 規定 好 的 座位表 或 撲克牌 確定 。</t>
-  </si>
-  <si>
-    <t>Step.2 荷官莊家位置的確定：座位決定之後，接下來決定荷官莊家位。第一個按鈕莊家的位置是荷官（發牌的人）將牌一張一張地分發給玩家，拿到最強牌的人確定為莊家位。 確定按鈕莊家位的玩家後，就開始正式發牌。</t>
-  </si>
-  <si>
-    <t>Step.2 荷官 莊家 位置 的 確定 ： 座位 決定 之 後 ， 接下 來 決定 荷官 莊家位 。 第一 個 按 鈕莊家 的 位置 是 荷官 （ 發牌 的 人 ） 將牌 一張 一張 地分 發給 玩家 ， 拿到 最強 牌 的 人 確定 為 莊家位 。 確定 按鈕 莊家位 的 玩家 後 ， 就 開始 正式 發牌 。</t>
-  </si>
-  <si>
-    <t>Step.3 發牌：每個玩家發到2張排面朝下的牌，游戲開始。 這2張牌稱為「底牌」或「口袋牌」。 游戲中只有2張牌是發給每位玩家的，除了進行攤牌外，沒有必要將它展示給其他玩家，並且必須 小心不要被人看到它。</t>
-  </si>
-  <si>
-    <t>Step.3 發牌 ： 每個 玩家 發到 2 張排 面朝 下 的 牌 ， 游戲 開始 。 這 2 張牌 稱 為 「 底牌 」 或 「 口袋 牌 」 。 游戲 中 只有 2 張牌 是 發給 每位 玩家 的 ， 除了 進行 攤牌 外 ， 沒有 必要 將它 展示 給 其他 玩家 ， 並且 必須 小心 不要 被 人 看到 它 。</t>
-  </si>
-  <si>
-    <t>Step.4 翻牌前：先下大小盲注，然後給每個玩家發2張底牌，大盲注後面第一個玩家選擇跟注、加注或者蓋牌放棄，按照順時針方向，其他玩家依次表態，大盲注玩家最後表態 ，如果玩家有加注情況，前面已經跟注的玩家需要再次表態甚至多次表態。</t>
-  </si>
-  <si>
-    <t>Step.4 翻牌前 ： 先下 大 小盲注 ， 然後給 每個 玩家 發 2 張 底牌 ， 大盲注 後 面 第一 個 玩家 選擇 跟注 、 加注 或者 蓋牌 放棄 ， 按照 順時針 方向 ， 其他 玩家 依次 表態 ， 大盲注 玩家 最後表態 ， 如果 玩家 有 加注 情況 ， 前面 已經 跟注 的 玩家 需要 再次 表態 甚至 多次 表態 。</t>
-  </si>
-  <si>
-    <t>Step.5 翻牌：同時發三張公牌，由小盲注開始（如果小盲注已蓋牌，由後面最近的玩家開始，以此類推），按照順時針方向依次表態，玩家可以選擇下注、加注、或者蓋牌放棄。</t>
-  </si>
-  <si>
-    <t>Step.5 翻牌 ： 同時 發三張 公牌 ， 由 小盲注 開始 （ 如果 小盲注 已蓋牌 ， 由後面 最近 的 玩家 開始 ， 以此 類推 ） ， 按照 順時針 方向 依次 表態 ， 玩家 可以 選擇 下注 、 加注 、 或者 蓋牌 放棄 。</t>
-  </si>
-  <si>
-    <t>Step.6 轉牌&amp;河牌：Turn—發第四張牌，由小盲注開始，按照順時針方向依次表態。 River—發第五張牌，由小盲注開始，按照順時針方向依次表態，玩家可以選擇下注、加注、或者蓋牌放棄。經過前面四輪發牌和下注，還剩餘2名以上的玩家時，開始比大小，這時候需要亮牌。</t>
-  </si>
-  <si>
-    <t>Step.6 轉牌 &amp; 河牌 ： Turn — 發 第四 張牌 ， 由 小盲注 開始 ， 按照 順時針 方向 依次 表態 。 River — 發 第五 張牌 ， 由 小盲注 開始 ， 按照 順時針 方向 依次 表態 ， 玩家 可以 選擇 下注 、 加注 、 或者 蓋牌 放棄 。 經過 前面 四輪 發牌 和 下注 ， 還剩 餘 2 名 以上 的 玩家 時 ， 開始 比 大小 ， 這時候 需要 亮牌 。</t>
-  </si>
-  <si>
-    <t>Step.7 亮牌：剩餘2名以上的玩家開始亮牌比大小，成牌最大的玩家贏取池底。亮牌是用自己的2張底牌和5張公共牌結合在一起，選出5張牌，通過比大小決定勝者。不論手中的牌使用幾張（甚至可以不用手中的底牌），湊成最大的成牌，跟其他玩家比大小。</t>
-  </si>
-  <si>
-    <t>Step.7 亮牌 ： 剩餘 2 名 以上 的 玩家 開始 亮牌 比 大小 ， 成牌 最大 的 玩家 贏取 池底 。 亮牌 是 用 自己 的 2 張 底牌 和 5 張 公共牌 結 合在一起 ， 選出 5 張牌 ， 通過 比 大小 決定 勝者 。 不論 手中 的 牌 使用 幾張 （ 甚至 可以 不用 手中 的 底牌 ） ， 湊成 最大 的 成牌 ， 跟 其他 玩家 比 大小 。</t>
+    <t>翻牌前 看牌 時機 肢體 語言 Tells 翻牌前 Pre - flop 不應 一 拿到 手牌 立刻 查看 以免 下意識 表情 或肢 體動作 洩漏 自身 牌力意 圖給 對手 正確 做法 先 觀察 其他 玩家 看牌 時 反應 來 搜集 資訊 直到 輪到 自己 行動 時才 查看 底牌 以確 保 透露 給 對手 資訊降 至 最低</t>
+  </si>
+  <si>
+    <t>坐下：您可以在賭場的空位中自由選擇座位，但是在德州撲克中與座位是一個非常重要的因素，因此在賽事或與牌友玩時通常，座位的順序由規定好的座位表或撲克牌確定。</t>
+  </si>
+  <si>
+    <t>坐下 您 可以 賭場 空位 中 自由 選擇 座位 但是 德州撲克 中 座位 非常 重要 因素 因此 賽事 或 牌友 玩時 通常 座位 順序 由 規定 好 座位表 或 撲克牌 確定</t>
+  </si>
+  <si>
+    <t>荷官莊家位置的確定：座位決定之後，接下來決定荷官莊家位。第一個按鈕莊家的位置是荷官（發牌的人）將牌一張一張地分發給玩家，拿到最強牌的人確定為莊家位。 確定按鈕莊家位的玩家後，就開始正式發牌。</t>
+  </si>
+  <si>
+    <t>荷官 莊家 位置 確定 座位 決定 之 後 接下 來 決定 荷官 莊家 位 第一 個 按鈕 莊家 位置 荷官 發牌 人 將牌 一張 一張 地分 發給 玩家 拿到 最強 牌 人 確定 為 莊家 位 確定 按鈕 莊家 位 玩家 後 開始 正式 發牌</t>
+  </si>
+  <si>
+    <t>發牌：每個玩家發到2張排面朝下的牌，游戲開始。 這2張牌稱為「底牌」或「口袋牌」。 游戲中只有2張牌是發給每位玩家的，除了進行攤牌外，沒有必要將它展示給其他玩家，並且必須 小心不要被人看到它。</t>
+  </si>
+  <si>
+    <t>發牌 每個 玩家 發到 2 張排 面朝 下 牌 游戲 開始 這 2 張牌 稱 為 底牌 或 口袋 牌 游戲 中 只有 2 張牌 發給 每位 玩家 除了 進行 攤牌 外 沒有 必要 將它 展示 給 其他 玩家 並且 必須 小心 不要 人 看到 它</t>
+  </si>
+  <si>
+    <t>翻牌前：先下大小盲注，然後給每個玩家發2張底牌，大盲注後面第一個玩家選擇跟注、加注或者蓋牌放棄，按照順時針方向，其他玩家依次表態，大盲注玩家最後表態 ，如果玩家有加注情況，前面已經跟注的玩家需要再次表態甚至多次表態。</t>
+  </si>
+  <si>
+    <t>翻牌前 先下 大 小盲注 然後給 每個 玩家 發 2 張 底牌 大盲注 後 面 第一 個 玩家 選擇 跟注 加注 或者 蓋牌 放棄 按照 順時針 方向 其他 玩家 依次 表態 大盲注 玩家 最後表態 如果 玩家 有 加注 情況 前面 已經 跟注 玩家 需要 再次 表態 甚至 多次 表態</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 翻牌：同時發三張公牌，由小盲注開始（如果小盲注已蓋牌，由後面最近的玩家開始，以此類推），按照順時針方向依次表態，玩家可以選擇下注、加注、或者蓋牌放棄。</t>
+  </si>
+  <si>
+    <t>翻牌 同時 發三張 公牌 由 小盲注 開始 如果 小盲注 已蓋牌 由後面 最近 玩家 開始 以此 類推 按照 順時針 方向 依次 表態 玩家 可以 選擇 下注 加注 或者 蓋牌 放棄</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 轉牌&amp;河牌：Turn—發第四張牌，由小盲注開始，按照順時針方向依次表態。 River—發第五張牌，由小盲注開始，按照順時針方向依次表態，玩家可以選擇下注、加注、或者蓋牌放棄。經過前面四輪發牌和下注，還剩餘2名以上的玩家時，開始比大小，這時候需要亮牌。</t>
+  </si>
+  <si>
+    <t>轉牌 &amp; 河牌 Turn — 發 第四 張牌 由 小盲注 開始 按照 順時針 方向 依次 表態 River — 發 第五 張牌 由 小盲注 開始 按照 順時針 方向 依次 表態 玩家 可以 選擇 下注 加注 或者 蓋牌 放棄 經過 前面 四輪 發牌 和 下注 還剩 餘 2 名 以上 玩家 時 開始 比 大小 這時候 需要 亮牌</t>
+  </si>
+  <si>
+    <t>亮牌：剩餘2名以上的玩家開始亮牌比大小，成牌最大的玩家贏取池底。亮牌是用自己的2張底牌和5張公共牌結合在一起，選出5張牌，通過比大小決定勝者。不論手中的牌使用幾張（甚至可以不用手中的底牌），湊成最大的成牌，跟其他玩家比大小。</t>
+  </si>
+  <si>
+    <t>亮牌 剩餘 2 名 以上 玩家 開始 亮牌 比 大小 成牌 最大 玩家 贏取 池底 亮牌 用 自己 2 張 底牌 和 5 張 公共牌 結 合在一起 選出 5 張牌 通過 比 大小 決定 勝者 不論 手中 牌 使用 幾張 甚至 可以 不用 手中 底牌 湊成 最大 成牌 跟 其他 玩家 比 大小</t>
   </si>
   <si>
     <t>叫注(也叫說話)：･讓牌 - 在無需跟進的情況下選擇把決定「讓」給下一位 ･押注 - 押上籌碼 ･棄牌 - 放棄繼續牌局的機會 ･加注 - 在其他玩家下注後，把現有的注金抬高 ･跟進 - 跟隨眾人押上同等的注額 ･全押 - 一次過把手上的籌碼全押上</t>
   </si>
   <si>
-    <t>叫注 ( 也 叫 說 話 ) ： ･ 讓 牌 - 在 無 需 跟 進 的 情況 下 選擇 把 決定 「 讓 」 給下 一位 ･ 押注 - 押 上 籌碼 ･ 棄牌 - 放棄 繼續 牌局 的 機會 ･ 加注 - 在 其他 玩家 下注 後 ， 把 現有 的 注金 抬高 ･ 跟 進 - 跟 隨眾 人 押 上 同等 的 注額 ･ 全押 - 一次 過把 手上 的 籌碼 全押 上</t>
-  </si>
-  <si>
-    <t>手牌大小（強度）※順序是從最強牌開始（概率以7張牌計算）：01 皇家同花順 (10･J･Q･K･A的同花色組合，概率：0.0031％)；02 同花順 (同花色加順子，概率：0.0311％)；03 四條 (同一個數位的4張牌，概率：0.168％)；04 葫蘆 (對子加三條，概率：2.60％)；05 同花 (5張牌同一個花色，概率：3.03％)；06 順子 (5張牌連續的數位，概率：4.62％)；07 三條 (同一個數位的3張牌，概率：4.83％)；08 兩對 (2對同一數位的對子牌，概率：23.5％)；09 一對 (同一個數位的對子牌，概率：43.8％)；10 高牌 (拿到強牌的人勝利，概率：17.41％)。</t>
-  </si>
-  <si>
-    <t>手牌 大小 （ 強度 ） ※ 順序 是 從 最 強牌 開始 （ 概率 以 7 張牌 計算 ） ： 01 皇家同花順 ( 10 ･ J ･ Q ･ K ･ A 的 同 花色 組合 ， 概率 ： 0.0031 ％ ) ； 02 同花順 ( 同 花色 加 順子 ， 概率 ： 0.0311 ％ ) ； 03 四條 ( 同一 個 數位 的 4 張牌 ， 概率 ： 0.168 ％ ) ； 04 葫蘆 ( 對子 加 三條 ， 概率 ： 2.60 ％ ) ； 05 同花 ( 5 張牌 同一 個 花色 ， 概率 ： 3.03 ％ ) ； 06 順子 ( 5 張牌 連續 的 數位 ， 概率 ： 4.62 ％ ) ； 07 三條 ( 同一 個 數位 的 3 張牌 ， 概率 ： 4.83 ％ ) ； 08 兩對 ( 2 對 同一 數位 的 對子 牌 ， 概率 ： 23.5 ％ ) ； 09 一對 ( 同一 個 數位 的 對子 牌 ， 概率 ： 43.8 ％ ) ； 10 高牌 ( 拿到 強牌 的 人勝利 ， 概率 ： 17.41 ％ ) 。</t>
+    <t>叫注 ( 叫 說 話 ) ･ 讓 牌 - 無 需 跟 進 情況 下 選擇 把 決定 讓 給下 一位 ･ 押注 - 押 上 籌碼 ･ 棄牌 - 放棄 繼續 牌局 機會 ･ 加注 - 其他 玩家 下注 後 把 現有 注金 抬高 ･ 跟 進 - 跟 隨眾 人 押 上 同等 注額 ･ 全押 - 一次 過把 手上 籌碼 全押 上</t>
+  </si>
+  <si>
+    <t>高牌是指沒有湊成以上任何牌型的情況，只能比單張牌的大小，也是遊戲中相當常見的狀況。</t>
+  </si>
+  <si>
+    <t>高牌 指 沒 有 湊成 以上 任何 牌型 情況 只能 比單 張牌 大小 遊戲 中相 當常見 狀況</t>
+  </si>
+  <si>
+    <t>一對是由兩張同一個數字的牌所組成，這是德州撲克中最常見的牌型，出現機率非常高。</t>
+  </si>
+  <si>
+    <t>一對 由 兩張 同一 個 數字 牌 所 組成 這是 德州撲克 中 最常見 牌型 出現 機率 非常 高</t>
+  </si>
+  <si>
+    <t>兩對是由兩組不同數字的對子所組成，是遊戲中相當常見的牌型。</t>
+  </si>
+  <si>
+    <t>兩對 由 兩組 不同 數字 對子 所 組成 遊戲 中相 當常見 牌型</t>
+  </si>
+  <si>
+    <t>三條是由三張同一個數字的牌所組成，出現的機率稍低。</t>
+  </si>
+  <si>
+    <t>三條 由 三張 同一 個 數字 牌 所 組成 出現 機率 稍低</t>
+  </si>
+  <si>
+    <t>順子是由五張數字連續的牌所組成，在遊戲中屬於機率偏低的牌型。</t>
+  </si>
+  <si>
+    <t>順子 由 五張 數字 連續 牌 所 組成 遊戲 中屬 於 機率 偏低 牌型</t>
+  </si>
+  <si>
+    <t>同花是指五張牌都是同一個花色，雖然強度很高，但出現的機率依然偏低。</t>
+  </si>
+  <si>
+    <t>同花 指五 張牌 同一 個 花色 雖然 強度 很 高 但 出現 機率 依然 偏低</t>
+  </si>
+  <si>
+    <t>葫蘆是由一個對子加上一個三條所組成，是一個非常強勢且出現機率較低的牌型。</t>
+  </si>
+  <si>
+    <t>葫蘆 由 對子 加上 三條 所 組成 非常 強勢 且 出現 機率 較 低 牌型</t>
+  </si>
+  <si>
+    <t>四條是由四張同一個數字的牌所組成，屬於出現機率極低的強大牌型。</t>
+  </si>
+  <si>
+    <t>四條 由 四張 同一 個 數字 牌 所 組成 屬 於 出現 機率 極低 的強 大牌 型</t>
+  </si>
+  <si>
+    <t>同花順的強度僅次於皇家同花順，是同花色加上順子的組合，出現的機率也是極度罕見。</t>
+  </si>
+  <si>
+    <t>同花順 強度 僅次 於 皇家同花順 同 花色 加上 順子 組合 出現 機率 極度 罕見</t>
+  </si>
+  <si>
+    <t>皇家同花順是德州撲克中最強的牌型，由十、J、Q、K、A 的同花色組合而成，出現的機率極度罕見。</t>
+  </si>
+  <si>
+    <t>皇家同花順 德州撲克 中 最強 牌型 由十 J Q K A 同 花色 組合 而成 出現 機率 極度 罕見</t>
   </si>
   <si>
     <t>同一個牌型的強弱對比：如果兩個玩家拿到同樣的牌型，則按以下方法確定一手牌的強度。強度為A&gt; K&gt; Q&gt; J&gt; 10&gt; ... &gt; 2。･首先比較手的「主要部分」的大小（一對的話比對子的強度，兩對的話看較大的對子強度，三條的話看數位的強度）。･如果它們相同，則比較其他牌裡數位最大的一張牌的大小（其餘卡）。･如果它們也相同的話，則平分底池。</t>
   </si>
   <si>
-    <t>同一 個 牌型 的 強弱 對 比 ： 如果 兩個 玩家 拿到 同樣 的 牌型 ， 則 按 以下 方法 確定 一手 牌 的 強度 。 強度 為 A &gt; K &gt; Q &gt; J &gt; 10 &gt; ... &gt; 2 。 ･ 首先 比較 手 的 「 主要 部分 」 的 大小 （ 一對 的 話 比 對子 的 強度 ， 兩對 的 話 看 較 大 的 對子 強度 ， 三條 的 話 看 數位 的 強度 ） 。 ･ 如果 它們 相同 ， 則比較 其他 牌裡 數位 最大 的 一 張牌 的 大小 （ 其餘卡 ） 。 ･ 如果 它們 也 相同 的 話 ， 則 平分 底池 。</t>
+    <t>同一 個 牌型 強弱 對 比 如果 兩個 玩家 拿到 同樣 牌型 則 按 以下 方法 確定 一手 牌 強度 強度 為 A K Q J 10 ... 2 ･ 首先 比較 手 主要 部分 大小 一對 話 比 對子 強度 兩對 話 看 較 大 對子 強度 三條 話 看 數位 強度 ･ 如果 它們 相同 則比較 其他 牌裡 數位 最大 一 張牌 大小 其餘卡 ･ 如果 它們 相同 話 則 平分 底池</t>
   </si>
   <si>
     <t>平局情況的底池分配：在平局的情況下，下注的籌碼被平分，並在排名第一的玩家之間平均分配。 但是，如果當時的籌碼總數有除不盡的情況，則一般常見的規則是把除盡後剩下的籌碼分給最先叫注的人（也就是「位置不佳的人」）。</t>
   </si>
   <si>
-    <t>平局 情況 的 底池 分配 ： 在 平局 的 情況 下 ， 下注 的 籌碼 被 平分 ， 並在 排名 第一 的 玩家 之間 平均分配 。 但是 ， 如果 當時 的 籌碼 總數 有 除 不 盡 的 情況 ， 則 一般 常見 的 規則 是 把 除 盡 後 剩下 的 籌碼 分給 最先 叫注 的 人 （ 也 就是 「 位置 不佳 的 人 」 ） 。</t>
+    <t>平局 情況 底池 分配 平局 情況 下 下注 籌碼 平分 並在 排名 第一 玩家 之間 平均分配 但是 如果 當時 籌碼 總數 有 除 不 盡 情況 則 一般 常見 規則 把 除 盡 後 剩下 籌碼 分給 最先 叫注 人 就是 位置 不佳 人</t>
   </si>
   <si>
     <t>位置的基本觀念：首先叫注的位置是不利的，而後面的位置被認為是有利的。 越是後面的玩家越有利，因為可以在查看其他玩家的動作之後自己做判斷。在不完整的訊息游戲（看不見對手的手牌）中，訊息量越多越有利，因此說可以在獲取其他玩家的訊息後採取行動的靠後位置是一個優勢。</t>
   </si>
   <si>
-    <t>位置 的 基本 觀念 ： 首先 叫注 的 位置 是 不利 的 ， 而後面 的 位置 被 認為 是 有利 的 。 越是 後 面 的 玩家 越 有利 ， 因為 可以 在 查看 其他 玩家 的 動作 之 後 自己 做判斷 。 在 不 完整 的 訊息 游戲 （ 看不見 對 手 的 手牌 ） 中 ， 訊息量 越多越 有利 ， 因此 說 可以 在 獲取 其他 玩家 的 訊息 後 採取 行動 的 靠 後 位置 是 一個 優勢 。</t>
+    <t>位置 基本 觀念 首先 叫注 位置 不利 而後面 位置 認為 有利 越是 後 面 玩家 越 有利 因為 可以 查看 其他 玩家 動作 之 後 自己 做判斷 不 完整 訊息 游戲 看不見 對手 手牌 中 訊息量 越多越 有利 因此 說 可以 獲取 其他 玩家 訊息 後 採取 行動 靠 後 位置 優勢</t>
   </si>
   <si>
     <t>SB（小盲位）：位於 BTN 莊家左側的位置。 在這個位置必須下半盲注。 翻牌前可以在 BTN 莊家位行動後進行棄牌，跟注和加注等操作。 翻牌後，必須最先下決定的位置，所以可以說是一個不利的位置。 另外，即使在翻牌前，也要注意在後面的 BB 大盲位置的行動，因此很難採取激進的叫注動作。</t>
   </si>
   <si>
-    <t>SB （ 小盲位 ） ： 位 於 BTN 莊家 左側 的 位置 。 在 這個 位置 必須 下 半 盲注 。 翻牌前 可以 在 BTN 莊家位 行動 後 進行 棄牌 ， 跟注 和 加注 等 操作 。 翻牌後 ， 必須 最先 下 決定 的 位置 ， 所以 可以 說 是 一個 不利 的 位置 。 另外 ， 即使 在 翻牌前 ， 也 要 注意 在後面 的 BB 大盲位 置 的 行動 ， 因此 很難 採取 激進 的 叫 注動作 。</t>
+    <t>SB 小盲位 位 於 BTN 莊家 左側 位置 這個 位置 必須 下 半 盲注 翻牌前 可以 BTN 莊家 位 行動 後 進行 棄牌 跟注 和 加注 等 操作 翻牌後 必須 最先 下 決定 位置 所以 可以 說 不利 位置 另外 即使 翻牌前 要 注意 在後面 BB 大盲位 置 行動 因此 很難 採取 激進 叫注 動作</t>
   </si>
   <si>
     <t>BB（大盲位）：位於 SB 小盲左側的位置。 在這個位置必須下盲注。 翻牌前可以在 SB 小盲位行動後進行棄牌，跟注和加注等操作。 翻牌後，您需要在 SB 小盲位旁邊採取行動。 在翻牌前，您可以在最後階段採取行動，但是如果在翻牌後，除了 SB 小盲位以外，該位置都被認為是不利的，因此它並不是一個好位置。</t>
   </si>
   <si>
-    <t>BB （ 大盲位 ） ： 位 於 SB 小盲 左側 的 位置 。 在 這個 位置 必須 下 盲注 。 翻牌前 可以 在 SB 小盲位 行動 後 進行 棄牌 ， 跟注 和 加注 等 操作 。 翻牌後 ， 您 需要 在 SB 小盲位 旁邊 採取 行動 。 在 翻牌前 ， 您 可以 在 最後階段 採取 行動 ， 但是 如果 在 翻牌後 ， 除了 SB 小盲位 以外 ， 該 位置 都 被 認為 是 不利 的 ， 因此 它並 不是 一個 好 位置 。</t>
+    <t>BB 大盲位 位 於 SB 小盲 左側 位置 這個 位置 必須 下 盲注 翻牌前 可以 SB 小盲位 行動 後 進行 棄牌 跟注 和 加注 等 操作 翻牌後 您 需要 SB 小盲位 旁邊 採取 行動 翻牌前 您 可以 最後階段 採取 行動 但是 如果 翻牌後 除了 SB 小盲位 以外 該 位置 認為 不利 因此 它並 不是 好 位置</t>
   </si>
   <si>
     <t>UTG（槍口位）：位於 BB 大盲左側的位置。 必須在翻牌前最先採取行動，並且由於翻牌後除了 SB 和 BB 之外，該位置都是不利的，因此從槍口指向的角度來看，這是危險的位置。 由於沒有任何先叫注對手的訊息，因此在游戲中唯一可以利用的訊息就是自己的手牌（底牌）。 因此，該位置如果要採取下注行為的話需要很強的手牌。</t>
   </si>
   <si>
-    <t>UTG （ 槍口位 ） ： 位 於 BB 大盲 左側 的 位置 。 必須 在 翻牌前 最先 採取 行動 ， 並且 由 於 翻牌後 除了 SB 和 BB 之外 ， 該 位置 都 是 不利 的 ， 因此 從 槍口 指向 的 角度 來 看 ， 這是 危險 的 位置 。 由 於 沒 有 任何 先叫 注對 手 的 訊息 ， 因此 在 游戲 中 唯一 可以 利用 的 訊息 就是 自己 的 手牌 （ 底牌 ） 。 因此 ， 該 位置 如果 要 採取 下注 行為 的 話 需要 很強 的 手牌 。</t>
+    <t>UTG 槍口位 位 於 BB 大盲 左側 位置 必須 翻牌前 最先 採取 行動 並且 由 於 翻牌後 除了 SB 和 BB 之外 該 位置 不利 因此 從 槍口 指向 角度 來 看 這是 危險 位置 由 於 沒 有 任何 先 叫注 對手 訊息 因此 游戲 中 唯一 可以 利用 訊息 就是 自己 手牌 底牌 因此 該 位置 如果 要 採取 下注 行為 話 需要 很強 手牌</t>
   </si>
   <si>
     <t>EP（早期位）：指需要及早採取行動的位置。 它取決於坐在桌子上的人數。 在10人桌的情況下，UTG 和其左邊的兩個人通常稱為早期位。 對于6人桌，只有UTG 處于早期位。</t>
   </si>
   <si>
-    <t>EP （ 早期位 ） ： 指 需要 及早 採取 行動 的 位置 。 它 取決 於 坐在 桌子 上 的 人數 。 在 10 人桌 的 情況 下 ， UTG 和 其 左邊 的 兩個 人 通常 稱為 早期位 。 對于 6 人桌 ， 只有 UTG 處于 早期位 。</t>
+    <t>EP 早期位 指 需要 及早 採取 行動 位置 它 取決 於 坐在 桌子 上 人數 10 人桌 情況 下 UTG 和 其 左邊 兩個 人 通常 稱為 早期位 對于 6 人桌 只有 UTG 處于 早期位</t>
   </si>
   <si>
     <t>MP（中期位）：指每個回合在中間採取行動的位置。 在10人桌的情況下，通常將在翻牌前從第4到第6的這3人位置叫做中期位。 對于6人桌，UTG 的左側2個人屬於中間位。</t>
   </si>
   <si>
-    <t>MP （ 中期位 ） ： 指 每個 回合 在 中間 採取 行動 的 位置 。 在 10 人桌 的 情況 下 ， 通常 將在 翻牌前 從 第 4 到 第 6 的 這 3 人 位置 叫做 中期位 。 對于 6 人桌 ， UTG 的 左側 2 個 人屬 於 中間 位 。</t>
+    <t>MP 中期位 指 每個 回合 中間 採取 行動 位置 10 人桌 情況 下 通常 將在 翻牌前 從 第 4 到 第 6 這 3 人 位置 叫做 中期位 對于 6 人桌 UTG 左側 2 個 人屬 於 中間 位</t>
   </si>
   <si>
     <t>CO（關煞位）：指的是 BTN 莊家位的前一個位置。</t>
   </si>
   <si>
-    <t>CO （ 關煞位 ） ： 指 的 是 BTN 莊家位 的 前 一個 位置 。</t>
+    <t>CO 關煞位 指 BTN 莊家 位 前 位置</t>
   </si>
   <si>
     <t>BTN（莊家按鈕位）：指的是每回合可以最後採取行動的位置，被認為是最佳位置。 在許多情況下，這個位置的玩家前面都會放置一枚寫著 DEALER 字樣的圓形按鈕。 不管是線上還是線下，這個位置都會做標記。</t>
   </si>
   <si>
-    <t>BTN （ 莊家按鈕位 ） ： 指 的 是 每 回合 可以 最後採取 行動 的 位置 ， 被 認為 是 最佳 位置 。 在許 多情 況下 ， 這個 位置 的 玩家 前面 都 會 放置 一枚 寫著 DEALER 字樣 的 圓形 按鈕 。 不管 是 線 上 還是 線 下 ， 這個 位置 都 會 做 標記 。</t>
+    <t>BTN 莊家 按鈕位 指 每 回合 可以 最後採取 行動 位置 認為 最佳 位置 在許 多情 況下 這個 位置 玩家 前面 會 放置 一枚 寫著 DEALER 字樣 圓形 按鈕 不管 線 上 還是 線 下 這個 位置 會 做 標記</t>
   </si>
   <si>
     <t>All-in（全下）：全下意味著把自己手上的籌碼全部下注在某牌桌上。 一旦全下，就不能下注或跟注，也不能棄牌，自動過渡到亮牌階段。 其餘玩家將繼續照常進行。</t>
   </si>
   <si>
-    <t>All - in （ 全 下 ） ： 全 下 意味著 把 自己 手上 的 籌碼 全部 下注 在 某牌 桌上 。 一旦 全 下 ， 就 不能 下注 或 跟注 ， 也 不能 棄牌 ， 自動 過渡 到 亮牌 階段 。 其餘 玩家 將繼續 照常 進行 。</t>
+    <t>All - in 全 下 全 下 意味著 把 自己 手上 籌碼 全部 下注 某牌 桌上 一旦 全 下 不能 下注 或 跟注 不能 棄牌 自動 過渡 到 亮牌 階段 其餘 玩家 將繼續 照常 進行</t>
   </si>
   <si>
     <t>Bet（下注）：下注意味著加大籌碼。 如果在前面的玩家尚未進行下注，則下注是該玩家可以採取的行動之一。 一個玩家只有在沒有其他人先進行下注的情況下才能下注。 如果已經有玩家下注，則玩家必須進行跟注動作或者有需要的話可以加注。</t>
   </si>
   <si>
-    <t>Bet （ 下注 ） ： 下注 意味著 加大 籌碼 。 如果 在 前面 的 玩家 尚未 進行 下注 ， 則 下注 是 該 玩家 可以 採取 的 行動 之一 。 一個 玩家 只有 在 沒 有 其他人 先 進行 下注 的 情況 下 才能 下注 。 如果 已經 有 玩家 下注 ， 則 玩家 必須 進行 跟注 動作 或者 有 需要 的 話 可以 加注 。</t>
+    <t>Bet 下注 下注 意味著 加大 籌碼 如果 前面 玩家 尚未 進行 下注 則 下注 該 玩家 可以 採取 行動 之一 玩家 只有 沒 有 其他人 先 進行 下注 情況 下 才能 下注 如果 已經 有 玩家 下注 則 玩家 必須 進行 跟注 動作 或者 有 需要 話 可以 加注</t>
   </si>
   <si>
     <t>Buy-in（買入）：參與游戲所需的金額。 對于諸如賭場的現金游戲，最低買入費由表格設定。 對于賽事，分為獎池和支付給主辦方的參與費。</t>
   </si>
   <si>
-    <t>Buy - in （ 買入 ） ： 參與 游戲 所 需 的 金額 。 對于 諸如 賭場 的 現金游戲 ， 最低 買入費 由 表格 設定 。 對于 賽事 ， 分為 獎池 和 支付 給主 辦方 的 參與費 。</t>
+    <t>Buy - in 買入 參與 游戲 所 需 金額 對于 諸如 賭場 現金游戲 最低 買入費 由 表格 設定 對于 賽事 分為 獎池 和 支付 給主 辦方 參與費</t>
   </si>
   <si>
     <t>Bank roll（總資金）：玩家的資金就是他用來玩撲克的全部金錢。 即准備的資金總額。 在線撲克中，指的是玩家帳戶裡所擁有的資金。</t>
   </si>
   <si>
-    <t>Bank roll （ 總資金 ） ： 玩家 的 資金 就是 他用 來 玩 撲克 的 全部 金錢 。 即 准備 的 資金 總額 。 在 線 撲克中 ， 指 的 是 玩家 帳戶裡 所 擁有 的 資金 。</t>
+    <t>Bank roll 總資金 玩家 資金 就是 他用 來 玩 撲克 全部 金錢 即 准備 資金 總額 線 撲克中 指 玩家 帳戶裡 所 擁有 資金</t>
   </si>
   <si>
     <t>Blind（盲注）：盲注是撲克游戲中強制下注的一種形式。 是必須在發牌前支付的賭注。 每回合由兩名玩家支付，但不是固定玩家支付，每一回合輪流變化。 通常，兩個賭注具有相同的大小，或者一個賭注大於另一個賭注。 後者稱為「大盲注和小盲注」。</t>
   </si>
   <si>
-    <t>Blind （ 盲注 ） ： 盲注 是 撲克游 戲中 強制 下注 的 一種 形式 。 是 必須 在 發牌 前 支付 的 賭注 。 每 回合 由 兩名 玩家 支付 ， 但 不是 固定 玩家 支付 ， 每一 回合 輪流 變化 。 通常 ， 兩個 賭注 具有 相同 的 大小 ， 或者 一個 賭 注大 於 另 一個 賭注 。 後 者 稱 為 「 大盲注 和 小盲注 」 。</t>
+    <t>Blind 盲注 盲注 撲克游 戲中 強制 下注 一種 形式 必須 發牌 前 支付 賭注 每 回合 由 兩名 玩家 支付 但 不是 固定 玩家 支付 每一 回合 輪流 變化 通常 兩個 賭注 具有 相同 大小 或者 賭 注大 於 另 賭注 後 者 稱 為 大盲注 和 小盲注</t>
   </si>
   <si>
     <t>Board（公共牌）：在使用公共牌的游戲中，Board一般指的是所有公共牌。 例如，在德州撲克中，由翻牌，轉牌和河牌組成。</t>
   </si>
   <si>
-    <t>Board （ 公共牌 ） ： 在 使用 公共牌 的 游戲 中 ， Board 一般 指 的 是 所有 公共牌 。 例如 ， 在 德州 撲克中 ， 由 翻牌 ， 轉牌 和 河牌 組成 。</t>
+    <t>Board 公共牌 使用 公共牌 游戲 中 Board 一般 指 所有 公共牌 例如 德州撲克 中 由 翻牌 轉牌 和 河牌 組成</t>
   </si>
   <si>
     <t>Button（按鈕）：按鈕，或者莊家按鈕，是一個提示，顯示當前誰是莊家。 莊家坐在的位置也稱為按鈕位。 或者說「莊家即按鈕」。</t>
   </si>
   <si>
-    <t>Button （ 按鈕 ） ： 按鈕 ， 或者 莊家 按鈕 ， 是 一個 提示 ， 顯示 當前 誰 是 莊家 。 莊家 坐在 的 位置 也 稱 為 按 鈕位 。 或者 說 「 莊家 即 按鈕 」 。</t>
+    <t>Button 按鈕 按鈕 或者 莊家 按鈕 提示 顯示 當前 誰 莊家 莊家 坐在 位置 稱 為 按鈕位 或者 說 莊家 即 按鈕</t>
   </si>
   <si>
     <t>Bad beat（小概率失敗）：Bad beat 是指拿到好牌非常有優勢的玩家在不太可能的情況下輸掉。 正常失敗和小概率失敗之間的界限因玩家而異。 通常，如果您以5-10％的勝率輸掉一手牌，或者如果您的對手由於您已經抽出兩張完美的牌而輸了， 則稱為小概率失敗。</t>
   </si>
   <si>
-    <t>Bad beat （ 小 概率 失敗 ） ： Bad beat 是 指 拿到 好牌 非常 有 優勢 的 玩家 在 不太可能 的 情況 下輸 掉 。 正常 失敗 和 小 概率 失敗 之間 的 界限 因 玩家 而異 。 通常 ， 如果 您 以 5 - 10 ％ 的 勝率 輸掉 一手 牌 ， 或者 如果 您 的 對 手 由 於 您 已經 抽出 兩張 完美 的 牌 而 輸 了 ， 則稱 為 小 概率 失敗 。</t>
+    <t>Bad beat 小 概率 失敗 Bad beat 指 拿到 好牌 非常 有 優勢 玩家 不太可能 情況 下輸 掉 正常 失敗 和 小 概率 失敗 之間 界限 因 玩家 而異 通常 如果 您 以 5 - 10 ％ 勝率 輸掉 一手 牌 或者 如果 您 對手 由 於 您 已經 抽出 兩張 完美 牌 輸 則稱 為 小 概率 失敗</t>
   </si>
   <si>
     <t>Blank（空白）：空白或磚塊指的是不會形成任何牌型的公共牌。 「轉牌是空白」表示轉牌沒有改變游戲狀況。 例如，在3高牌（花色不同的牌）翻牌後，轉牌出現2，表示為空白。</t>
   </si>
   <si>
-    <t>Blank （ 空白 ） ： 空白 或 磚塊 指 的 是 不會 形成 任何 牌型 的 公共牌 。 「 轉牌 是 空白 」 表示 轉牌 沒有 改變 游戲 狀況 。 例如 ， 在 3 高牌 （ 花色 不同 的 牌 ） 翻牌後 ， 轉牌 出現 2 ， 表示 為 空白 。</t>
+    <t>Blank 空白 空白 或 磚塊 指 不會 形成 任何 牌型 公共牌 轉牌 空白 表示 轉牌 沒有 改變 游戲 狀況 例如 3 高牌 花色 不同 牌 翻牌後 轉牌 出現 2 表示 為 空白</t>
   </si>
   <si>
     <t>Bust out（出局）：淘汰或出局意味著失去自己的全部籌碼或輸掉賽事。 淘汰某人意味著把某人從桌子排除或從賽事中擊敗。</t>
   </si>
   <si>
-    <t>Bust out （ 出局 ） ： 淘汰 或 出局 意味著 失去 自己 的 全部 籌碼 或 輸掉 賽事 。 淘汰 某人 意味著 把 某人 從 桌子 排除 或 從 賽事 中擊敗 。</t>
+    <t>Bust out 出局 淘汰 或 出局 意味著 失去 自己 全部 籌碼 或 輸掉 賽事 淘汰 某人 意味著 把 某人 從 桌子 排除 或 從 賽事 中擊敗</t>
   </si>
   <si>
     <t>Call（跟注）：跟上一位玩家投入相同籌碼。 跟注是相對于對手的加注可以采取的行動之一。</t>
   </si>
   <si>
-    <t>Call （ 跟注 ） ： 跟上 一位 玩家 投入 相同 籌碼 。 跟注 是 相 對 于 對 手 的 加注 可以 采取 的 行動 之一 。</t>
+    <t>Call 跟注 跟上 一位 玩家 投入 相同 籌碼 跟注 相 對 于 對手 加注 可以 采取 行動 之一</t>
   </si>
   <si>
     <t>Check（看牌）：前面無人下注，自己也不下注，也叫「看牌」或「過牌」。 看牌是玩家可以採取的行動之一。 不進行加注動作的玩家可以選擇看牌動作。</t>
   </si>
   <si>
-    <t>Check （ 看牌 ） ： 前面 無人 下注 ， 自己 也 不 下注 ， 也 叫 「 看牌 」 或 「 過牌 」 。 看牌 是 玩家 可以 採取 的 行動 之一 。 不 進行 加注 動作 的 玩家 可以 選擇 看牌 動作 。</t>
+    <t>Check 看牌 前面 無人 下注 自己 不 下注 叫 看牌 或 過牌 看牌 玩家 可以 採取 行動 之一 不 進行 加注 動作 玩家 可以 選擇 看牌 動作</t>
   </si>
   <si>
     <t>Cut off（關煞位）：在有規定莊家按鈕位的游戲中，關煞位在按鈕位的右邊。</t>
   </si>
   <si>
-    <t>Cut off （ 關煞位 ） ： 在 有 規定 莊家按鈕位 的 游戲 中 ， 關煞位 在 按 鈕位 的 右邊 。</t>
+    <t>Cut off 關煞位 有 規定 莊家 按鈕位 游戲 中 關煞位 按鈕位 右邊</t>
   </si>
   <si>
     <t>Cap（上限）：上限是您在一局中可以加的最後一次加注，或者是一局中可以下注的最大金額。 通常在一局中限制第三，第四或第五次加注。 最後加注的成為上限。</t>
   </si>
   <si>
-    <t>Cap （ 上限 ） ： 上限 是 您 在 一局 中 可以 加 的 最 後 一次 加注 ， 或者 是 一局 中 可以 下注 的 最大 金額 。 通常 在 一局 中 限制 第三 ， 第四 或 第五次 加注 。 最 後 加注 的 成為 上限 。</t>
+    <t>Cap 上限 上限 您 一局 中 可以 加 最 後 一次 加注 或者 一局 中 可以 下注 最大 金額 通常 一局 中 限制 第三 第四 或 第五次 加注 最 後 加注 成為 上限</t>
   </si>
   <si>
     <t>Community cards（公共牌）：由荷官發出的桌上的玩家共有的牌。</t>
   </si>
   <si>
-    <t>Community cards （ 公共牌 ） ： 由 荷官 發出 的 桌上 的 玩家 共有 的 牌 。</t>
+    <t>Community cards 公共牌 由 荷官 發出 桌上 玩家 共有 牌</t>
   </si>
   <si>
     <t>Check-Raise（看牌加注）：看牌加注是一種打法，指的是「玩家先看牌然後在下一個對手下注時加注」。</t>
   </si>
   <si>
-    <t>Check - Raise （ 看牌 加注 ） ： 看牌 加注 是 一種 打法 ， 指 的 是 「 玩家 先看 牌然 後 在 下 一個 對 手下 注時 加注 」 。</t>
+    <t>Check - Raise 看牌 加注 看牌 加注 一種 打法 指 玩家 先看 牌然 後 下 對手 下注 時 加注</t>
   </si>
   <si>
     <t>Draw（聽牌）：聽牌是指未完成的組合，還需要1張或1張以上的牌才能組成特定的牌型。</t>
   </si>
   <si>
-    <t>Draw （ 聽牌 ） ： 聽牌 是 指未 完成 的 組合 ， 還 需要 1 張 或 1 張 以上 的 牌 才能 組 成特定 的 牌型 。</t>
+    <t>Draw 聽牌 聽牌 指未 完成 組合 還 需要 1 張 或 1 張 以上 牌 才能 組 成特定 牌型</t>
   </si>
   <si>
     <t>Dealer（荷官）：荷官指的是發牌的人。</t>
   </si>
   <si>
-    <t>Dealer （ 荷官 ） ： 荷官 指 的 是 發牌 的 人 。</t>
+    <t>Dealer 荷官 荷官 指 發牌 人</t>
   </si>
   <si>
     <t>Drawing dead（聽死牌）：玩家就算發牌之後也沒有勝算的話，就稱作「他在聽死牌」。</t>
   </si>
   <si>
-    <t>Drawing dead （ 聽死牌 ） ： 玩家 就算 發牌 之 後 也 沒 有 勝算 的 話 ， 就 稱作 「 他 在 聽 死牌 」 。</t>
+    <t>Drawing dead 聽死牌 玩家 就算 發牌 之 後 沒 有 勝算 話 稱作 他 聽 死牌</t>
   </si>
   <si>
     <t>Edge（優勢）：「擁有優勢」意味著比其他玩家更具優勢。 例如，好的手牌比弱的手牌有優勢。 技術水準高或桌上位置好的玩家也有優勢。</t>
   </si>
   <si>
-    <t>Edge （ 優勢 ） ： 「 擁有 優勢 」 意味著 比 其他 玩家 更具 優勢 。 例如 ， 好 的 手牌 比弱 的 手牌 有 優勢 。 技術 水準 高 或 桌上 位置 好 的 玩家 也 有 優勢 。</t>
+    <t>Edge 優勢 擁有 優勢 意味著 比 其他 玩家 更具 優勢 例如 好 手牌 比弱 手牌 有 優勢 技術 水準 高 或 桌上 位置 好 玩家 有 優勢</t>
   </si>
   <si>
     <t>Early（早期）：在玩家相對于荷官的相對位置決定游戲順序的游戲中，早期位是必須首先採取行動的玩家。 例如，在德州撲克的全圈桌中，盲注之後的前三個位置是早期位。 它們也稱為UTG（槍口位），UTG + 1，UTG + 2。</t>
   </si>
   <si>
-    <t>Early （ 早期 ） ： 在 玩家 相對于 荷官 的 相 對 位置 決定 游戲 順序 的 游戲 中 ， 早期位 是 必須 首先 採取 行動 的 玩家 。 例如 ， 在 德州 撲克 的 全圈 桌中 ， 盲注 之 後 的 前三個 位置 是 早期位 。 它們 也 稱 為 UTG （ 槍口位 ） ， UTG + 1 ， UTG + 2 。</t>
+    <t>Early 早期 玩家 相對于 荷官 相 對 位置 決定 游戲 順序 游戲 中 早期位 必須 首先 採取 行動 玩家 例如 德州撲克 全圈 桌中 盲注 之 後 前三個 位置 早期位 它們 稱 為 UTG 槍口位 UTG + 1 UTG + 2</t>
   </si>
   <si>
     <t>Flop（翻牌）：在德州撲克和奧馬哈等使用公共牌的撲克游戲中，翻牌指的是前三張公共牌。</t>
   </si>
   <si>
-    <t>Flop （ 翻牌 ） ： 在 德州 撲克 和 奧馬哈 等 使用 公共牌 的 撲克游戲 中 ， 翻牌 指 的 是 前三張 公共牌 。</t>
+    <t>Flop 翻牌 德州撲克 和 奧馬哈 等 使用 公共牌 撲克游戲 中 翻牌 指 前三張 公共牌</t>
   </si>
   <si>
     <t>Fold（棄牌）：棄牌的玩家放置其牌，並在本回合中退出該賽事。 該玩家已經下注的籌碼留在底池中，可以從下一輪重新加入游戲。</t>
   </si>
   <si>
-    <t>Fold （ 棄牌 ） ： 棄牌 的 玩家 放置 其牌 ， 並在 本 回合 中 退出 該賽 事 。 該 玩家 已經 下注 的 籌碼 留在 底池 中 ， 可以 從下 一輪 重新加入 游戲 。</t>
-  </si>
-  <si>
-    <t>Fish（菜鳥）：Fish 指的是菜鳥。 或者玩得差的玩家來說，他是玩的好的玩家的菜鴨。 Fish 指沒有策略，甚至還會採取負期望的行動的玩家。 所以「他是一條 Fish」。 菜鳥用很爛的牌入池，還頻繁下注。 還用 Fish 代替了以前使用的一些侮辱性詞語，例如，遲鈍（白癡），idiot（蠢蛋）和傻瓜。</t>
-  </si>
-  <si>
-    <t>Fish （ 菜 鳥 ） ： Fish 指 的 是 菜 鳥 。 或者 玩得 差 的 玩家 來 說 ， 他 是 玩 的 好 的 玩家 的 菜 鴨 。 Fish 指沒有 策略 ， 甚至 還會 採取負 期望 的 行動 的 玩家 。 所以 「 他 是 一條 Fish 」 。 菜 鳥用 很爛 的 牌入 池 ， 還頻 繁 下注 。 還用 Fish 代替 了 以前 使用 的 一些 侮辱性 詞語 ， 例如 ， 遲鈍 （ 白 癡 ） ， idiot （ 蠢蛋 ） 和 傻瓜 。</t>
+    <t>Fold 棄牌 棄牌 玩家 放置 其牌 並在 本 回合 中 退出 該賽 事 該 玩家 已經 下注 籌碼 留在 底池 中 可以 從下 一輪 重新加入 游戲</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fish（菜鳥）：Fish 指的是菜鳥。  Fish 指沒有策略，甚至還會採取負期望的行動的玩家。  菜鳥用很爛的牌入池，還頻繁下注。 </t>
+  </si>
+  <si>
+    <t>Fish 菜 鳥 Fish 指 菜 鳥 Fish 指沒有 策略 甚至 還會 採取負 期望 行動 玩家 菜 鳥用 很爛 牌入 池 還頻 繁 下注</t>
   </si>
   <si>
     <t>Freeroll（免費賽）：Freeroll 免費賽是指具有贊助獎品或有贊助商的不需要買入的賽事。 Freeroll 免費賽指2名玩家擁有同等實力的手牌聽牌，其中1名玩家組成牌型的話將拿走全部獎池的情況。 （第二個玩家聽牌沒有擊中）。</t>
   </si>
   <si>
-    <t>Freeroll （ 免費賽 ） ： Freeroll 免費賽 是 指 具有 贊助 獎品 或 有 贊助商 的 不 需要 買入 的 賽事 。 Freeroll 免費賽 指 2 名 玩家 擁有 同等 實力 的 手牌 聽牌 ， 其中 1 名 玩家 組成 牌型 的 話將 拿走 全部 獎池 的 情況 。 （ 第二 個 玩家 聽牌 沒有擊 中 ） 。</t>
+    <t>Freeroll 免費賽 Freeroll 免費賽 指 具有 贊助 獎品 或 有 贊助商 不 需要 買入 賽事 Freeroll 免費賽 指 2 名 玩家 擁有 同等 實力 手牌 聽牌 其中 1 名 玩家 組成 牌型 話將 拿走 全部 獎池 情況 第二 個 玩家 聽牌 沒有擊 中</t>
   </si>
   <si>
     <t>Grind（安全打法）：安全打法指的是不願冒太大風險，根據一定的下注限額持續取得利益的一種打法。 「Grinder」和「Rounder」這兩個術語是指，為了賺取自己的收入一部分或者全額（即使可以採取高風險高回報的打法的 時候）進行的安全打法。</t>
   </si>
   <si>
-    <t>Grind （ 安全 打法 ） ： 安全 打法 指 的 是 不願 冒 太大風險 ， 根據 一定 的 下注 限額 持續 取得 利益 的 一種 打法 。 「 Grinder 」 和 「 Rounder 」 這兩個術語 是 指 ， 為 了 賺取 自己 的 收入 一部分 或者 全額 （ 即使 可以 採取 高風險 高 回報 的 打法 的 時候 ） 進行 的 安全 打法 。</t>
+    <t>Grind 安全 打法 安全 打法 指 不願 冒 太大風險 一定 下注 限額 持續 取得 利益 一種 打法 Grinder 和 Rounder 這兩個術語 指 為 賺取 自己 收入 一部分 或者 全額 即使 可以 採取 高風險 高 回報 打法 時候 進行 安全 打法</t>
   </si>
   <si>
     <t>Heads-up（單挑）：只有2個玩家玩的撲克游戲稱為「單挑」。 單挑游戲是不規則的撲克形式，將是最激烈的戰鬥。 因為玩家無力等待強牌，所以除了相信自己的打法運氣和發現對手的弱點外，他們別無選擇。</t>
   </si>
   <si>
-    <t>Heads - up （ 單挑 ） ： 只有 2 個 玩家 玩 的 撲克游 戲稱 為 「 單挑 」 。 單挑游戲 是 不 規則 的 撲克 形式 ， 將是 最 激烈 的 戰鬥 。 因為 玩家 無力 等待 強牌 ， 所以 除了 相信 自己 的 打法 運氣 和 發現 對 手 的 弱點 外 ， 他們 別無選擇 。</t>
+    <t>Heads - up 單挑 只有 2 個 玩家 玩 撲克游 戲稱 為 單挑 單挑游戲 不 規則 撲克 形式 將是 最 激烈 戰鬥 因為 玩家 無力 等待 強牌 所以 除了 相信 自己 打法 運氣 和 發現 對手 弱點 外 他們 別無選擇</t>
   </si>
   <si>
     <t>Hole cards（手牌）：手牌指的是只有自己可以看見的卡牌。 比如，德州撲克中指的是荷官發給自己的2張牌。</t>
   </si>
   <si>
-    <t>Hole cards （ 手牌 ） ： 手牌 指 的 是 只有 自己 可以 看見 的 卡牌 。 比如 ， 德州 撲克 中指 的 是 荷官 發給 自己 的 2 張牌 。</t>
+    <t>Hole cards 手牌 手牌 指 只有 自己 可以 看見 卡牌 比如 德州撲克 中指 荷官 發給 自己 2 張牌</t>
   </si>
   <si>
     <t>Kicker（踢牌）：踢牌者是指組成撲克牌型的5張牌以外的1張牌，但是如果有2手牌具有相等值的牌型組合，則 其作用是確定這2手牌的強弱高下。 因此，少於5張牌型組合的牌才能使用踢牌。 也就是說，僅適用于四條，三條，一對（兩對）和高牌。 如果兩個玩家的手牌相等，則踢牌確定哪個玩家是獲勝者。 最高的踢牌是最強的踢牌。 狹義是有且只有一張踢牌。 也就是說，當兩個玩家的手牌相似時，只有那張踢牌才能決定哪個更強。 如果玩家擁有完全相同的一手牌，則最高的非組合牌將成為踢牌，他們將平分底池。</t>
   </si>
   <si>
-    <t>Kicker （ 踢牌 ） ： 踢 牌者 是 指 組成 撲克牌 型 的 5 張牌 以外 的 1 張牌 ， 但是 如果 有 2 手牌 具有 相等值 的 牌型 組合 ， 則 其 作用 是 確定 這 2 手牌 的 強弱 高下 。 因此 ， 少 於 5 張牌 型 組合 的 牌 才能 使用 踢牌 。 也 就是 說 ， 僅適 用于 四條 ， 三條 ， 一對 （ 兩對 ） 和 高牌 。 如果 兩個 玩家 的 手牌 相等 ， 則 踢 牌 確定 哪個 玩家 是 獲勝者 。 最高 的 踢 牌 是 最強 的 踢 牌 。 狹義是 有且 只有 一張 踢 牌 。 也 就是 說 ， 當兩個 玩家 的 手牌 相似 時 ， 只有 那張 踢 牌 才能 決定 哪個 更強 。 如果 玩家 擁有 完全相同 的 一手 牌 ， 則 最高 的 非 組合牌 將成 為 踢 牌 ， 他們將 平分 底池 。</t>
+    <t>Kicker 踢牌 踢牌 者 指 組成 撲克 牌型 5 張牌 以外 1 張牌 但是 如果 有 2 手牌 具有 相等值 牌型 組合 則 其 作用 確定 這 2 手牌 強弱 高下 因此 少 於 5 張 牌型 組合 牌 才能 使用 踢牌 就是 說 僅適 用于 四條 三條 一對 兩對 和 高牌 如果 兩個 玩家 手牌 相等 則 踢牌 確定 哪個 玩家 獲勝者 最高 踢牌 最強 踢牌 狹義是 有且 只有 一張 踢牌 就是 說 當兩個 玩家 手牌 相似 時 只有 那張 踢牌 才能 決定 哪個 更強 如果 玩家 擁有 完全相同 一手 牌 則 最高 非 組合牌 將成 為 踢牌 他們將 平分 底池</t>
   </si>
   <si>
     <t>Limit（限額）：限額是下注金額或下注額的另一個術語。 例如，NL400是最大買入額為$400的限額以及無限額（NL）的下注結構。</t>
   </si>
   <si>
-    <t>Limit （ 限額 ） ： 限額 是 下注 金額 或 下注 額 的 另 一個術語 。 例如 ， NL400 是 最大 買入 額為 $ 400 的 限額 以及 無限額 （ NL ） 的 下注 結構 。</t>
+    <t>Limit 限額 限額 下注 金額 或 下注 額 另 一個術語 例如 NL400 最大 買入 額為 $ 400 限額 無限額 NL 下注 結構</t>
   </si>
   <si>
     <t>Late（後期位）：在游戲中玩家行為順序由莊家的位置決定的情況下，後期位置是指最後兩個位置（關煞位和按鈕位）。 處在這些位置的玩家比其他位置的玩家要有優勢。 因為他們可以在看了其他前面玩家的行動之後自己再採取相應的行動。</t>
   </si>
   <si>
-    <t>Late （ 後期位 ） ： 在 游戲 中 玩家 行為 順序 由 莊家 的 位置 決定 的 情況 下 ， 後期位 置 是 指 最後兩個 位置 （ 關煞位 和 按 鈕位 ） 。 處 在 這些 位置 的 玩家 比 其他 位置 的 玩家 要 有 優勢 。 因為 他們 可以 在 看 了 其他 前面 玩家 的 行動 之 後 自己 再 採取 相應 的 行動 。</t>
+    <t>Late 後期位 游戲 中 玩家 行為 順序 由 莊家 位置 決定 情況 下 後期位 置 指 最後兩個 位置 關煞位 和 按鈕位 處 這些 位置 玩家 比 其他 位置 玩家 要 有 優勢 因為 他們 可以 看 其他 前面 玩家 行動 之 後 自己 再 採取 相應 行動</t>
   </si>
   <si>
     <t>Limp（跟大盲）：在帶有盲注（強制下注）的游戲中，如果玩家將跟大盲注作為第一個動作，則表示玩家想要緩慢進行。 想要跟大盲注，不會選擇加注。</t>
   </si>
   <si>
-    <t>Limp （ 跟大盲 ） ： 在 帶 有 盲注 （ 強制 下注 ） 的 游戲 中 ， 如果 玩家 將跟 大盲注 作為 第一 個動作 ， 則 表示 玩家 想要 緩慢 進行 。 想要 跟 大盲注 ， 不會 選擇 加注 。</t>
+    <t>Limp 跟大盲 帶 有 盲注 強制 下注 游戲 中 如果 玩家 將跟 大盲注 作為 第一 個動作 則 表示 玩家 想要 緩慢 進行 想要 跟 大盲注 不會 選擇 加注</t>
   </si>
   <si>
     <t>Middle（中期位）：在游戲中玩家行為順序由莊家的位置決定的情況下，中期位是指從發牌者的角度來看位於桌子中央的人。 例如，在一個德州撲克全額的10人桌中，第6、7和8位稱為中期位，即MP，MP2，MP3。 處于這些位置的玩家對之後的玩家處于劣勢，將與之後的玩家進行戰鬥，但在面對之前的玩家 時處于有利的位置（ 因為可以看到之前的行動）。</t>
   </si>
   <si>
-    <t>Middle （ 中期位 ） ： 在 游戲 中 玩家 行為 順序 由 莊家 的 位置 決定 的 情況 下 ， 中期位 是 指 從 發牌 者 的 角度 來 看位 於 桌子 中央 的 人 。 例如 ， 在 一個 德州 撲克 全額 的 10 人桌 中 ， 第 6 、 7 和 8 位稱 為 中期位 ， 即 MP ， MP2 ， MP3 。 處于 這些 位置 的 玩家 對 之 後 的 玩家 處于 劣勢 ， 將與 之 後 的 玩家 進行 戰鬥 ， 但 在 面 對 之前 的 玩家 時處 于 有利 的 位置 （ 因為 可以 看到 之前 的 行動 ） 。</t>
+    <t>Middle 中期位 游戲 中 玩家 行為 順序 由 莊家 位置 決定 情況 下 中期位 指 從 發牌 者 角度 來 看位 於 桌子 中央 人 例如 德州撲克 全額 10 人桌 中 第 6 7 和 8 位稱 為 中期位 即 MP MP2 MP3 處于 這些 位置 玩家 對 之 後 玩家 處于 劣勢 將與 之 後 玩家 進行 戰鬥 但 面 對 之前 玩家 時處 于 有利 位置 因為 可以 看到 之前 行動</t>
   </si>
   <si>
     <t>Muck（棄牌區）：棄牌區指的是撲克桌上所有已使用過的紙牌放置的區域。 它包含所有洗牌卡（在某些時候將最上層的牌去掉）或玩家棄掉的牌。 棄牌區意味著不去看那些牌就放置在那。</t>
   </si>
   <si>
-    <t>Muck （ 棄牌 區 ） ： 棄牌 區指 的 是 撲克 桌上 所有 已 使用 過的 紙牌 放置 的 區域 。 它 包含 所有 洗牌 卡 （ 在 某些 時 候將 最 上層 的 牌 去掉 ） 或 玩家 棄掉 的 牌 。 棄牌 區 意味著 不去 看 那些 牌 就 放置 在 那 。</t>
+    <t>Muck 棄牌 區 棄牌 區指 撲克 桌上 所有 已 使用 過的 紙牌 放置 區域 它 包含 所有 洗牌 卡 某些 時 候將 最 上層 牌 去掉 或 玩家 棄掉 牌 棄牌 區 意味著 不去 看 那些 牌 放置 那</t>
   </si>
   <si>
     <t>Nuts（必勝牌）：必勝牌指的是在特定情況下的最強牌。 如果在已發的牌之中，某玩家擁有最好的一手牌，那麼他就是拿到必勝牌。 在某些牌型類別中也使用此術語。 例如必勝同花牌或者必勝順子牌指的是已知牌面中最強的同花或者順子。</t>
   </si>
   <si>
-    <t>Nuts （ 必勝牌 ） ： 必勝牌 指 的 是 在 特定 情況 下 的 最 強牌 。 如果 在 已發 的 牌 之中 ， 某 玩家 擁有 最好 的 一手 牌 ， 那麼 他 就是 拿到 必勝牌 。 在 某些 牌型 類別 中 也 使用 此術語 。 例如 必勝 同花 牌 或者 必勝 順子 牌指 的 是 已知 牌面 中 最強 的 同花 或者 順子 。</t>
-  </si>
-  <si>
-    <t>Odds（賠率）：例如，如果有一定數量的聽牌（可以使自己的牌型增強）[剩餘1張（可能多於1張）來牌的話就可以形成牌型] ，發這種牌有一定的概率。 這種概率通常稱為賠率。 在賠率不佳的情況下，聽牌不太可能形成牌型。</t>
-  </si>
-  <si>
-    <t>Odds （ 賠率 ） ： 例如 ， 如果 有 一定 數量 的 聽牌 （ 可以 使 自己 的 牌型 增強 ） [ 剩餘 1 張 （ 可能 多 於 1 張 ） 來牌 的 話 就 可以 形成 牌型 ] ， 發 這種 牌 有 一定 的 概率 。 這種 概率 通常 稱為 賠率 。 在 賠率 不佳 的 情況 下 ， 聽牌 不太可能 形成 牌型 。</t>
+    <t>Nuts 必勝牌 必勝牌 指 特定 情況 下 最 強牌 如果 已發 牌 之中 某 玩家 擁有 最好 一手 牌 那麼 他 就是 拿到 必勝牌 某些 牌型 類別 中 使用 此術語 例如 必勝 同花 牌 或者 必勝 順子 牌指 已知 牌面 中 最強 同花 或者 順子</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odds（賠率）：一定數量的聽牌，剩餘1張（可能多於1張）來牌的話就可以形成牌型並使自己的牌型增強 ，發這種牌有一定的概率。 這種概率通常稱為賠率。 </t>
+  </si>
+  <si>
+    <t>Odds 賠率 一定 數量 聽牌 剩餘 1 張 可能 多 於 1 張 來牌 話 可以 形成 牌型 並使 自己 牌型 增強 發 這種 牌 有 一定 概率 這種 概率 通常 稱為 賠率</t>
   </si>
   <si>
     <t>Outs（出路）：也叫補牌，能夠使玩家在某個階段所有可能獲勝的公共牌。 如口袋對8的玩家需要再獲得一張8，那麼他就有兩個「出路」（兩張不同花色的8）。</t>
   </si>
   <si>
-    <t>Outs （ 出路 ） ： 也 叫 補牌 ， 能夠 使 玩家 在 某個 階段 所有 可能 獲勝 的 公共牌 。 如 口袋 對 8 的 玩家 需要 再 獲得 一張 8 ， 那麼 他 就 有 兩個 「 出路 」 （ 兩張 不同 花色 的 8 ） 。</t>
+    <t>Outs 出路 叫 補牌 能夠 使 玩家 某個 階段 所有 可能 獲勝 公共牌 如 口袋 對 8 玩家 需要 再 獲得 一張 8 那麼 他 有 兩個 出路 兩張 不同 花色 8</t>
   </si>
   <si>
     <t>Pocket pair（口袋對）：在德州撲克中，口袋對是由兩個玩家的底牌組成的對子牌。 例如，如果玩家有兩個K，便叫做有口袋K。</t>
   </si>
   <si>
-    <t>Pocket pair （ 口袋 對 ） ： 在 德州 撲克中 ， 口袋 對 是 由 兩個 玩家 的 底牌 組成 的 對子 牌 。 例如 ， 如果 玩家 有 兩個 K ， 便 叫做 有 口袋 K 。</t>
+    <t>Pocket pair 口袋 對 德州撲克 中 口袋 對 由 兩個 玩家 底牌 組成 對子 牌 例如 如果 玩家 有 兩個 K 便 叫做 有 口袋 K</t>
   </si>
   <si>
     <t>Pot（底池）：底池是一個獎池，包括在成牌過程中進行的所有下注。 如果底池分配在兩個或更多玩家之間，例如，最佳牌型和最差牌型獲勝的高/低局賽事，或者如果兩個或更多玩家拿到相同牌型的話，則稱為平分獎池。</t>
   </si>
   <si>
-    <t>Pot （ 底池 ） ： 底池 是 一個 獎池 ， 包括 在 成牌 過程 中 進行 的 所有 下注 。 如果 底池 分配 在 兩個 或 更 多 玩家 之間 ， 例如 ， 最佳 牌型 和 最差 牌型 獲勝 的 高 / 低局 賽事 ， 或者 如果 兩個 或 更 多 玩家 拿到 相同 牌型 的 話 ， 則稱 為 平分 獎池 。</t>
+    <t>Pot 底池 底池 獎池 包括 成牌 過程 中 進行 所有 下注 如果 底池 分配 兩個 或 更 多 玩家 之間 例如 最佳 牌型 和 最差 牌型 獲勝 高 低局 賽事 或者 如果 兩個 或 更 多 玩家 拿到 相同 牌型 話 則稱 為 平分 獎池</t>
   </si>
   <si>
     <t>Pot Limit（底池限注）：底池限制是一種「底池大小必須小於或等於當前底池大小」的下注結構。 下注可以是任何值，但必須小於或等於當前底池大小，但通常大於上次下注或加注的大小。</t>
   </si>
   <si>
-    <t>Pot Limit （ 底池 限注 ） ： 底池 限制 是 一種 「 底池 大小 必須 小 於 或 等 於 當前 底池 大小 」 的 下注 結構 。 下注 可以 是 任何 值 ， 但 必須 小 於 或 等 於 當前 底池 大小 ， 但 通常 大 於 上次 下注 或 加注 的 大小 。</t>
+    <t>Pot Limit 底池 限注 底池 限制 一種 底池 大小 必須 小 於 或 等 於 當前 底池 大小 下注 結構 下注 可以 任何 值 但 必須 小 於 或 等 於 當前 底池 大小 但 通常 大 於 上次 下注 或 加注 大小</t>
   </si>
   <si>
     <t>Pot Odds（底池賠率）：底池賠率是「可以贏得的獎金」與「獲得獎金的機會所需的成本」之間的比率。 因此，它們是給定賭注的反向成本效益比。</t>
   </si>
   <si>
-    <t>Pot Odds （ 底池 賠率 ） ： 底池 賠率 是 「 可以 贏得 的 獎金 」 與 「 獲得 獎金 的 機會 所 需 的 成本 」 之間 的 比率 。 因此 ， 它們 是 給定 賭注 的 反向 成本 效益 比 。</t>
+    <t>Pot Odds 底池 賠率 底池 賠率 可以 贏得 獎金 獲得 獎金 機會 所 需 成本 之間 比率 因此 它們 給定 賭注 反向 成本 效益 比</t>
   </si>
   <si>
     <t>Pre flop（翻牌前）：指的是德州撲克和奧馬哈等游戲中，發出底牌後，公共牌出現以前的第一輪叫注階段。</t>
   </si>
   <si>
-    <t>Pre flop （ 翻牌前 ） ： 指 的 是 德州 撲克 和 奧馬哈 等 游戲 中 ， 發出 底牌 後 ， 公共牌 出現 以前 的 第一 輪 叫 注階段 。</t>
+    <t>Pre flop 翻牌前 指 德州撲克 和 奧馬哈 等 游戲 中 發出 底牌 後 公共牌 出現 以前 第一 輪 叫注 階段</t>
   </si>
   <si>
     <t>Raise（加注）：加注是當一個玩家面對另一位玩家的下注時他可以採取的動作。 加注是超過對手下注金額的下注。 每輪加注的數量和大小可能會根據每個地方的規則而受到不同限制。 通常，每輪下注允許3，4或5次（5次不常見）加注。 再次加注到對手的加注時，該加注稱為再加注。</t>
   </si>
   <si>
-    <t>Raise （ 加注 ） ： 加注 是 當一個 玩家 面對 另 一位 玩家 的 下注 時 他 可以 採取 的 動作 。 加注 是 超過 對 手下 注金額 的 下注 。 每輪 加注 的 數量 和 大小 可能 會 根據 每個 地方 的 規則 而 受到 不同 限制 。 通常 ， 每輪 下注 允許 3 ， 4 或 5 次 （ 5 次 不常見 ） 加注 。 再次 加注 到 對 手 的 加注 時 ， 該 加注 稱為 再 加注 。</t>
+    <t>Raise 加注 加注 當一個 玩家 面對 另 一位 玩家 下注 時 他 可以 採取 動作 加注 超過 對手 下注 金額 下注 每輪 加注 數量 和 大小 可能 會 每個 地方 規則 受到 不同 限制 通常 每輪 下注 允許 3 4 或 5 次 5 次 不常見 加注 再次 加注 到 對手 加注 時 該 加注 稱為 再 加注</t>
   </si>
   <si>
     <t>Re-raise（再加注）：再加注是在另一位玩家已經加注之後加注。 如果一位玩家下注，第二位玩家加注，而第三位玩家在轉牌上加注，則第三位玩家算是再加注。</t>
   </si>
   <si>
-    <t>Re - raise （ 再 加注 ） ： 再 加注 是 在 另 一位 玩家 已經 加注 之 後 加注 。 如果 一位 玩家 下注 ， 第二位 玩家 加注 ， 而 第三位 玩家 在 轉牌 上 加注 ， 則 第三位 玩家 算是 再 加注 。</t>
+    <t>Re - raise 再 加注 再 加注 另 一位 玩家 已經 加注 之 後 加注 如果 一位 玩家 下注 第二位 玩家 加注 第三位 玩家 轉牌 上 加注 則 第三位 玩家 算是 再 加注</t>
   </si>
   <si>
     <t>River（河牌）：德州撲克和奧馬哈等游戲中，第5張公共牌叫河牌。</t>
   </si>
   <si>
-    <t>River （ 河牌 ） ： 德州 撲克 和 奧馬哈 等 游戲 中 ， 第 5 張 公共牌 叫 河牌 。</t>
+    <t>River 河牌 德州撲克 和 奧馬哈 等 游戲 中 第 5 張 公共牌 叫 河牌</t>
   </si>
   <si>
     <t>Rag（廢牌）：廢牌指的是沒有價值或很弱的牌。 例如，在德州撲克中，擁有一張A和一張低牌（例如4等）的起手牌被表示為A廢牌。</t>
   </si>
   <si>
-    <t>Rag （ 廢牌 ） ： 廢牌 指 的 是 沒 有 價值 或 很 弱 的 牌 。 例如 ， 在 德州 撲克中 ， 擁有 一張 A 和 一張 低牌 （ 例如 4 等 ） 的 起 手牌 被 表示 為 A 廢牌 。</t>
+    <t>Rag 廢牌 廢牌 指 沒 有 價值 或 很 弱 牌 例如 德州撲克 中 擁有 一張 A 和 一張 低牌 例如 4 等 起 手牌 表示 為 A 廢牌</t>
   </si>
   <si>
     <t>Rake（抽水）：抽水指的是每局要固定從獎池中抽取一定比例給賭場等。 收取抽水的牌型稱作抽水牌。 抽水取決於各種條件。 通常，如果超過某個金額限制，將抽出5％的底池作為抽水。 每手最大抽水也根據特定規則和賭注進行控制。 如果牌局沒有進行到翻牌階段，則不會收取抽水。 這也稱為「不翻牌，不抽水」。</t>
   </si>
   <si>
-    <t>Rake （ 抽水 ） ： 抽水 指 的 是 每局 要 固定 從 獎池 中 抽取 一定 比例 給賭場 等 。 收取 抽水 的 牌型 稱作 抽水 牌 。 抽水 取決 於 各種 條件 。 通常 ， 如果 超過 某個 金額 限制 ， 將 抽出 5 ％ 的 底 池作 為 抽水 。 每手 最大 抽水 也 根據 特定 規則 和 賭注 進行 控制 。 如果 牌局 沒有 進行 到 翻牌 階段 ， 則不會 收取 抽水 。 這也稱 為 「 不 翻牌 ， 不 抽水 」 。</t>
+    <t>Rake 抽水 抽水 指 每局 要 固定 從 獎池 中 抽取 一定 比例 給賭場 等 收取 抽水 牌型 稱作 抽水 牌 抽水 取決 於 各種 條件 通常 如果 超過 某個 金額 限制 將 抽出 5 ％ 底 池作 為 抽水 每手 最大 抽水 特定 規則 和 賭注 進行 控制 如果 牌局 沒有 進行 到 翻牌 階段 則不會 收取 抽水 這也稱 為 不 翻牌 不 抽水</t>
   </si>
   <si>
     <t>Rock（石頭）：石頭指的是持保守態度的玩家，只有在拿到很少的幾手強牌的時候才入池。 他的策略是「只打最強的牌」，但是當拿到期望值很高的強牌時，即使很可能輸掉，也只能保持積極的態度打下去。</t>
   </si>
   <si>
-    <t>Rock （ 石頭 ） ： 石頭 指 的 是 持 保守 態度 的 玩家 ， 只有 在 拿到 很少 的 幾手 強牌 的 時候 才 入池 。 他 的 策略 是 「 只 打 最強 的 牌 」 ， 但是 當 拿到 期望值 很 高 的 強牌 時 ， 即使 很 可能 輸掉 ， 也 只能 保持 積極 的 態度 打 下去 。</t>
+    <t>Rock 石頭 石頭 指 持 保守 態度 玩家 只有 拿到 很少 幾手 強牌 時候 才 入池 他 策略 只 打 最強 牌 但是 當 拿到 期望值 很 高 強牌 時 即使 很 可能 輸掉 只能 保持 積極 態度 打 下去</t>
   </si>
   <si>
     <t>Ring game（現金桌）：現金桌是在賭場中始終開放的賭桌，您可以在這裡持籌碼坐下並以該賭桌的速度持續 玩游戲。 玩家可以自由進入游戲並站起。 如果您想以較低或較高的速度進行游戲，則必須移動桌子。</t>
   </si>
   <si>
-    <t>Ring game （ 現金桌 ） ： 現金桌 是 在 賭場 中始 終開 放 的 賭桌 ， 您 可以 在 這裡持 籌碼 坐下 並以 該 賭桌 的 速度 持續 玩游 戲 。 玩家 可以 自由 進入 游戲 並站 起 。 如果 您 想 以 較 低 或 較 高 的 速度 進行 游戲 ， 則必須 移動 桌子 。</t>
+    <t>Ring game 現金桌 現金桌 賭場 中始 終開 放 賭桌 您 可以 這裡持 籌碼 坐下 並以 該 賭桌 速度 持續 玩游 戲 玩家 可以 自由 進入 游戲 並站 起 如果 您 想 以 較 低 或 較 高 速度 進行 游戲 則必須 移動 桌子</t>
   </si>
   <si>
     <t>Shark（鯊魚）：鯊魚指的是桌上的強大且採取積極打法的玩家。 鯊魚攻擊弱小的玩家並從中盈利。</t>
   </si>
   <si>
-    <t>Shark （ 鯊魚 ） ： 鯊魚 指 的 是 桌上 的 強大且 採取 積極 打法 的 玩家 。 鯊魚 攻擊 弱小 的 玩家 並從 中 盈利 。</t>
+    <t>Shark 鯊魚 鯊魚 指 桌上 強大且 採取 積極 打法 玩家 鯊魚 攻擊 弱小 玩家 並從 中 盈利</t>
   </si>
   <si>
     <t>Showdown（亮牌）：亮牌是牌型（游戲）的最後部分，剩餘玩家展示自己的牌，並決定誰擁有最好的牌以及誰贏得底池。 亮牌將一樣在最後一輪下注之後進行。</t>
   </si>
   <si>
-    <t>Showdown （ 亮牌 ） ： 亮牌 是 牌型 （ 游戲 ） 的 最 後 部分 ， 剩餘 玩家 展示 自己 的 牌 ， 並決定 誰 擁有 最好 的 牌 以及 誰 贏得 底池 。 亮牌 將一樣 在 最後一輪 下注 之後進行 。</t>
+    <t>Showdown 亮牌 亮牌 牌型 游戲 最 後 部分 剩餘 玩家 展示 自己 牌 並決定 誰 擁有 最好 牌 誰 贏得 底池 亮牌 將一樣 最後一輪 下注 之後進行</t>
   </si>
   <si>
     <t>Slowplay（慢打）：慢打指的是「為了使對手消除警惕，拿到強牌的時候也故意採取消極示弱的打法」，「給人以為是弱牌的印象」或「讓對手誤以 為自己拿到的是最強牌」 的戰略戰術。</t>
   </si>
   <si>
-    <t>Slowplay （ 慢打 ） ： 慢打 指 的 是 「 為 了 使 對 手 消除 警惕 ， 拿到 強牌 的 時候 也 故意 採 取消 極 示弱 的 打法 」 ， 「 給人以 為 是 弱牌 的 印象 」 或 「 讓 對 手誤 以 為 自己 拿到 的 是 最 強牌 」 的 戰略 戰術 。</t>
+    <t>Slowplay 慢打 慢打 指 為 使 對手 消除 警惕 拿到 強牌 時候 故意 採 取消 極 示弱 打法 給人以 為 弱牌 印象 或 讓 對手 誤以 為 自己 拿到 最 強牌 戰略 戰術</t>
   </si>
   <si>
     <t>Side Pot（邊池）：邊池是指用全押玩家的牌局中放在側面的底池。 牌局的主要底池是指所有活躍玩家都能獲得的底池。 如果一名玩家全押並且至少有兩名對手仍在賽事中並且他們不是全押，則所有隨後的下注都放在邊池中，而不是全押的玩家可以獲得。</t>
   </si>
   <si>
-    <t>Side Pot （ 邊池 ） ： 邊池 是 指用 全押 玩家 的 牌局 中 放在 側面 的 底池 。 牌局 的 主要 底池 是 指 所有 活躍 玩家 都 能 獲得 的 底池 。 如果 一名 玩家 全押 並且 至少 有 兩名 對 手 仍 在 賽事 中 並且 他們 不是 全押 ， 則 所有 隨後的 下注 都 放在 邊池 中 ， 而 不是 全押 的 玩家 可以 獲得 。</t>
+    <t>Side Pot 邊池 邊池 指用 全押 玩家 牌局 中 放在 側面 底池 牌局 主要 底池 指 所有 活躍 玩家 能 獲得 底池 如果 一名 玩家 全押 並且 至少 有 兩名 對手 仍 賽事 中 並且 他們 不是 全押 則 所有 隨後的 下注 放在 邊池 中 不是 全押 玩家 可以 獲得</t>
   </si>
   <si>
     <t>Semi bluff（半詐牌）：半詐牌指的是用目前較弱但有可能發展成強牌的手牌進行虛張聲勢。 半詐牌的目標不一定是淘汰所有對手。 因為如果在亮牌為止完成牌型，仍然有機會獲得底池。 因此，半詐牌的目的之一是在早期下注中將籌碼盡可能收集到底池中，以增加可能獲得的籌碼。 這一舉動是有益的，因為對手很可能棄牌並且自己可能可以贏得一個大底池。 半詐牌適用的典型情況是當自己在聽牌的時候，如果發出了適當的牌，將很可能形成牌型。</t>
   </si>
   <si>
-    <t>Semi bluff （ 半詐牌 ） ： 半詐牌 指 的 是 用 目前 較弱 但 有 可能 發展 成 強牌 的 手牌 進行 虛張 聲勢 。 半詐牌 的 目標 不 一定 是 淘汰 所有 對手 。 因為 如果 在 亮牌 為止 完成 牌型 ， 仍然 有 機會 獲得 底池 。 因此 ， 半詐牌 的 目的 之一 是 在 早期 下注 中將 籌碼 盡 可能 收集 到底 池中 ， 以 增加 可能 獲得 的 籌碼 。 這一 舉動 是 有益 的 ， 因為 對 手 很 可能 棄牌 並且 自己 可能 可以 贏得 一個 大底 池 。 半詐牌 適用 的 典型 情況 是當 自己 在 聽牌 的 時候 ， 如果 發出 了 適當 的 牌 ， 將 很 可能 形成 牌型 。</t>
+    <t>Semi bluff 半詐牌 半詐牌 指 用 目前 較弱 但 有 可能 發展 成 強牌 手牌 進行 虛張 聲勢 半詐牌 目標 不 一定 淘汰 所有 對手 因為 如果 亮牌 為止 完成 牌型 仍然 有 機會 獲得 底池 因此 半詐牌 目的 之一 早期 下注 中將 籌碼 盡 可能 收集 到底 池中 以 增加 可能 獲得 籌碼 這一 舉動 有益 因為 對手 很 可能 棄牌 並且 自己 可能 可以 贏得 大底 池 半詐牌 適用 典型 情況 是當 自己 聽牌 時候 如果 發出 適當 牌 將 很 可能 形成 牌型</t>
   </si>
   <si>
     <t>Starting hand chat（起始手牌表）：起始手牌表是可以入池的手牌的概率表格歸納，並說明瞭根據這些手要採取的操作。 SHC（起始手牌表）對于初學者在第一輪下注中制定策略特別有用。</t>
   </si>
   <si>
-    <t>Starting hand chat （ 起始 手牌表 ） ： 起始 手牌 表是 可以 入池 的 手牌 的 概率 表格 歸納 ， 並說明 瞭根據 這些 手要 採取 的 操作 。 SHC （ 起始 手牌表 ） 對于 初學者 在 第一 輪 下注 中 制定 策略 特別 有用 。</t>
+    <t>Starting hand chat 起始 手牌表 起始 手牌 表是 可以 入池 手牌 概率 表格 歸納 並說明 瞭根據 這些 手要 採取 操作 SHC 起始 手牌表 對于 初學者 第一 輪 下注 中 制定 策略 特別 有用</t>
   </si>
   <si>
     <t>Streak（連運）：連運指的是牌局中連著幸運贏牌或連著厄運輸牌的情況。</t>
   </si>
   <si>
-    <t>Streak （ 連運 ） ： 連運指 的 是 牌局 中連著 幸運 贏牌 或 連著 厄 運輸牌 的 情況 。</t>
+    <t>Streak 連運 連運指 牌局 中連著 幸運 贏牌 或 連著 厄 運輸牌 情況</t>
   </si>
   <si>
     <t>Turn（轉牌）：德州撲克或奧馬哈等有使用公共牌的游戲中，第4張公共牌稱作轉牌。</t>
   </si>
   <si>
-    <t>Turn （ 轉牌 ） ： 德州 撲克 或 奧馬哈 等 有 使用 公共牌 的 游戲 中 ， 第 4 張 公共牌 稱作 轉牌 。</t>
+    <t>Turn 轉牌 德州撲克 或 奧馬哈 等 有 使用 公共牌 游戲 中 第 4 張 公共牌 稱作 轉牌</t>
   </si>
   <si>
     <t>Tell（小動作）：小動作是指玩家無意間透露出來的一些下意識的動作，這些動作有可能讓他輸掉。 其中也包括有意識的動作。 比如發現對方正在觀察自己的時候刻意作出一些假動作演技讓對手作出錯誤判斷。</t>
   </si>
   <si>
-    <t>Tell （ 小動作 ） ： 小動作 是 指 玩家 無意間 透露 出來 的 一些 下意識 的 動作 ， 這些 動作 有 可能 讓 他 輸掉 。 其中 也 包括 有意 識 的 動作 。 比如 發現 對 方正 在 觀察 自己 的 時候 刻意 作出 一些 假動作 演技 讓 對 手 作出 錯誤 判斷 。</t>
-  </si>
-  <si>
-    <t>Tilt（上頭）：從廣義上講，上頭指的是指玩家無法做出合理判斷，出現了一些情緒化的狀態。 例如，玩家為了儘快奪回自己損失的大量籌碼採取激進的方式下注，明顯可以看出是已弱牌去碰運氣想要拿大獎池的情況，我 們就說他是上頭了。</t>
-  </si>
-  <si>
-    <t>Tilt （ 上頭 ） ： 從 廣義上講 ， 上頭 指 的 是 指 玩家 無法 做出 合理 判斷 ， 出現 了 一些 情緒化 的 狀態 。 例如 ， 玩家 為 了 儘 快 奪 回 自己 損失 的 大量 籌碼 採取 激進 的 方式 下注 ， 明顯 可以 看出 是 已 弱牌 去 碰運氣 想要 拿大獎 池 的 情況 ， 我 們 就 說 他 是 上頭 了 。</t>
-  </si>
-  <si>
-    <t>Tournament（賽事）：撲克賽事是一種游戲形式，每個玩家都可以通過買入來參加賽事。 每個玩家最初獲得相同數量的籌碼，如果輸掉了手上所有籌碼，就輸掉了賽事。 在可重購的賽事中，玩家可以在初始階段再次買入。 獎金是根據贏得賽事的玩家的排名分配的。 根據特定的支出結構，確定獲得多少獎金。 當然，可以使用金錢以外的獎品。 例如，實際物品或者是更高級別賽事的門票等。</t>
-  </si>
-  <si>
-    <t>Tournament （ 賽事 ） ： 撲克賽 事 是 一種 游戲 形式 ， 每個 玩家 都 可以 通過 買入 來 參加賽 事 。 每個 玩家 最初 獲得 相同 數量 的 籌碼 ， 如果 輸掉 了 手上 所有 籌碼 ， 就 輸掉 了 賽事 。 在 可 重購 的 賽事 中 ， 玩家 可以 在 初始 階段 再次 買入 。 獎金 是 根據 贏得賽 事 的 玩家 的 排名 分配 的 。 根據 特定 的 支出 結構 ， 確定 獲得 多少 獎金 。 當然 ， 可以 使用 金錢 以外 的 獎品 。 例如 ， 實際 物品 或者 是 更 高級 別賽 事 的 門票 等 。</t>
+    <t>Tell 小動作 小動作 指 玩家 無意間 透露 出來 一些 下意識 動作 這些 動作 有 可能 讓 他 輸掉 其中 包括 有意 識 動作 比如 發現 對 方正 觀察 自己 時候 刻意 作出 一些 假動作 演技 讓 對手 作出 錯誤 判斷</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tilt（上頭）：上頭指的是指玩家無法做出合理判斷，出現了一些情緒化的狀態。 </t>
+  </si>
+  <si>
+    <t>Tilt 上頭 上頭 指 指 玩家 無法 做出 合理 判斷 出現 一些 情緒化 狀態</t>
+  </si>
+  <si>
+    <t>Tournament（賽事）：撲克賽事是一種游戲形式，每個玩家都可以通過買入來參加賽事。 每個玩家最初獲得相同數量的籌碼，如果輸掉了手上所有籌碼，就輸掉了賽事。 在可重購的賽事中，玩家可以在初始階段再次買入。 獎金是根據贏得賽事的玩家的排名分配的。 根據特定的支出結構，確定獲得多少獎金。 當然，可以使用金錢以外的獎品。</t>
+  </si>
+  <si>
+    <t>Tournament 賽事 撲克賽 事 一種 游戲 形式 每個 玩家 可以 通過 買入 來 參加賽 事 每個 玩家 最初 獲得 相同 數量 籌碼 如果 輸掉 手上 所有 籌碼 輸掉 賽事 可 重購 賽事 中 玩家 可以 初始 階段 再次 買入 獎金 贏得賽 事 玩家 排名 分配 特定 支出 結構 確定 獲得 多少 獎金 當然 可以 使用 金錢 以外 獎品</t>
   </si>
   <si>
     <t>UTG(under the gun)（槍口位）：大盲注左手邊第一個為槍口位，翻牌前最先行動，在德州撲克裡位置越靠後越有利，因此坐在槍口位的玩家是最被動的玩家，由於起手牌要求比其他位置都要高，往往會翻牌前棄牌。</t>
   </si>
   <si>
-    <t>UTG ( under the gun ) （ 槍口位 ） ： 大盲注 左手 邊 第一 個 為 槍口位 ， 翻牌前 最 先行 動 ， 在 德州 撲克裡 位置 越靠後越 有利 ， 因此 坐在 槍口位 的 玩家 是 最 被 動 的 玩家 ， 由 於 起 手牌 要求 比 其他 位置 都 要 高 ， 往往 會 翻牌前 棄牌 。</t>
+    <t>UTG ( under the gun ) 槍口位 大盲注 左手 邊 第一 個 為 槍口位 翻牌前 最先 行動 德州撲克 裡 位置 越靠後越 有利 因此 坐在 槍口位 玩家 最 動 玩家 由 於 起 手牌 要求 比 其他 位置 要 高 往往 會 翻牌前 棄牌</t>
   </si>
   <si>
     <t>概率與賠率的基本概念：概率是自己擊中公共牌後能贏的機率；賠率是投入籌碼和贏回籌碼之間的比例。打牌不算概率幾乎是在瞎玩，概率和賠率就是幫你做正確決定的工具。</t>
   </si>
   <si>
-    <t>概率 與 賠率 的 基本概念 ： 概率 是 自己 擊中 公共牌 後 能贏 的 機率 ； 賠率 是 投入 籌碼 和 贏回 籌碼 之間 的 比例 。 打牌 不算 概率 幾乎 是 在 瞎 玩 ， 概率 和 賠率 就是 幫 你 做 正確 決定 的 工具 。</t>
+    <t>概率 賠率 基本概念 概率 自己 擊中 公共牌 後 能贏 機率 賠率 投入 籌碼 和 贏回 籌碼 之間 比例 打牌 不算 概率 幾乎 瞎 玩 概率 和 賠率 就是 幫 你 做 正確 決定 工具</t>
   </si>
   <si>
     <t>Outs (出路) 與 42 定律：第一步，數能贏的牌叫做 Outs（出路）。第二步，算概率。簡單算法是「42 定律」：在發出翻牌之後，能贏的概率是用你能贏的牌的張數乘以 4；在轉牌後，用你能贏的數量乘以 2。這是因為未知的牌大約剩 50 張左右（46或47張）所換算出的百分比捷徑。</t>
   </si>
   <si>
-    <t>Outs ( 出路 ) 與 42 定律 ： 第一步 ， 數能贏 的 牌 叫做 Outs （ 出路 ） 。 第二步 ， 算 概率 。 簡單 算法 是 「 42 定律 」 ： 在 發出 翻牌 之 後 ， 能贏 的 概率 是 用 你 能贏 的 牌 的 張數 乘以 4 ； 在 轉牌 後 ， 用 你 能贏 的 數量 乘以 2 。 這是 因為 未知 的 牌大約 剩 50 張 左右 （ 46 或 47 張 ） 所換 算出 的 百分比 捷徑 。</t>
+    <t>Outs ( 出路 ) 42 定律 第一步 數能贏 牌 叫做 Outs 出路 第二步 算 概率 簡單 算法 42 定律 發出 翻牌 之 後 能贏 概率 用 你 能贏 牌 張數 乘以 4 轉牌 後 用 你 能贏 數量 乘以 2 這是 因為 未知 牌大約 剩 50 張 左右 46 或 47 張 所換 算出 百分比 捷徑</t>
   </si>
   <si>
     <t>賠率計算與決策應用：賠率是你要付出的籌碼和已經在底池裡籌碼的比例。例如底池 100，對手下注 50（底池變 150），你跟注 50 去贏 150，賠率就是 1:3（25%）。拿賠率對比算出來的概率，如果贏的概率高於投入的賠率，數學上就應該跟注；反之則棄牌。</t>
   </si>
   <si>
-    <t>賠率 計算 與 決策 應用 ： 賠率 是 你 要 付出 的 籌碼 和 已經 在 底 池裡 籌碼 的 比例 。 例如 底池 100 ， 對 手下 注 50 （ 底池 變 150 ） ， 你 跟注 50 去贏 150 ， 賠率 就是 1 : 3 （ 25% ） 。 拿 賠率 對 比算 出來 的 概率 ， 如果 贏的 概率 高 於 投入 的 賠率 ， 數學 上 就 應該 跟注 ； 反之 則 棄牌 。</t>
+    <t>賠率 計算 決策 應用 賠率 你 要 付出 籌碼 和 已經 底 池裡 籌碼 比例 例如 底池 100 對手 下注 50 底池 變 150 你 跟注 50 去贏 150 賠率 就是 1 : 3 25% 拿 賠率 對 比算 出來 概率 如果 贏的 概率 高 於 投入 賠率 數學 上 應該 跟注 反之 則 棄牌</t>
   </si>
   <si>
     <t>隱含賠率 (Implied Odds)：當單算賠率不足以跟注時，需考慮對手後手的籌碼。當你確定發出你要的牌（中牌）後，對手會支付他後手還不在底池裡的籌碼時，就可以把這些籌碼預先算入你能贏的底池中來重新計算賠率。這通常適用於對手牌力極強（如 AA）而難以棄牌的情況。</t>
   </si>
   <si>
-    <t>隱含 賠率 ( Implied Odds ) ： 當單 算 賠率 不足以 跟注 時 ， 需考慮 對 手後手 的 籌碼 。 當你 確定 發出 你 要 的 牌 （ 中牌 ） 後 ， 對 手會 支付 他後手 還不在 底 池裡 的 籌碼 時 ， 就 可以 把 這些 籌碼 預先 算入 你 能贏 的 底池 中來 重新 計算 賠率 。 這 通常 適用 於 對 手牌力 極強 （ 如 AA ） 而 難以 棄牌 的 情況 。</t>
+    <t>隱含 賠率 ( Implied Odds ) 當單 算 賠率 不足以 跟注 時 需考慮 對手 後 手 籌碼 當你 確定 發出 你 要 牌 中牌 後 對手 會 支付 他後手 還不在 底 池裡 籌碼 時 可以 把 這些 籌碼 預先 算入 你 能贏 底池 中來 重新 計算 賠率 這 通常 適用 於 對手 牌力 極強 如 AA 難以 棄牌 情況</t>
   </si>
   <si>
     <t>棄牌率 (Fold Equity)：即使目前牌力落後，但透過再加注等激進打法，讓對手覺得自己牌力不夠大而選擇蓋牌的機率。打棄牌率對於玩家的讀牌能力有一定要求，讀對手牌力範圍越準，就越能找到詐唬（偷雞）的時機。</t>
   </si>
   <si>
-    <t>棄牌 率 ( Fold Equity ) ： 即使 目前 牌力 落 後 ， 但 透過 再 加注 等 激進 打法 ， 讓 對 手覺 得 自己 牌力 不夠 大 而 選擇 蓋牌 的 機率 。 打 棄牌 率 對 於 玩家 的 讀牌 能力 有 一定 要求 ， 讀 對 手牌 力範圍 越準 ， 就 越 能 找到 詐唬 （ 偷雞 ） 的 時機 。</t>
+    <t>棄牌 率 ( Fold Equity ) 即使 目前 牌力 落 後 但 透過 再 加注 等 激進 打法 讓 對手 覺得 自己 牌力 不夠 大 選擇 蓋牌 機率 打 棄牌 率 對 於 玩家 讀牌 能力 有 一定 要求 讀 對手 牌力 範圍 越準 越 能 找到 詐唬 偷雞 時機</t>
   </si>
   <si>
     <t>範圍與範圍優勢：在撲克對抗中，範圍是不可忽略的因素。翻牌前在前位（如槍口位 UTG）加注（Raise）的人，通常會被認為牌力範圍很強（例如範圍內包含最大的同花 A）。玩家可以有效地利用自己的範圍優勢來進行詐唬（偷雞），前提是對手也具備解讀範圍的能力。</t>
   </si>
   <si>
-    <t>範圍 與 範圍 優勢 ： 在 撲克 對 抗中 ， 範圍 是 不可 忽略 的 因素 。 翻牌前 在 前位 （ 如 槍口位 UTG ） 加注 （ Raise ） 的 人 ， 通常 會 被 認為 牌力 範圍 很強 （ 例如 範圍 內 包含 最大 的 同花 A ） 。 玩家 可以 有效 地 利用 自己 的 範圍 優勢 來 進行 詐 唬 （ 偷雞 ） ， 前提 是 對 手 也 具備 解讀 範圍 的 能力 。</t>
+    <t>範圍 範圍 優勢 撲克 對 抗中 範圍 不可 忽略 因素 翻牌前 前位 如 槍口位 UTG 加注 Raise 人 通常 會 認為 牌力 範圍 很強 例如 範圍 內 包含 最大 同花 A 玩家 可以 有效 地 利用 自己 範圍 優勢 來 進行 詐唬 偷雞 前提 對手 具備 解讀 範圍 能力</t>
   </si>
   <si>
     <t>翻牌前動作與範圍判斷：翻牌前起 Raise 的人，其範圍是「無上限」的（包含 AA、KK 等）。相反地，面對加注卻只是選擇跟注（沒有 3bet）的玩家，通常會被認為排除了最頂級的牌力，範圍主要集中在中等牌力，因為拿大牌通常會選擇 3bet 來避免給後面玩家太好的賠率。</t>
   </si>
   <si>
-    <t>翻牌前 動作 與 範圍 判斷 ： 翻牌前 起 Raise 的 人 ， 其範圍 是 「 無 上限 」 的 （ 包含 AA 、 KK 等 ） 。 相反 地 ， 面對 加注 卻 只是 選擇 跟注 （ 沒有 3bet ） 的 玩家 ， 通常 會 被 認為 排除 了 最 頂級 的 牌力 ， 範圍 主要 集中 在 中等 牌力 ， 因為 拿 大牌 通常 會選擇 3bet 來 避免 給後面 玩家 太好 的 賠率 。</t>
+    <t>翻牌前 動作 範圍 判斷 翻牌前 起 Raise 人 其範圍 無 上限 包含 AA KK 等 相反 地 面對 加注 卻 只是 選擇 跟注 沒有 3bet 玩家 通常 會 認為 排除 最 頂級 牌力 範圍 主要 集中 中等 牌力 因為 拿 大牌 通常 會選擇 3bet 來 避免 給後面 玩家 太好 賠率</t>
   </si>
   <si>
     <t>3bet 的作用與好處：當拿到一、二等強牌時，面對前位加注強烈建議進行 3bet。好處包含：1. 利用位置優勢搶奪主動權，讓翻牌後更容易打；2. 把自己的範圍擴大並維持在最高範圍；3. 隔離後面牌力較弱的玩家入池。</t>
   </si>
   <si>
-    <t>3bet 的 作用 與 好 處 ： 當 拿到 一 、 二等 強牌 時 ， 面對 前位 加注 強烈 建議 進行 3bet 。 好處 包含 ： 1 . 利用 位置 優勢 搶 奪主動權 ， 讓 翻牌後 更 容易 打 ； 2 . 把 自己 的 範圍 擴大 並維持 在 最高 範圍 ； 3 . 隔離後面 牌力 較 弱 的 玩家 入池 。</t>
+    <t>3bet 作用 好 處 當 拿到 一 二等 強牌 時 面對 前位 加注 強烈 建議 進行 3bet 好處 包含 1 . 利用 位置 優勢 搶 奪主動權 讓 翻牌後 更 容易 打 2 . 把 自己 範圍 擴大 並維持 最高 範圍 3 . 隔離後面 牌力 較 弱 玩家 入池</t>
   </si>
   <si>
     <t>大盲位的底端範圍：當翻牌前已有多人入池，大盲位玩家因為擁有極佳的賠率而選擇最後跟注時，其範圍通常沒有頂端牌力（否則會選擇加注），但包含了極廣的「底端範圍」（各種小牌）。因此，當翻牌發出如 4、5、6 這類小牌面時，大盲位反而是最有可能擊中牌面的人。</t>
   </si>
   <si>
-    <t>大盲位 的 底端 範圍 ： 當 翻牌前 已有 多人入 池 ， 大盲位 玩家 因為 擁有 極佳 的 賠率 而 選擇 最 後 跟注 時 ， 其範圍 通常 沒有 頂端 牌力 （ 否則 會 選擇 加注 ） ， 但 包含 了 極廣 的 「 底端 範圍 」 （ 各種 小牌 ） 。 因此 ， 當 翻牌 發出 如 4 、 5 、 6 這類 小牌 面時 ， 大盲位 反而 是 最 有 可能 擊中 牌面 的 人 。</t>
+    <t>大盲位 底端 範圍 當 翻牌前 已有 多人入 池 大盲位 玩家 因為 擁有 極佳 賠率 選擇 最 後 跟注 時 其範圍 通常 沒有 頂端 牌力 否則 會 選擇 加注 但 包含 極廣 底端 範圍 各種 小牌 因此 當 翻牌 發出 如 4 5 6 這類 小牌 面時 大盲位 反而 最 有 可能 擊中 牌面 人</t>
   </si>
   <si>
     <t>形象 (Image) 對詐唬的影響：偷雞能否成功，除了合理的範圍建構外，「形象」也是關鍵因素。如果玩家平時打法非常兇且具創造性，對手較容易去抓他的詐唬；但如果是同樣的範圍操作換成形象不同的玩家來打，對手極可能就會選擇棄牌。</t>
   </si>
   <si>
-    <t>形象 ( Image ) 對詐 唬 的 影響 ： 偷雞 能否 成功 ， 除了 合理 的 範圍 建構 外 ， 「 形象 」 也 是 關鍵 因素 。 如果 玩家 平時 打法 非常 兇且 具創 造性 ， 對手 較 容易 去 抓 他 的 詐 唬 ； 但 如果 是 同樣 的 範圍 操作 換成 形象 不同 的 玩家 來 打 ， 對 手極 可能 就會 選擇 棄牌 。</t>
+    <t>形象 ( Image ) 對 詐唬 影響 偷雞 能否 成功 除了 合理 範圍 建構 外 形象 關鍵 因素 如果 玩家 平時 打法 非常 兇且 具創 造性 對手 較 容易 去 抓 他 詐唬 但 如果 同樣 範圍 操作 換成 形象 不同 玩家 來 打 對手 極 可能 就會 選擇 棄牌</t>
   </si>
 </sst>
 </file>
@@ -919,8 +973,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1223,1147 +1280,1219 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B142"/>
+  <dimension ref="A1:B151"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="178.8984375" customWidth="1"/>
-    <col min="2" max="2" width="95.69921875" customWidth="1"/>
+    <col min="1" max="1" width="57.69921875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="57.3984375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="7" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="8" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="9" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="10" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="11" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="12" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="13" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="14" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="15" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="16" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="17" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="18" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="19" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="20" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="21" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="22" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="23" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="24" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="25" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="26" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="27" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="28" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="29" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="30" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="31" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="32" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="33" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="34" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="35" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="36" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="37" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="38" spans="1:2" ht="116" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="39" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="40" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="41" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="42" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="43" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="44" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+    <row r="45" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+    <row r="46" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+    <row r="47" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+    <row r="48" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+    <row r="49" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+    <row r="50" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+    <row r="51" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+    <row r="52" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+    <row r="53" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+    <row r="54" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+    <row r="55" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+    <row r="56" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+    <row r="57" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+    <row r="58" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+    <row r="59" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+    <row r="60" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+    <row r="61" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+    <row r="62" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+    <row r="63" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+    <row r="64" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+    <row r="65" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+    <row r="66" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+    <row r="67" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+    <row r="68" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+    <row r="69" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+    <row r="70" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+    <row r="71" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+    <row r="72" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+    <row r="73" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+    <row r="74" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+    <row r="75" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+    <row r="76" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+    <row r="77" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+    <row r="78" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
+    <row r="79" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+    <row r="80" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+    <row r="81" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+    <row r="82" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+    <row r="83" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="1" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+    <row r="84" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+    <row r="85" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+    <row r="86" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+    <row r="87" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+    <row r="88" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+    <row r="89" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+    <row r="90" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+    <row r="91" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="1" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+    <row r="92" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+    <row r="93" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+    <row r="94" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+    <row r="95" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="1" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+    <row r="96" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
+    <row r="97" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="1" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
+      <c r="A98" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
+    <row r="99" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="1" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
+    <row r="100" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="1" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
+    <row r="101" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+    <row r="102" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+    <row r="103" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
+    <row r="104" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+      <c r="A104" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
+    <row r="105" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
+    <row r="106" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
+    <row r="107" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A107" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
+    <row r="108" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="1" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
+    <row r="109" spans="1:2" ht="159.5" x14ac:dyDescent="0.3">
+      <c r="A109" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
+    <row r="110" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+      <c r="A110" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="1" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
+    <row r="111" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A111" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="1" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
+    <row r="112" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A112" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="1" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
+    <row r="113" spans="1:2" ht="116" x14ac:dyDescent="0.3">
+      <c r="A113" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
+    <row r="114" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A114" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
+    <row r="115" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A115" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="1" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
+    <row r="116" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A116" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" s="1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
+    <row r="117" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A117" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="1" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
+    <row r="118" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
+    <row r="119" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A119" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="1" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
+    <row r="120" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A120" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="1" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
+    <row r="121" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+      <c r="A121" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
+    <row r="122" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+      <c r="A122" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="1" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
+    <row r="123" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A123" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
+    <row r="124" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A124" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
+    <row r="125" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A125" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
+    <row r="126" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+      <c r="A126" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="1" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
+    <row r="127" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
+      <c r="A127" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
+    <row r="128" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A128" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
+    <row r="129" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A129" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
+    <row r="130" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A130" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="1" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
+    <row r="131" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A131" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
+    <row r="132" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A132" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="1" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
+    <row r="133" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A133" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="1" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
+    <row r="134" spans="1:2" ht="130.5" x14ac:dyDescent="0.3">
+      <c r="A134" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="1" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
+    <row r="135" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A135" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="1" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
+    <row r="136" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A136" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="1" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
+    <row r="137" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A137" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="1" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
+    <row r="138" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A138" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="1" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
+    <row r="139" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+      <c r="A139" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" s="1" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
+    <row r="140" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
+      <c r="A140" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="1" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
+    <row r="141" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A141" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" s="1" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
+    <row r="142" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+      <c r="A142" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" s="1" t="s">
         <v>283</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A143" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A144" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A145" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A146" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A147" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A148" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A149" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+      <c r="A150" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
+      <c r="A151" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>301</v>
       </c>
     </row>
   </sheetData>

--- a/test/斷詞結果檢查.xlsx
+++ b/test/斷詞結果檢查.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pytest\NLP\final\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my program\NLP\NLP_Poker_Chinese\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87C266C4-9335-4C16-8EDF-FFFB6682AA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1982D6D8-AABB-46EB-90F8-AA95FE197462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="310">
   <si>
     <t>欄位 A (text)</t>
   </si>
@@ -33,10 +33,10 @@
     <t>clean_text</t>
   </si>
   <si>
-    <t>第一輪前先決定座位及起始發牌位置。洗牌並切牌。本次輪到擔任盲注的玩家們下盲注。為每位玩家發兩張底牌。翻牌前（preflop）喊注。</t>
-  </si>
-  <si>
-    <t>第一 輪前 先 決定 座位 及 起始 發牌 位置 洗牌 並 切牌 本次 輪到 擔任 盲注 玩家 們 下 盲注 為 每位 玩家 發兩張 底牌 翻牌前 preflop 喊注</t>
+    <t>第一輪前先決定座位及起始發牌位置。洗牌並切牌。本次輪到擔任盲注的玩家們下盲注。為每位玩家發兩張底牌。翻牌前（pre_flop）喊注。</t>
+  </si>
+  <si>
+    <t>第一 輪前 先 決定 座位 及 起始 發牌 位置 洗牌 並 切牌 本次 輪到 擔任 盲注 玩家 們 下 盲注 為 每位 玩家 發兩張 底牌 翻牌前 pre_flop 喊注</t>
   </si>
   <si>
     <t>消一張牌後發出三張公共牌。翻牌圈（flop）喊注。</t>
@@ -66,31 +66,31 @@
     <t>座位分配方式與發牌次序。一般撲克錦標賽的座位均採取隨機分配，私人遊戲多以抽牌比大小決定起始座位順序及第一個發牌者位置。抽牌選位的方法為每人發一張牌，抽到最大牌者為莊位(button)，同大小則比花色。每一輪結束後，莊家依順時針方向由玩家依序輪流擔任。</t>
   </si>
   <si>
-    <t>座位 分配 方式 發牌 次序 一般 撲克錦標賽 座位 均 採取 隨機 分配 私人 遊戲 多 以 抽牌 比 大小 決定 起始 座位 順序 及 第一 個 發牌 者 位置 抽牌 選位 方法 為 每人 發一 張牌 抽到 最大 牌者 為 莊位 ( button ) 同 大小 則比 花色 每一輪 結束 後 莊家 依 順時針 方向 由 玩家 依序 輪流 擔任</t>
-  </si>
-  <si>
-    <t>下盲注（blinds）及切牌後進行發牌。在三人桌(含)以上皆由莊位（dealer button）位置的下家(小盲注，Small Bind)開始，依順時鐘方向派發，每輪一張共兩輪。每一個參加的玩家都會得到兩張底牌。</t>
-  </si>
-  <si>
-    <t>下 盲注 blinds 及 切牌 後 進行 發牌 三人桌 ( 含 ) 以上 皆 由 莊位 dealer button 位置 下家 ( 小盲注 Small Bind ) 開始 依順 時鐘 方向 派發 每輪 一張 共 兩輪 每一個 參加 玩家 會 得到 兩張 底牌</t>
-  </si>
-  <si>
-    <t>若為兩人桌(單挑，head up)的話，由莊位為小盲、另一位為大盲，由大盲開始發牌。</t>
-  </si>
-  <si>
-    <t>若為 兩人桌 ( 單挑 head up ) 話 由 莊位 為 小盲 另 一位 為大盲 由大盲 開始 發牌</t>
-  </si>
-  <si>
-    <t>Howard Lederer於其教學DVD中建議，由玩家擔任發牌者進行發牌時，由發牌者之上上家進行洗牌，由發牌者之上家(CO位子，Cut-off)進行切牌，以降低作弊風險。</t>
-  </si>
-  <si>
-    <t>Howard Lederer 於 其 教學 DVD 中建 議 由 玩家 擔任 發牌 者 進行 發牌 時 由 發牌 者 之上 上家 進行 洗牌 由 發牌 者 之上 家 ( CO 位子 Cut - off ) 進行 切牌 以 降低 作弊 風險</t>
-  </si>
-  <si>
-    <t>標準德州撲克遊戲盲注的位置，小盲注與大盲注緊接於發牌者之後。坐在發牌人（dealer）位置的玩家，前面有按鈕（button）作標示。位於發牌人順時針方向次一位置的玩家須下小盲注（small blind），金額等於大盲注（big blind）的一半。小盲注玩家的下一家的玩家須下大盲注，金額等於最低下注額。每局以順時針方向輪流。</t>
-  </si>
-  <si>
-    <t>標準 德州撲克 遊戲 盲注 位置 小盲注 大盲注 緊接 於 發牌 者 之 後 坐在 發牌 人 dealer 位置 玩家 前面 有 按鈕 button 作標示 位 於 發牌 人 順時針 方向 次 一 位置 玩家 須下 小盲注 small blind 金額 等 於 大盲注 big blind 一半 小盲注 玩家 下 一家 玩家 須下 大盲注 金額 等 於 最低 下注 額 每局 以 順時針 方向 輪流</t>
+    <t>座位 分配 方式 發牌 次序 一般 撲克錦標賽 座位 均 採取 隨機 分配 私人 遊戲 多 抽牌 比 大小 決定 起始 座位 順序 及 第一 個 發牌者 位置 抽牌 選位 方法 為 每人 發一 張牌 抽到 最大 牌者 為 莊位 button 同 大小 則比 花色 每一輪 結束 後 莊家 依 順時針 方向 玩家 依序 輪流 擔任</t>
+  </si>
+  <si>
+    <t>下盲注（blinds）及切牌後進行發牌。在三人桌(含)以上皆由莊位（dealer_button）位置的下家(小盲注，small_blind)開始，依順時鐘方向派發，每輪一張共兩輪。每一個參加的玩家都會得到兩張底牌。</t>
+  </si>
+  <si>
+    <t>下 盲注 blinds 及 切牌 後 進行 發牌 三人桌 含 以上 皆 莊位 dealer_button 位置 下家 小盲注 small_blind 開始 依順 時鐘 方向 派發 每輪 一張 共 兩輪 每一個 參加 玩家 會 得到 兩張 底牌</t>
+  </si>
+  <si>
+    <t>若為兩人桌(單挑，heads_up)的話，由莊位為小盲、另一位為大盲，由大盲開始發牌。</t>
+  </si>
+  <si>
+    <t>若為 兩人桌 單挑 heads_up 話 莊位 為 小盲 另 一位 為大盲 由大盲 開始 發牌</t>
+  </si>
+  <si>
+    <t>由玩家擔任發牌者進行發牌時，由發牌者之上上家進行洗牌，由發牌者之上家進行切牌，以降低作弊風險。</t>
+  </si>
+  <si>
+    <t>玩家 擔任 發牌者 進行 發牌 時 發牌者 之上 上家 進行 洗牌 發牌者 之上 家 進行 切牌 降低 作弊 風險</t>
+  </si>
+  <si>
+    <t>標準德州撲克遊戲盲注的位置，小盲注與大盲注緊接於發牌者之後。坐在發牌人（dealer）位置的玩家，前面有按鈕（button）作標示。位於發牌人順時針方向次一位置的玩家須下小盲注（small_blind），金額等於大盲注（Big_Blind）的一半。小盲注玩家的下一家的玩家須下大盲注，金額等於最低下注額。每局以順時針方向輪流。</t>
+  </si>
+  <si>
+    <t>標準 德州撲克 遊戲 盲注 位置 小盲注 大盲注 緊接 發牌者 之 後 坐在 發牌 人 dealer 位置 玩家 前面 有 按鈕 button 作標示 位 發牌 人 順時針 方向 次 一 位置 玩家 須下 小盲注 small_blind 金額 等於 大盲注 big_blind 一半 小盲注 玩家 下 一家 玩家 須下 大盲注 金額 等於 最低 下注 額 每局 順時針 方向 輪流</t>
   </si>
   <si>
     <t>在撲克比賽中，盲注/底注（ante）的金額會隨時間逐漸提高。有時大小盲注有不同比例，例如大小盲注分別為15元和10元也十分正常。</t>
@@ -99,250 +99,259 @@
     <t>撲克 比賽 中 盲注 底注 ante 金額會 隨時間 逐漸 提高 有時 大 小盲注 有 不同 比例 例如 大 小盲注 分別 為 15 元 和 10 元 十分 正常</t>
   </si>
   <si>
-    <t>如只剩兩名玩家，「一對一」（heads-up）特別規則會生效。在這個情況下，莊位下小盲注，而他的對手須下大盲注。第一輪由莊位先叫注，翻牌後的各輪皆由大盲注先行叫注。</t>
-  </si>
-  <si>
-    <t>如 只 剩 兩名 玩家 一對 一 heads - up 特別 規則 會 生效 這個 情況 下 莊位 下 小盲注 他 對手 須下 大盲注 第一 輪 由 莊位 先 叫注 翻牌後 各輪 皆 由 大盲注 先行 叫注</t>
-  </si>
-  <si>
-    <t>德州撲克最常見的三個變種為限注（limit）、無限注（no-limit）和彩池限注（pot-limit）。</t>
-  </si>
-  <si>
-    <t>德州撲克 最常見 三個 變種 為 限注 limit 無限注 no - limit 和 彩池限注 pot - limit</t>
-  </si>
-  <si>
-    <t>最低加注(min-raise)金額限制：在翻牌前(pre-flop)想第一位加注的玩家需至少為大盲的兩倍。其餘時候若該圈尚未有玩家加注，則想加注的玩家需大於大盲注。若該圈有兩位以上玩家加注或下注(bet)，則需至少大於或等於該圈最後一個下注玩家的金額，加上最後兩個下注玩家的差額。若該圈只有一位玩家下注，則需大於下注玩家的兩倍。</t>
-  </si>
-  <si>
-    <t>最低 加注 ( min - raise ) 金額 限制 翻牌前 ( pre - flop ) 想 第一位 加注 玩家 需 至少 為大盲 兩倍 其餘 時候 若 該 圈 尚未 有 玩家 加注 則想 加注 玩家 需大 於 大盲注 若該 圈 有 兩位 以上 玩家 加注 或 下注 ( bet ) 則需 至少 大 於 或 等 於 該 圈 最後一個 下注 玩家 金額 加上 最後兩個 下注 玩家 差額 若該 圈 只有 一位 玩家 下注 則需 大 於 下注 玩家 兩倍</t>
+    <t>如只剩兩名玩家，「一對一」（heads_up）特別規則會生效。在這個情況下，莊位下小盲注，而他的對手須下大盲注。第一輪由莊位先叫注，翻牌後的各輪皆由大盲注先行叫注。</t>
+  </si>
+  <si>
+    <t>如 只 剩 兩名 玩家 一對 一 heads_up 特別 規則 會 生效 這個 情況 下 莊位 下 小盲注 他 對手 須下 大盲注 第一 輪 莊位 先 叫注 翻牌後 各輪 皆 大盲注 先行 叫注</t>
+  </si>
+  <si>
+    <t>德州撲克最常見的三個變種為限注（limit）、無限注（no_limit）和彩池限注（pot_limit）。</t>
+  </si>
+  <si>
+    <t>最低加注(min_raise)金額限制：在翻牌前(Pre_flop)想第一位加注的玩家需至少為大盲的兩倍。其餘時候若該圈尚未有玩家加注，則想加注的玩家需大於大盲注。若該圈有兩位以上玩家加注或下注(bet)，則需至少大於或等於該圈最後一個下注玩家的金額，加上最後兩個下注玩家的差額。若該圈只有一位玩家下注，則需大於下注玩家的兩倍。</t>
+  </si>
+  <si>
+    <t>最低 加注 min_raise 金額 限制 翻牌前 pre_flop 想 第一位 加注 玩家 需 至少 為大盲 兩倍 其餘 時候 若 該 圈 尚未 有 玩家 加注 則想 加注 玩家 需 大於 大盲注 若該 圈 有 兩位 以上 玩家 加注 或 下注 bet 則需 至少 大於 或 等於 該圈 最後一個 下注 玩家 金額 加上 最後兩個 下注 玩家 差額 若該 圈 只有 一位 玩家 下注 則需 大於 下注 玩家 兩倍</t>
   </si>
   <si>
     <t>德州撲克的基礎行動選項：蓋牌（Fold）與過牌（Check）。蓋牌指玩家放棄繼續這局牌，將底牌交還給發牌者，並失去已投入彩池的籌碼。過牌指在當前下注圈尚未有任何人下注的情況下，玩家選擇不投入籌碼，並將行動權順時針交給下一位玩家。</t>
   </si>
   <si>
-    <t>德州撲克 基礎 行動 選項 蓋牌 Fold 過牌 Check 蓋牌 指 玩家 放棄 繼續 這局 牌 將 底牌 交還給 發牌 者 並 失去 已 投入 彩池 籌碼 過牌 指在 當前 下注圈 尚未 有 任何人 下注 情況 下 玩家 選擇 不 投入 籌碼 並將 行動 權 順時針 交給 下 一位 玩家</t>
+    <t>德州撲克 基礎 行動 選項 蓋牌 fold 過牌 check 蓋牌 指 玩家 放棄 繼續 這局 牌 將 底牌 交還給 發牌者 並 失去 已 投入 彩池 籌碼 過牌 指在 當前 下注圈 尚未 有 任何人 下注 情況 下 玩家 選擇 不 投入 籌碼 並將 行動 權 順時針 交給 下 一位 玩家</t>
   </si>
   <si>
     <t>德州撲克的基礎行動選項：跟注（Call）與加注（Raise）。跟注指玩家投入與當前最高下注額相等的籌碼，以獲得繼續參與遊戲的權利。加注指玩家在當前最高下注額的基礎上，進一步提高下注金額，迫使後面的玩家必須跟進更高的金額才能繼續遊戲。</t>
   </si>
   <si>
-    <t>德州撲克 基礎 行動 選項 跟注 Call 加注 Raise 跟注 指 玩家 投入 當前 最高 下注 額 相等 籌碼 以 獲得 繼續 參與 遊戲 權利 加注 指 玩家 當前 最高 下注 額 基礎 上 進 一步 提高 下注 金額 迫使 後 面 玩家 必須 跟 進 更 高 金額 才能 繼續 遊戲</t>
-  </si>
-  <si>
-    <t>All-in後未達最低加注額時的限制：若玩家所餘籌碼All-in後仍低於最低加注金額，則此注僅視為跟注（call）而不能被當成加注（raise）。在該圈若未有其他人再加注的情況下，原先已經行動過的加注者僅可選擇跟注補齊或蓋牌，於此圈不可再行加注。</t>
-  </si>
-  <si>
-    <t>All - in 後 未 達 最低 加注 額時 限制 若 玩家 所餘籌碼 All - in 後 仍 低 於 最低 加注 金額 則此 注僅視 為 跟注 call 不能 當成 加注 raise 該 圈 若 未有 其他人 再 加注 情況 下 原先 已經 行動 過的 加注 者 僅可選擇 跟注 補齊 或 蓋牌 於 此圈 不可 再行 加注</t>
-  </si>
-  <si>
-    <t>All-in後未達最低加注額的特殊變種規則：依少部份賭場規定，若All-in的籌碼量大於最低加注額的一半以上，原加注者即可重新加注。或是規定當連續多個All-in累積的籌碼量，加總已經超過了最小加注額後，原加注者即可重新加注。</t>
-  </si>
-  <si>
-    <t>All - in 後 未 達 最低 加注 額 特殊 變種 規則 依少 部份 賭場 規定 若 All - in 籌碼量 大 於 最低 加注 額 一半 以上 原 加注 者 即可 重新 加注 或是 規定 當連續 多個 All - in 累積 籌碼量 加總 已經 超過 最小 加注 額 後 原 加注 者 即可 重新 加注</t>
-  </si>
-  <si>
-    <t>攤牌(Show down)方式：如有兩名以上的玩家在最後一輪下注結束時仍未蓋牌，則須進行攤牌。每名玩家以自己的兩張底牌，加上桌面五張公共牌，共七張牌中，取最大的五張牌組合決定勝負。當中可包括兩張或一張底牌，甚至只有公共牌，其餘的兩張不列入比較範圍。若一名玩家加注而其他所有玩家均蓋牌，則無需開牌即可贏得彩池。</t>
-  </si>
-  <si>
-    <t>攤牌 ( Show down ) 方式 如有 兩名 以上 玩家 最後一輪 下注 結束 時 仍 未蓋牌 則須 進行 攤牌 每名 玩家 以 自己 兩張 底牌 加上 桌面 五張 公共牌 共七 張牌 中 取 最大 五 張牌 組合 決定 勝負 當中 可 包括 兩張 或 一張 底牌 甚至 只有 公共牌 其餘 兩張 不 列入 比較 範圍 若 一名 玩家 加注 其他 所有 玩家 均 蓋牌 則無需 開牌 即可 贏得 彩池</t>
-  </si>
-  <si>
-    <t>最佳手牌（nut hand）：某五張公用牌翻開後，可判定該局能夠組成的最大可能牌型，即為該局的最佳手牌。</t>
-  </si>
-  <si>
-    <t>最佳手牌 nut hand 某五張 公用 牌 翻開 後 可 判定 該局 能夠 組成 最大 可能 牌型 即為 該局 最佳手牌</t>
+    <t>德州撲克 基礎 行動 選項 跟注 call 加注 raise 跟注 指 玩家 投入 當前 最高 下注 額 相等 籌碼 獲得 繼續 參與 遊戲 權利 加注 指 玩家 當前 最高 下注 額 基礎 上 進 一步 提高 下注 金額 迫使 後 面 玩家 必須 跟 進 更 高 金額 才能 繼續 遊戲</t>
+  </si>
+  <si>
+    <t>all_in後未達最低加注額時的限制：若玩家所餘籌碼all_in後仍低於最低加注金額，則此注僅視為跟注（call）而不能被當成加注（raise）。在該圈若未有其他人再加注的情況下，原先已經行動過的加注者僅可選擇跟注補齊或蓋牌，於此圈不可再行加注。</t>
+  </si>
+  <si>
+    <t>all_in 後 未 達 最低 加注 額時 限制 若 玩家 所餘籌碼 all_in 後 仍 低 最低 加注 金額 則此 注僅視 為 跟注 call 不能 當成 加注 raise 該 圈 若 未有 其他人 再 加注 情況 下 原先 已經 行動 過的 加注者 僅可選擇 跟注 補齊 或 蓋牌 此圈 不可 再行 加注</t>
+  </si>
+  <si>
+    <t>all_in後未達最低加注額的特殊變種規則：依少部份賭場規定，若all_in的籌碼量大於最低加注額的一半以上，原加注者即可重新加注。或是規定當連續多個all_in累積的籌碼量，加總已經超過了最小加注額後，原加注者即可重新加注。</t>
+  </si>
+  <si>
+    <t>all_in 後 未 達 最低 加注 額 特殊 變種 規則 依少 部份 賭場 規定 若 all_in 籌碼量 大於 最低 加注 額 一半 以上 原 加注者 即可 重新 加注 或是 規定 當連續 多個 all_in 累積 籌碼量 加總 已經 超過 最小 加注 額 後 原 加注者 即可 重新 加注</t>
+  </si>
+  <si>
+    <t>攤牌(show_down)方式：如有兩名以上的玩家在最後一輪下注結束時仍未蓋牌，則須進行攤牌。每名玩家以自己的兩張底牌，加上桌面五張公共牌，共七張牌中，取最大的五張牌組合決定勝負。當中可包括兩張或一張底牌，甚至只有公共牌，其餘的兩張不列入比較範圍。若一名玩家加注而其他所有玩家均蓋牌，則無需開牌即可贏得彩池。</t>
+  </si>
+  <si>
+    <t>攤牌 show_down 方式 如有 兩名 以上 玩家 最後一輪 下注 結束 時 仍 未蓋牌 則須 進行 攤牌 每名 玩家 自己 兩張 底牌 加上 桌面 五張 公共牌 共七 張牌 中 取 最大 五 張牌 組合 決定 勝負 當中 可 包括 兩張 或 一張 底牌 甚至 只有 公共牌 其餘 兩張 不 列入 比較 範圍 若 一名 玩家 加注 其他 所有 玩家 均 蓋牌 則無需 開牌 即可 贏得 彩池</t>
+  </si>
+  <si>
+    <t>最佳手牌（nut_hand）：某五張公用牌翻開後，可判定該局能夠組成的最大可能牌型，即為該局的最佳手牌。</t>
+  </si>
+  <si>
+    <t>最佳手牌 nut_hand 某五張 公用 牌 翻開 後 可 判定 該局 能夠 組成 最大 可能 牌型 即為 該局 最佳手牌</t>
   </si>
   <si>
     <t>攤牌平手與次大牌（kicker）規則：如多於一名玩家擁有最大的手牌，彩池由他們平等均分，不能平分的零頭由發牌者順時針方向尚未蓋牌的第一個玩家獲得。若玩家牌型大小相若，須以次大牌（kicker）決定勝負，若次大牌相同則依序比到使用的五張為止。攤牌時只計算數字大小，花色在德州撲克中無分大小。</t>
   </si>
   <si>
-    <t>攤牌 平手 次大牌 kicker 規則 如多 於 一名 玩家 擁有 最大 手牌 彩池 由 他們 平等 均分 不能 平分 零頭 由 發牌 者 順時針 方向 尚未 蓋牌 第一 個 玩家 獲得 若 玩家 牌型 大小 相若 須以 次大牌 kicker 決定 勝負 若 次大牌 相同 則 依序 比 到 使用 五張 為止 攤牌 時 只 計算 數字 大小 花色 德州撲克 中無分 大小</t>
-  </si>
-  <si>
-    <t>開牌次序與自行蓋牌（muck）：通常未蓋牌玩家可依序自行決定是否開牌。開牌順序為最後一圈的最後加注者為第一開牌者；若全數All-in，由第一個All-in玩家先開；若無人加注，以按鈕位置順時針第一家未蓋牌者先開。決定開牌需兩張底牌全翻，玩家亦可選擇不開牌直接放棄，稱為muck。</t>
-  </si>
-  <si>
-    <t>開牌 次序 自行 蓋牌 muck 通常 未蓋牌 玩家 可 依序 自行 決定 是否 開牌 開牌 順序 為 最 後 一圈 最 後 加注 者 為 第一 開牌 者 若 全數 All - in 由 第一 個 All - in 玩家 先開 若無人 加注 以 按鈕位 置 順時針 第一家 未蓋 牌者 先開 決定 開牌 需 兩張 底牌 全翻 玩家 亦可 選擇 不 開牌 直接 放棄 稱為 muck</t>
-  </si>
-  <si>
-    <t>主彩池(Main pot)分配規則：當沒有玩家全押(all-in)時，彩池由最後一輪下注結束時，未蓋牌的玩家中牌型最大的者獨得。</t>
-  </si>
-  <si>
-    <t>主彩池 ( Main pot ) 分配 規則 當沒有 玩家 全押 ( all - in ) 時 彩池 由 最後一輪 下注 結束 時 未蓋牌 玩家 中 牌型 最大 者 獨得</t>
-  </si>
-  <si>
-    <t>邊池(Side pot)形成與分配規則：當有一或多個玩家全押時，超過全押玩家押注金額的部份將會形成一或多個邊池。已全押之玩家無法贏取全押後形成之彩池，最多只能自其他跟牌之玩家處，取得相當於本身全押之總籌碼數。各個邊池由參與該邊池投注中，持有最大牌面的玩家贏得。</t>
-  </si>
-  <si>
-    <t>邊池 ( Side pot ) 形成 分配 規則 當有 一 或 多個 玩家 全押 時 超過 全押 玩家 押注 金額 部份 將會 形成 一 或 多個 邊池 已 全押 之 玩家 無法 贏取 全押 後 形成 之彩池 最 多 只能 自 其他 跟牌 之 玩家 處 取得 相當 於 本身 全押 之 總籌 碼數 各個 邊池 由 參 該 邊池 投注 中 持有 最大 牌面 玩家 贏得</t>
+    <t>攤牌 平手 次大牌 kicker 規則 如多 一名 玩家 擁有 最大 手牌 彩池 他們 平等 均分 不能 平分 零頭 發牌者 順時針 方向 尚未 蓋牌 第一 個 玩家 獲得 若 玩家 牌型 大小 相若 須以 次大牌 kicker 決定 勝負 若 次大牌 相同 則 依序 比 到 使用 五張 為止 攤牌 時 只 計算 數字 大小 花色 德州撲克 中無分 大小</t>
+  </si>
+  <si>
+    <t>開牌次序與自行蓋牌（muck）：通常未蓋牌玩家可依序自行決定是否開牌。開牌順序為最後一圈的最後加注者為第一開牌者；若全數all_in，由第一個all_in玩家先開；若無人加注，以按鈕位置順時針第一家未蓋牌者先開。決定開牌需兩張底牌全翻，玩家亦可選擇不開牌直接放棄，稱為muck。</t>
+  </si>
+  <si>
+    <t>開牌 次序 自行 蓋牌 muck 通常 未蓋牌 玩家 可 依序 自行 決定 是否 開牌 開牌 順序 為 最 後 一圈 最 後 加注者 為 第一 開牌 者 若 全數 all_in 第一 個 all_in 玩家 先開 若無人 加注 按鈕位 置 順時針 第一家 未蓋 牌者 先開 決定 開牌 需 兩張 底牌 全翻 玩家 亦可 選擇 不 開牌 直接 放棄 稱為 muck</t>
+  </si>
+  <si>
+    <t>主彩池(main_pot)分配規則：當沒有玩家全押(all_in)時，彩池由最後一輪下注結束時，未蓋牌的玩家中牌型最大的者獨得。</t>
+  </si>
+  <si>
+    <t>主彩池 main_pot 分配 規則 當沒有 玩家 全押 all_in 時 彩池 最後一輪 下注 結束 時 未蓋牌 玩家 中 牌型 最大 者 獨得</t>
+  </si>
+  <si>
+    <t>邊池(side_pot)形成與分配規則：當有一或多個玩家全押時，超過全押玩家押注金額的部份將會形成一或多個邊池。已全押之玩家無法贏取全押後形成之彩池，最多只能自其他跟牌之玩家處，取得相當於本身全押之總籌碼數。各個邊池由參與該邊池投注中，持有最大牌面的玩家贏得。</t>
+  </si>
+  <si>
+    <t>邊池 side_pot 形成 分配 規則 當有 一 或 多個 玩家 全押 時 超過 全押 玩家 押注 金額 部份 將會 形成 一 或 多個 邊池 已 全押 之 玩家 無法 贏取 全押 後 形成 之彩池 最 多 只能 自 其他 跟牌 之 玩家 處 取得 相當 本身 全押 之 總籌 碼數 各個 邊池 參 該 邊池 投注 中 持有 最大 牌面 玩家 贏得</t>
   </si>
   <si>
     <t>無人跟注的邊池處理：無人跟注的邊池（僅有一位玩家下注，剩下其他玩家都蓋牌）將會由該下注玩家直接贏得，形同退還下注於該邊池之籌碼。</t>
   </si>
   <si>
-    <t>無人 跟注 邊池 處理 無人 跟注 邊池 僅有 一位 玩家 下注 剩下 其他 玩家 蓋牌 將會 由 該 下注 玩家 直接 贏得 形同 退還 下注 於 該 邊池 之 籌碼</t>
+    <t>無人 跟注 邊池 處理 無人 跟注 邊池 僅有 一位 玩家 下注 剩下 其他 玩家 蓋牌 將會 該 下注 玩家 直接 贏得 形同 退還 下注 該 邊池 之 籌碼</t>
   </si>
   <si>
     <t>彩池無法均分時的小額籌碼分配：當彩池由兩個以上玩家平分時，若有無法平分之小額籌碼（零頭），將由順時鐘方向算過去，最靠近發牌者(Dealer)的贏家取得。</t>
   </si>
   <si>
-    <t>彩池 無法 均分 時 小額 籌碼 分配 當彩池 由 兩個 以上 玩家 平分 時 若有 無法 平分 之小額 籌碼 零頭 將由順 時鐘 方向 算過 去 最靠近 發牌 者 ( Dealer ) 贏家 取得</t>
-  </si>
-  <si>
-    <t>牌型大小通用規則：德州撲克的牌型大小不分花色，有可能平手，從大到小比牌。若五張比完大小相同，則均分彩池內的籌碼。一般大小依序為：皇家同花順 &gt; 同花順 &gt; 四條（鐵支） &gt; 葫蘆 &gt; 同花 &gt; 順子 &gt; 三條 &gt; 兩對 &gt; 對子 &gt; 散牌（烏龍）。</t>
-  </si>
-  <si>
-    <t>牌型 大小 通用 規則 德州撲克 牌型 大小 不 分 花色 有 可能 平手 從大到 小比牌 若五張 比 完 大小 相同 則 均分 彩池 內 籌碼 一般 大小 依序 為 皇家同花順 同花順 四條 鐵支 葫蘆 同花 順子 三條 兩對 對子 散牌 烏龍</t>
-  </si>
-  <si>
-    <t>皇家同花順（Royal Straight Flush）與同花順（Straight Flush）：同花順為五張同花色的連續數字牌，數字最大者為贏家。皇家同花順為最大的同花順，由同花色的A、K、Q、J和10組成。若公牌開出最大同花順，則未蓋牌玩家平分籌碼。</t>
-  </si>
-  <si>
-    <t>皇家同花順 Royal Straight Flush 同花順 Straight Flush 同花順 為 五 張同 花色 連續 數字 牌 數字 最大者 為 贏家 皇家同花順 為 最大 同花順 由同 花色 A K Q J 和 10 組成 若公牌 開出 最大 同花順 則未蓋牌 玩家 平分 籌碼</t>
-  </si>
-  <si>
-    <t>四條（鐵支，Four of a kind）：其中四張是相同數字的牌，第五張是剩下牌組中最大的一張牌。若有一家以上持有四條，則比較第五張起腳牌（kicker），最大者為贏家；若第五張也相同則平分彩池。</t>
-  </si>
-  <si>
-    <t>四條 鐵支 Four of a kind 其中 四張 相同 數字 牌 第五 張是 剩下 牌組 中 最大 一 張牌 若有 一家 以上 持有 四條 則比較 第五 張起 腳牌 kicker 最大者 為 贏家 若 第五 張 相同 則 平分 彩池</t>
-  </si>
-  <si>
-    <t>葫蘆（滿堂紅，Full house）：由三張相同數字及任何兩張其他相同數字的牌組成。如果同時有多人拿到葫蘆，三張相同數字中較大者為贏家；若三張數字相同，則再比剩下兩張牌中數字較大者。</t>
-  </si>
-  <si>
-    <t>葫蘆 滿堂紅 Full house 由三張 相同 數字 及 任何 兩張 其他 相同 數字 牌 組成 如果 同時 有 多 人 拿到 葫蘆 三張 相同 數字 中較 大者 為 贏家 若三張 數字 相同 則再 比 剩下 兩張牌 中 數字 較大者</t>
+    <t>彩池 無法 均分 時 小額 籌碼 分配 當彩池 兩個 以上 玩家 平分 時 若有 無法 平分 之小額 籌碼 零頭 將由順 時鐘 方向 算過 去 最靠近 發牌者 dealer 贏家 取得</t>
+  </si>
+  <si>
+    <t>牌型大小通用規則：德州撲克的牌型大小不分花色，有可能平手，從大到小比牌。若五張比完大小相同，則均分彩池內的籌碼。一般大小依序為：皇家同花順 &gt; 同花順 &gt; 四條（鐵支） &gt; 葫蘆 &gt; 同花 &gt; 順子 &gt; 三條 &gt; 兩對 &gt; 對子 &gt; 高牌（烏龍）。</t>
+  </si>
+  <si>
+    <t>牌型 大小 通用 規則 德州撲克 牌型 大小 不 分 花色 有 可能 平手 從大到 小比牌 若五張 比 完 大小 相同 則 均分 彩池 內 籌碼 一般 大小 依序 為 皇家同花順 同花順 四條 鐵支 葫蘆 同花 順子 三條 兩對 對子 高牌 烏龍</t>
+  </si>
+  <si>
+    <t>皇家同花順（royal_straight_flush）與同花順（straight_flush）：同花順為五張同花色的連續數字牌，數字最大者為贏家。皇家同花順為最大的同花順，由同花色的A_K_Q_J_10。若公牌開出最大同花順，則未蓋牌玩家平分籌碼。</t>
+  </si>
+  <si>
+    <t>皇家同花順 royal_straight_flush 同花順 straight_flush 同花順 為 五 張同 花色 連續 數字 牌 數字 最大者 為 贏家 皇家同花順 為 最大 同花順 由同 花色 a_k_q_j_10 若公牌 開出 最大 同花順 則未蓋牌 玩家 平分 籌碼</t>
+  </si>
+  <si>
+    <t>四條（鐵支，four_of_a_kind）：其中四張是相同數字的牌，第五張是剩下牌組中最大的一張牌。若有一家以上持有四條，則比較第五張起腳牌（kicker），最大者為贏家；若第五張也相同則平分彩池。</t>
+  </si>
+  <si>
+    <t>四條 鐵支 four_of_a_kind 其中 四張 相同 數字 牌 第五 張是 剩下 牌組 中 最大 一 張牌 若有 一家 以上 持有 四條 則比較 第五 張起 腳牌 kicker 最大者 為 贏家 若 第五 張 相同 則 平分 彩池</t>
+  </si>
+  <si>
+    <t>葫蘆（滿堂紅，full_house）：由三張相同數字及任何兩張其他相同數字的牌組成。如果同時有多人拿到葫蘆，三張相同數字中較大者為贏家；若三張數字相同，則再比剩下兩張牌中數字較大者。</t>
+  </si>
+  <si>
+    <t>葫蘆 滿堂紅 full_house 由三張 相同 數字 及 任何 兩張 其他 相同 數字 牌 組成 如果 同時 有 多 人 拿到 葫蘆 三張 相同 數字 中較 大者 為 贏家 若三張 數字 相同 則再 比 剩下 兩張牌 中 數字 較大者</t>
   </si>
   <si>
     <t>同花（Flush）：由五張不按順序但相同花色的牌組成。如果不只一人有此牌組，則牌面數字最大的人贏得該局；如果最大數字相同，則依序由第二、第三、第四或者第五張牌來決定勝負。</t>
   </si>
   <si>
-    <t>同花 Flush 由五張 不 按 順序 但 相同 花色 牌 組成 如果 不 只 一人 有 此牌 組 則牌面 數字 最大 人 贏得 該局 如果 最大 數字 相同 則 依序 由 第二 第三 第四 或者 第五 張牌 來 決定 勝負</t>
-  </si>
-  <si>
-    <t>順子（Straight）：由五張連續數字的牌組成。如果不只一人有此牌組，則五張牌中數字最大的贏得此局。其中 10-J-Q-K-A 為最大的順子，A-2-3-4-5 為最小的順子。</t>
-  </si>
-  <si>
-    <t>順子 Straight 由五張 連續 數字 牌 組成 如果 不 只 一人 有 此牌 組 則五 張牌 中 數字 最大 贏得 此局 其中 10 - J - Q - K - A 為 最大 順子 A - 2 - 3 - 4 - 5 為 最小 順子</t>
-  </si>
-  <si>
-    <t>三條（Three of a kind）：由三張相同數字和兩張不同數字的雜牌組成。如果不只一人有此牌組，則三張牌中數字最大者贏得該局。若三張數字相同，則依序比較剩下的兩張雜牌。</t>
-  </si>
-  <si>
-    <t>三條 Three of a kind 由三張 相同 數字 和 兩張 不同 數字 雜牌 組成 如果 不 只 一人 有 此牌 組 則三 張牌 中 數字 最大者 贏得 該局 若三張 數字 相同 則 依序 比較 剩下 兩張 雜牌</t>
-  </si>
-  <si>
-    <t>兩對（Two pair）、對子（Pair）與散牌（高牌，High card）：兩對由兩組同數字對子加一張雜牌組成；對子由兩張同數字加三張雜牌組成；散牌為無法組成牌型的五張雜牌。比牌時皆由持有的最大對子先比，若相同則依序比較剩下的雜牌（kicker），數字大者勝。</t>
-  </si>
-  <si>
-    <t>兩對 Two pair 對子 Pair 散牌 高牌 High card 兩對 由 兩 組同 數字 對子 加一張 雜牌 組成 對子 由 兩 張同 數字 加三張 雜牌 組成 散牌 為 無法 組成 牌型 五張 雜牌 比牌 時 皆 由 持有 最大 對子 先比 若 相同 則 依序 比較 剩下 雜牌 kicker 數字 大者勝</t>
-  </si>
-  <si>
-    <t>限注式德州撲克（Limit Texas Hold'em）：下注金額是固定的。首兩輪（即翻牌前和翻牌）的下注和加注須與大盲注相同，稱為「小注」。其後兩輪（即轉牌和河牌）的下注和加注須等於大盲注的兩倍，稱為「大注」。每一個押注圈只允許最多四次動作，即一次下注與三次加注（下注、加注、再加注、最後加注），達到上限後任何人皆不能再加注。</t>
-  </si>
-  <si>
-    <t>限注式 德州撲克 Limit Texas Hold ' em 下注 金額 固定 首兩輪 即 翻牌前 和 翻牌 下注 和 加注 須與 大盲注 相同 稱為 小注 其後兩輪 即 轉牌 和 河牌 下注 和 加注 須等 於 大盲注 兩倍 稱為 大注 每一個 押注 圈 只 允許 最多 四次 動作 即 一次 下注 三次 加注 下注 加注 再 加注 最 後 加注 達到 上限 後 任何人 皆 不能 再 加注</t>
-  </si>
-  <si>
-    <t>彩池限注德州撲克（Pot-limit Texas Hold'em）：每輪下注過程中，下注金額最低須等於大盲注金額。加注額設有上限限制，玩家最大可加注與目前底池金額相等的籌碼。計算可加注的最大彩池上限時，需先包含本次自己必須跟注（call）的籌碼量。每輪加注次數並沒有限制。</t>
-  </si>
-  <si>
-    <t>彩池限注 德州撲克 Pot - limit Texas Hold ' em 每輪 下注 過程 中 下注 金額 最低 須等 於 大盲注 金額 加注 額設 有 上限 限制 玩家 最大 可 加注 目前 底池 金額 相等 籌碼 計算 可 加注 最大 彩池 上限 時 需先 包含 本次 自己 必須 跟注 call 籌碼量 每輪 加注 次數 並沒有 限制</t>
-  </si>
-  <si>
-    <t>無限注德州撲克（No-limit Texas Hold'em）：為最受歡迎的變種玩法。玩家在輪到自己下注時，可下注檯面上任何下限以上的籌碼，最大可下注當時持有的全部籌碼，即為「全押」（All-in）。下注金額最低須等於大盲注金額；若要加注，最小加注額為大盲注或該輪最後一次加注額之較大者（加注幅度至少需等於前次的加注額）。每一輪可加注的籌碼和次數均無上限。</t>
-  </si>
-  <si>
-    <t>無限注 德州撲克 No - limit Texas Hold ' em 為 最受 歡迎 變種 玩法 玩家 輪 到 自己 下注 時 可 下注 檯 面上 任何 下限 以上 籌碼 最大 可 下注 當時 持有 全部 籌碼 即為 全押 All - in 下注 金額 最低 須等 於 大盲注 金額 若 要 加注 最小 加注 額為 大盲注 或 該 輪 最 後 一次 加注 額之較 大者 加注 幅度 至少 需等 於 前次 加注 額 每一輪 可 加注 籌碼 和 次 數均 無 上限</t>
+    <t>同花 flush 由五張 不 按 順序 但 相同 花色 牌 組成 如果 不 只 一人 有 此牌 組 則牌面 數字 最大 人 贏得 該局 如果 最大 數字 相同 則 依序 第二 第三 第四 或者 第五 張牌 來 決定 勝負</t>
+  </si>
+  <si>
+    <t>順子（Straight）：由五張連續數字的牌組成。如果不只一人有此牌組，則五張牌中數字最大的贏得此局。</t>
+  </si>
+  <si>
+    <t>順子 straight 由五張 連續 數字 牌 組成 如果 不 只 一人 有 此牌 組 則五 張牌 中 數字 最大 贏得 此局</t>
+  </si>
+  <si>
+    <t>三條（Three_of_a_kind）：由三張相同數字和兩張不同數字的雜牌組成。如果不只一人有此牌組，則三張牌中數字最大者贏得該局。若三張數字相同，則依序比較剩下的兩張雜牌。</t>
+  </si>
+  <si>
+    <t>三條 three_of_a_kind 由三張 相同 數字 和 兩張 不同 數字 雜牌 組成 如果 不 只 一人 有 此牌 組 則三 張牌 中 數字 最大者 贏得 該局 若三張 數字 相同 則 依序 比較 剩下 兩張 雜牌</t>
+  </si>
+  <si>
+    <t>兩對（two_pair）、對子（Pair）與散牌（高牌，high_card）：兩對由兩組同數字對子加一張雜牌組成；對子由兩張同數字加三張雜牌組成；散牌為無法組成牌型的五張雜牌。比牌時皆由持有的最大對子先比，若相同則依序比較剩下的雜牌（kicker），數字大者勝。</t>
+  </si>
+  <si>
+    <t>兩對 two_pair 對子 pair 散牌 高牌 high _ card 兩對 兩 組同 數字 對子 加一張 雜牌 組成 對子 兩 張同 數字 加三張 雜牌 組成 散牌 為 無法 組成 牌型 五張 雜牌 比牌 時 皆 持有 最大 對子 先比 若 相同 則 依序 比較 剩下 雜牌 kicker 數字 大者勝</t>
+  </si>
+  <si>
+    <t>限注式德州撲克：下注金額是固定的。首兩輪（即翻牌前和翻牌）的下注和加注須與大盲注相同，稱為「小注」。其後兩輪（即轉牌和河牌）的下注和加注須等於大盲注的兩倍，稱為「大注」。每一個押注圈只允許最多四次動作，即一次下注與三次加注（下注、加注、再加注、最後加注），達到上限後任何人皆不能再加注。</t>
+  </si>
+  <si>
+    <t>限注式 德州撲克 下注 金額 固定 首兩輪 即 翻牌前 和 翻牌 下注 和 加注 須與 大盲注 相同 稱為 小注 其後兩輪 即 轉牌 和 河牌 下注 和 加注 須 等於 大盲注 兩倍 稱為 大注 每一個 押注 圈 只 允許 最多 四次 動作 即 一次 下注 三次 加注 下注 加注 再 加注 最 後 加注 達到 上限 後 任何人 皆 不能 再 加注</t>
+  </si>
+  <si>
+    <t>彩池限注德州撲：每輪下注過程中，下注金額最低須等於大盲注金額。加注額設有上限限制，玩家最大可加注與目前底池金額相等的籌碼。計算可加注的最大彩池上限時，需先包含本次自己必須跟注（call）的籌碼量。每輪加注次數並沒有限制。</t>
+  </si>
+  <si>
+    <t>彩池限注 德州 撲 每輪 下注 過程 中 下注 金額 最低 須 等於 大盲注 金額 加注 額設 有 上限 限制 玩家 最大 可 加注 目前 底池 金額 相等 籌碼 計算 可 加注 最大 彩池 上限 時 需先 包含 本次 自己 必須 跟注 call 籌碼量 每輪 加注 次數 並沒有 限制</t>
+  </si>
+  <si>
+    <t>無限注德州撲克：為最受歡迎的變種玩法。玩家在輪到自己下注時，可下注檯面上任何下限以上的籌碼，最大可下注當時持有的全部籌碼，即為「全押」（all_in）。下注金額最低須等於大盲注金額；若要加注，最小加注額為大盲注或該輪最後一次加注額之較大者（加注幅度至少需等於前次的加注額）。每一輪可加注的籌碼和次數均無上限。</t>
+  </si>
+  <si>
+    <t>無限注 德州撲克 為 最受 歡迎 變種 玩法 玩家 輪 到 自己 下注 時 可 下注 檯 面上 任何 下限 以上 籌碼 最大 可 下注 當時 持有 全部 籌碼 即為 全押 all_in 下注 金額 最低 須 等於 大盲注 金額 若 要 加注 最小 加注 額為 大盲注 或 該 輪 最 後 一次 加注 額之較 大者 加注 幅度 至少 需 等於 前次 加注 額 每一輪 可 加注 籌碼 和 次 數均 無 上限</t>
   </si>
   <si>
     <t>德州撲克的位置策略：位置往往比牌力更關鍵，行動越晚資訊越多。SB與BB（盲注位）翻牌後最先行動，資訊最少，應打得更保守。UTG與MP（前中位）起手牌範圍要嚴格，避免邊緣牌。CO與BTN（後位）可以主動偷盲、控制底池。同一手牌在後位是賺錢牌，在前位可能是陷阱。</t>
   </si>
   <si>
-    <t>德州撲克 位置 策略 位置 往往 比牌力 更 關鍵 行動 越晚 資訊越 多 SB BB 盲注位 翻牌後 最先 行動 資訊 最少 應打 得 更 保守 UTG MP 前中位 起手 牌範圍 要 嚴格 避免 邊緣牌 CO BTN 後位 可以 主動 偷盲 控制 底池 同一 手牌 後位 賺 錢牌 前位 可能 陷阱</t>
-  </si>
-  <si>
-    <t>起手牌選擇範圍：早位應以強牌（如AA至TT對子、AK、AQs）為主；中位可加入AQo、KQs及中等對子；後位可放寬到ATo以上、同花連張及小對子來偷盲或看翻牌。同花牌價值通常大於雜色牌，因為帶有順子、同花與阻斷牌的操作潛力。</t>
-  </si>
-  <si>
-    <t>起手牌 選擇 範圍 早位 應以 強牌 如 AA 至 TT 對子 AK AQs 為主 中位 可 加入 AQo KQs 及 中等 對子 後位 可放 寬 到 ATo 以上 同花 連張 及 小 對子 來 偷 盲 或 看 翻牌 同花 牌價值 通常 大 於 雜色牌 因為 帶 有 順子 同花 阻斷 牌 操作 潛力</t>
-  </si>
-  <si>
-    <t>翻牌後數學與2與4法則：Pot Odds（底池賠率）公式為「要跟的籌碼 ÷（底池＋要跟）」。快速估算聽牌成功率可使用「2與4法則」：剩一張牌可看時，成功率約為 outs（出路）乘上 2%；剩兩張牌可看時，約為 outs 乘上 4%。若計算出的聽牌成功率大於或等於 Pot Odds，跟注通常是正期望值（EV+）。</t>
-  </si>
-  <si>
-    <t>翻牌後 數學 2 4 法則 Pot Odds 底池 賠率 公式 為 要 跟 籌碼 ÷ 底池 ＋ 要 跟 快速 估算 聽牌 成功率 可 使用 2 4 法則 剩一 張牌 可 看時 成功率 約 為 outs 出路 乘 上 2% 剩兩 張牌 可 看時 約 為 outs 乘 上 4% 若計算出 聽牌 成功率 大 於 或 等 於 Pot Odds 跟注 通常 正 期望值 EV +</t>
-  </si>
-  <si>
-    <t>常見聽牌機率與賠率：同花聽牌（Flush Draw）有9張outs，翻牌到河牌成功率約35%，賠率約1.9比1。開口順子聽牌（OESD）有8張outs，成功率約31.5%，賠率約2.1比1。內聽順子（Gutshot）有4張outs，成功率約16.5%，賠率約5比1。</t>
-  </si>
-  <si>
-    <t>常見 聽牌 機率 賠率 同花 聽牌 Flush Draw 有 9 張 outs 翻牌 到 河牌 成功率 約 35% 賠率 約 1.9 比 1 開口 順子 聽牌 OESD 有 8 張 outs 成功率 約 31.5% 賠率 約 2.1 比 1 內 聽 順子 Gutshot 有 4 張 outs 成功率 約 16.5% 賠率 約 5 比 1</t>
-  </si>
-  <si>
-    <t>遊戲人數與牌局組成：德州撲克一般支援 2 到 10 名玩家，現金局（Cash Game）通常以 6 到 9 人最為普遍。遊戲中每位玩家會獲發 2 張隱藏的「手牌（Hole cards）」。桌面會發出 5 張所有人共用的「公共牌（Community cards）」，分為前三張的「翻牌（Flop）」、第四張的「轉牌（Turn）」與第五張的「河牌（River）」。</t>
-  </si>
-  <si>
-    <t>遊戲 人數 牌局 組成 德州撲克 一般 支援 2 到 10 名 玩家 現金局 Cash Game 通常 以 6 到 9 人 最 為 普遍 遊戲 中 每位 玩家 會 獲發 2 張隱藏 手牌 Hole cards 桌面 會 發出 5 張 所有人 共用 公共牌 Community cards 分為 前三張 翻牌 Flop 第四 張 轉牌 Turn 第五 張 河牌 River</t>
-  </si>
-  <si>
-    <t>最佳五張牌組合與打公牌（Play the board）：玩家需從手裡的 2 張手牌，加上桌面的 5 張公共牌，共 7 張牌中選出任意 5 張，做出最大的牌型組合。這 5 張牌可以是手裡 2 張加桌面 3 張，或是手裡 1 張加桌面 4 張；若桌面 5 張公共牌已是最大組合，也可以完全不使用手牌，稱為「打公牌（Play the board）」。</t>
-  </si>
-  <si>
-    <t>最佳 五張牌 組合 打公牌 Play the board 玩家 需從 手裡 2 張手牌 加上 桌面 5 張 公共牌 共 7 張牌 中選出 任意 5 張 做出 最大 牌型 組合 這 5 張牌 可以 手裡 2 張加 桌面 3 張 或是 手裡 1 張加 桌面 4 張 若 桌面 5 張 公共牌 已 最大 組合 可以 完全 不 使用 手牌 稱為 打公牌 Play the board</t>
-  </si>
-  <si>
-    <t>盲注與發牌順序：發牌前，小盲位（Small Blind, SB）與大盲位（Big Blind, BB）玩家必須強制支付盲注籌碼。發牌時由小盲位開始，接著是大盲、槍口位（Under the Gun, UTG），依順時針方向輪流，最後發給莊家按鈕位（Button）。每位玩家共會獲發兩張手牌。</t>
-  </si>
-  <si>
-    <t>盲注 發牌 順序 發牌 前 小盲位 Small Blind , SB 大盲位 Big Blind , BB 玩家 必須 強制 支付 盲注 籌碼 發牌 時 由 小盲位 開始 接著 大盲 槍口位 Under the Gun , UTG 依 順時針 方向 輪流 最後發給 莊家 按鈕位 Button 每位 玩家 共會 獲發 兩張 手牌</t>
-  </si>
-  <si>
-    <t>翻牌前後行動順序與選項：翻牌前（Pre-flop）因為盲注已下注，由大盲注左側的槍口位（UTG）第一個行動，可選擇棄牌（Fold）、跟注（Call）或加注（Raise）。翻牌後（Post-flop）則由小盲位開始行動；若該下注圈尚未有人下注，玩家多出「過牌（Check）」的選擇。若前方已經有人下注或加注，則後方玩家不能選擇過牌。</t>
-  </si>
-  <si>
-    <t>翻牌前 後 行動 順序 選項 翻牌前 Pre - flop 因為 盲注 已 下注 由 大盲注 左側 槍口位 UTG 第一 個 行動 可選擇 棄牌 Fold 跟注 Call 或 加注 Raise 翻牌後 Post - flop 則由 小盲位 開始 行動 若該 下注圈 尚未 有人 下注 玩家 多出 過牌 Check 選擇 若 前方 已經 有人 下注 或 加注 則後方 玩家 不能 選擇 過牌</t>
-  </si>
-  <si>
-    <t>下注圈結束的標誌：每一輪下注（Betting round）結束的標誌是，所有決定繼續參與該局的玩家，最終都投入了一樣多的籌碼於彩池中。如果玩家不想再投入與其他人同等的籌碼，就必須選擇棄牌（Fold）。</t>
-  </si>
-  <si>
-    <t>下注圈 結束 標誌 每一輪 下注 Betting round 結束 標誌 所有 決定 繼續 參與 該局 玩家 最終 投入 一樣 多 籌碼 於 彩池 中 如果 玩家 不想 再 投入 其他人 同等 籌碼 必須 選擇 棄牌 Fold</t>
-  </si>
-  <si>
-    <t>銷牌（Burn card）規則：在發出任何公共牌（翻牌、轉牌、河牌）之前，發牌員都必須先「銷牌（Burn）」，即捨棄牌堆頂端的第一張牌（不予使用）。銷牌後才發出公共牌（翻牌發 3 張，轉牌與河牌各發 1 張），此機制的目的是為了防止作弊或作號。</t>
-  </si>
-  <si>
-    <t>銷牌 Burn card 規則 發出 任何 公共牌 翻牌 轉牌 河牌 之前 發牌員 必須 先 銷牌 Burn 即 捨 棄牌 堆頂 端的 第一 張牌 不予 使用 銷牌 後 才 發出 公共牌 翻牌 發 3 張 轉牌 河牌 各發 1 張 此機制 目的 為 防止 作弊 或 作號</t>
+    <t>德州撲克 位置 策略 位置 往往 比牌力 更 關鍵 行動 越晚 資訊越 多 sb bb 盲注位 翻牌後 最先 行動 資訊 最少 應打 得 更 保守 utg mp 前中位 起手 牌範圍 要 嚴格 避免 邊緣牌 co btn 後位 可以 主動 偷盲 控制 底池 同一 手牌 後位 賺 錢牌 前位 可能 陷阱</t>
+  </si>
+  <si>
+    <t>起手牌選擇範圍：早位應以強牌為主；中位可加入AQo、KQs及中等對子；後位可放寬、同花連張及小對子來偷盲或看翻牌。同花牌價值通常大於雜色牌，因為帶有順子、同花與阻斷牌的操作潛力。</t>
+  </si>
+  <si>
+    <t>起手牌 選擇 範圍 早位 應以 強牌 為 主 中位 可 加入 aqo kqs 及 中等對子 後位 可放 寬 同花 連張 及 小對子 來 偷 盲 或 看 翻牌 同花 牌價值 通常 大於 雜色牌 因為 帶 有 順子 同花 阻斷 牌 操作 潛力</t>
+  </si>
+  <si>
+    <t>outs，有一或多張牌可以把你的牌型變成一手贏牌的牌型</t>
+  </si>
+  <si>
+    <t>outs 有 一 或 多 張牌 可以 把 你 牌型 變成 一手 贏牌 牌型</t>
+  </si>
+  <si>
+    <t>二與四法則是一種快速估算聽牌成功機率的實用技巧。玩家可以評估能幫助自己湊成強牌的出路（outs）數量，並根據剩餘未發出的公共牌數量按比例放大，藉此在牌桌上迅速心算出聽牌勝率。</t>
+  </si>
+  <si>
+    <t>二 四法則 一種 快速 估算 聽牌 成功 機率 實用 技巧 玩家 可以 評估 能 幫助 自己 湊成 強牌 出路 outs 數量 並根據 剩餘未 發出 公共牌 數量 按 比例 放大 藉此 牌 桌上 迅速 心算 出聽牌 勝率</t>
+  </si>
+  <si>
+    <t>底池賠率（pot_odds）是德州撲克中評估投資報酬率的重要數學指標。它的核心概念是比較玩家「必須跟注的成本」與「最終可能贏得的總獎金」之間的比例，藉此衡量跟注是否划算。</t>
+  </si>
+  <si>
+    <t>底池 賠率 pot_odds 德州撲克 中 評估 投資 報酬 率 重要 數學 指標 它 核心 概念 比 較 玩家 必須 跟注 成本 最終 可能 贏得 總獎 金 之間 比例 藉此 衡量 跟注 是否 划算</t>
+  </si>
+  <si>
+    <t>在進行跟注決策時，玩家應比較聽牌成功率與底池賠率。當估算出的勝率優於賠率時，代表這個跟注動作長期下來具有正向的期望值，屬於能穩定獲利的有利決策。</t>
+  </si>
+  <si>
+    <t>進行 跟注 決策 時 玩家 應比較 聽牌 成功率 底池 賠率 當 估算 出 勝率 優 賠率 時 代表 這個 跟注 動作長 期下 來 具有 正向 期望值 屬於能 穩定 獲利 有利 決策</t>
+  </si>
+  <si>
+    <t>常見聽牌機率與賠率：同花聽牌（flush_draw）有9張outs，翻牌到河牌成功率相對高，賠率約1.9比1。開口順子聽牌（OESD）有8張outs，成功率相對高，賠率約2.1比1。內聽順子（Gutshot）有4張outs，成功率約中等，賠率約5比1。</t>
+  </si>
+  <si>
+    <t>常見 聽牌 機率 賠率 同花 聽牌 flush_draw 有 9 張 outs 翻牌 到 河牌 成功率 相對 高 賠率 約 1.9 比 1 開口 順子 聽牌 oesd 有 8 張 outs 成功率 相對 高 賠率 約 2.1 比 1 內 聽 順子 gutshot 有 4 張 outs 成功率 約 中等 賠率 約 5 比 1</t>
+  </si>
+  <si>
+    <t>遊戲人數與牌局組成：德州撲克一般支援 2 到 10 名玩家，現金局（cash_game）通常以 6 到 9 人最為普遍。遊戲中每位玩家會獲發 2 張隱藏的「手牌（hole_cards）」。桌面會發出 5 張所有人共用的「公共牌（Community_cards）」，分為前三張的「翻牌（Flop）」、第四張的「轉牌（Turn）」與第五張的「河牌（River）」。</t>
+  </si>
+  <si>
+    <t>遊戲 人數 牌局 組成 德州撲克 一般 支援 2 到 10 名 玩家 現金局 cash_game 通常 6 到 9 人 最 為 普遍 遊戲 中 每位 玩家 會 獲發 2 張隱藏 手牌 hole_cards 桌面 會 發出 5 張 所有人 共用 公共牌 community_cards 分為 前三張 翻牌 flop 第四 張 轉牌 turn 第五 張 河牌 river</t>
+  </si>
+  <si>
+    <t>最佳五張牌組合與打公牌（Play_the_board）：玩家需從手裡的 2 張手牌，加上桌面的 5 張公共牌，共 7 張牌中選出任意 5 張，做出最大的牌型組合。這 5 張牌可以是手裡 2 張加桌面 3 張，或是手裡 1 張加桌面 4 張；若桌面 5 張公共牌已是最大組合，也可以完全不使用手牌，稱為「打公牌（Play_the_board）」。</t>
+  </si>
+  <si>
+    <t>盲注與發牌順序：發牌前，小盲位（small_blind, SB）與大盲位（Big_Blind, BB）玩家必須強制支付盲注籌碼。發牌時由小盲位開始，接著是大盲、槍口位（Under_the_Gun, UTG），依順時針方向輪流，最後發給莊家按鈕位（Button）。每位玩家共會獲發兩張手牌。</t>
+  </si>
+  <si>
+    <t>盲注 發牌 順序 發牌 前 小盲位 small_blind , sb 大盲位 big_blind , bb 玩家 必須 強制 支付 盲注 籌碼 發牌 時 小盲位 開始 接著 大盲 槍口位 under_the_gun , utg 依 順時針 方向 輪流 最後發給 莊家 按鈕位 button 每位 玩家 共會 獲發 兩張 手牌</t>
+  </si>
+  <si>
+    <t>翻牌前後行動順序與選項：翻牌前（Pre_flop）因為盲注已下注，由大盲注左側的槍口位（UTG）第一個行動，可選擇棄牌（Fold）、跟注（Call）或加注（Raise）。翻牌後（Post_flop）則由小盲位開始行動；若該下注圈尚未有人下注，玩家多出「過牌（Check）」的選擇。若前方已經有人下注或加注，則後方玩家不能選擇過牌。</t>
+  </si>
+  <si>
+    <t>下注圈結束的標誌：每一輪下注（Betting_round）結束的標誌是，所有決定繼續參與該局的玩家，最終都投入了一樣多的籌碼於彩池中。如果玩家不想再投入與其他人同等的籌碼，就必須選擇棄牌（Fold）。</t>
+  </si>
+  <si>
+    <t>下注圈 結束 標誌 每一輪 下注 betting_round 結束 標誌 所有 決定 繼續 參與 該局 玩家 最終 投入 一樣 多 籌碼 彩池 中 如果 玩家 不想 再 投入 其他人 同等 籌碼 必須 選擇 棄牌 fold</t>
+  </si>
+  <si>
+    <t>銷牌（Burn_card）規則：在發出任何公共牌（翻牌、轉牌、河牌）之前，發牌員都必須先「銷牌（Burn）」，即捨棄牌堆頂端的第一張牌（不予使用）。銷牌後才發出公共牌（翻牌發 3 張，轉牌與河牌各發 1 張），此機制的目的是為了防止作弊或作號。</t>
+  </si>
+  <si>
+    <t>銷牌 burn_card 規則 發出 任何 公共牌 翻牌 轉牌 河牌 之前 發牌 員 必須 先 銷牌 burn 即 捨 棄牌 堆頂 端的 第一 張牌 不予 使用 銷牌 後 才 發出 公共牌 翻牌 發 3 張 轉牌 河牌 各發 1 張 此機制 目的 為 防止 作弊 或 作號</t>
   </si>
   <si>
     <t>翻牌後行動順序與棄牌遞延：翻牌後的各個下注圈，標準順序是由小盲位開始順時針行動，按鈕位（Button）通常是最後一個行動的優勢位置。若前方的盲注位玩家已棄牌，則由按鈕位左側「剩下未棄牌的第一位玩家」開始行動。</t>
   </si>
   <si>
-    <t>翻牌後 行動 順序 棄牌 遞延 翻牌後 各個 下注圈 標準 順序 由 小盲位 開始 順時針 行動 按鈕位 Button 通常 最後一個 行動 優勢 位置 若 前方 盲注位 玩家 已 棄牌 則由 按鈕位 左側 剩下 未 棄牌 第一位 玩家 開始 行動</t>
+    <t>翻牌後 行動 順序 棄牌 遞延 翻牌後 各個 下注圈 標準 順序 小盲位 開始 順時針 行動 按鈕位 button 通常 最後一個 行動 優勢 位置 若 前方 盲注位 玩家 已 棄牌 則由 按鈕位 左側 剩下 未 棄牌 第一位 玩家 開始 行動</t>
   </si>
   <si>
     <t>攤牌與下注逼退（Bluffing 概念）：在最後一圈行動中，若所有玩家皆選擇過牌（Check）或跟注至金額相同，則進入攤牌（Showdown）比大小。若玩家不想攤牌比牌力，可以選擇下注或加注更多的籌碼，利用下注壓力迫使跟不下的對手棄牌（Fold），藉此直接贏得底池。</t>
   </si>
   <si>
-    <t>攤牌 下注 逼退 Bluffing 概念 最 後 一圈 行動 中 若 所有 玩家 皆 選擇 過牌 Check 或 跟注 至金額 相同 則進入 攤牌 Showdown 比 大小 若 玩家 不想 攤牌 比牌力 可以 選擇 下注 或 加注 更 多 籌碼 利用 下注 壓力 迫使 跟 不下 對手 棄牌 Fold 藉此 直接 贏得 底池</t>
+    <t>攤牌 下注 逼退 bluffing 概念 最 後 一圈 行動 中 若 所有 玩家 皆 選擇 過牌 check 或 跟注 至金額 相同 則進入 攤牌 showdown 比 大小 若 玩家 不想 攤牌 比牌力 可以 選擇 下注 或 加注 更 多 籌碼 利用 下注 壓力 迫使 跟 不下 對手 棄牌 fold 藉此 直接 贏得 底池</t>
   </si>
   <si>
     <t>新加入牌桌的觀察策略與玩家分類：加入新牌桌時不應急於入局，應優先觀察對手打法。特別是透過對手攤牌（Showdown）時秀出的底牌，回溯其下注邏輯。這有助於快速將玩家分類，辨識出高手、激進型玩家、保守型玩家、喜歡詐唬（Bluff）的玩家，以及情緒失控（上頭 / Tilt）的玩家。</t>
   </si>
   <si>
-    <t>新 加入 牌桌 觀察 策略 玩家 分類 加入 新 牌桌 時不應 急 於 入局 應 優先 觀察 對手 打法 特別 透過 對手 攤牌 Showdown 時秀出 底牌 回溯 其 下注 邏輯 這 有助 於 快速 將 玩家 分類 辨識出 高手 激進型 玩家 保守 型 玩家 喜歡 詐唬 Bluff 玩家 情緒 失控 上頭 Tilt 玩家</t>
-  </si>
-  <si>
-    <t>翻牌前的看牌時機與肢體語言（Tells）：翻牌前（Pre-flop）不應一拿到手牌就立刻查看，以免下意識的表情或肢體動作洩漏自身的牌力意圖給對手。正確的做法是先觀察其他玩家看牌時的反應來搜集資訊，直到輪到自己行動時才查看底牌，以確保透露給對手的資訊降至最低。</t>
-  </si>
-  <si>
-    <t>翻牌前 看牌 時機 肢體 語言 Tells 翻牌前 Pre - flop 不應 一 拿到 手牌 立刻 查看 以免 下意識 表情 或肢 體動作 洩漏 自身 牌力意 圖給 對手 正確 做法 先 觀察 其他 玩家 看牌 時 反應 來 搜集 資訊 直到 輪到 自己 行動 時才 查看 底牌 以確 保 透露 給 對手 資訊降 至 最低</t>
+    <t>新 加入 牌桌 觀察 策略 玩家 分類 加入 新 牌桌 時不應 急 入局 應 優先 觀察 對手 打法 特別 透過 對手 攤牌 showdown 時秀出 底牌 回溯 其 下注 邏輯 這 有助 快速 將 玩家 分類 辨識出 高手 激進型 玩家 保守 型 玩家 喜歡 詐唬 bluff 玩家 情緒 失控 上頭 tilt 玩家</t>
+  </si>
+  <si>
+    <t>翻牌前的看牌時機與肢體語言（Tells）：翻牌前（Pre_flop）不應一拿到手牌就立刻查看，以免下意識的表情或肢體動作洩漏自身的牌力意圖給對手。正確的做法是先觀察其他玩家看牌時的反應來搜集資訊，直到輪到自己行動時才查看底牌，以確保透露給對手的資訊降至最低。</t>
+  </si>
+  <si>
+    <t>翻牌前 看牌 時機 肢體 語言 tells 翻牌前 pre_flop 不應 一 拿到 手牌 立刻 查看 以免 下意識 表情 或肢 體動作 洩漏 自身 牌力意 圖給 對手 正確 做法 先 觀察 其他 玩家 看牌 時 反應 來 搜集 資訊 直到 輪到 自己 行動 時才 查看 底牌 以確 保 透露 給 對手 資訊降 至 最低</t>
   </si>
   <si>
     <t>坐下：您可以在賭場的空位中自由選擇座位，但是在德州撲克中與座位是一個非常重要的因素，因此在賽事或與牌友玩時通常，座位的順序由規定好的座位表或撲克牌確定。</t>
   </si>
   <si>
-    <t>坐下 您 可以 賭場 空位 中 自由 選擇 座位 但是 德州撲克 中 座位 非常 重要 因素 因此 賽事 或 牌友 玩時 通常 座位 順序 由 規定 好 座位表 或 撲克牌 確定</t>
+    <t>坐下 您 可以 賭場 空位 中 自由 選擇 座位 但是 德州撲克 中 座位 非常 重要 因素 因此 賽事 或 牌友 玩時 通常 座位 順序 規定 好 座位表 或 撲克牌 確定</t>
   </si>
   <si>
     <t>荷官莊家位置的確定：座位決定之後，接下來決定荷官莊家位。第一個按鈕莊家的位置是荷官（發牌的人）將牌一張一張地分發給玩家，拿到最強牌的人確定為莊家位。 確定按鈕莊家位的玩家後，就開始正式發牌。</t>
@@ -366,13 +375,13 @@
     <t xml:space="preserve"> 翻牌：同時發三張公牌，由小盲注開始（如果小盲注已蓋牌，由後面最近的玩家開始，以此類推），按照順時針方向依次表態，玩家可以選擇下注、加注、或者蓋牌放棄。</t>
   </si>
   <si>
-    <t>翻牌 同時 發三張 公牌 由 小盲注 開始 如果 小盲注 已蓋牌 由後面 最近 玩家 開始 以此 類推 按照 順時針 方向 依次 表態 玩家 可以 選擇 下注 加注 或者 蓋牌 放棄</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 轉牌&amp;河牌：Turn—發第四張牌，由小盲注開始，按照順時針方向依次表態。 River—發第五張牌，由小盲注開始，按照順時針方向依次表態，玩家可以選擇下注、加注、或者蓋牌放棄。經過前面四輪發牌和下注，還剩餘2名以上的玩家時，開始比大小，這時候需要亮牌。</t>
-  </si>
-  <si>
-    <t>轉牌 &amp; 河牌 Turn — 發 第四 張牌 由 小盲注 開始 按照 順時針 方向 依次 表態 River — 發 第五 張牌 由 小盲注 開始 按照 順時針 方向 依次 表態 玩家 可以 選擇 下注 加注 或者 蓋牌 放棄 經過 前面 四輪 發牌 和 下注 還剩 餘 2 名 以上 玩家 時 開始 比 大小 這時候 需要 亮牌</t>
+    <t>翻牌 同時 發三張 公牌 小盲注 開始 如果 小盲注 已蓋牌 由後面 最近 玩家 開始 以此 類推 按照 順時針 方向 依次 表態 玩家 可以 選擇 下注 加注 或者 蓋牌 放棄</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 轉牌&amp;河牌：Turn—發第四張牌，由小盲注開始，按照順時針依次表態。 River—發第五張牌，由小盲注開始，按照順時針方向依次表態，玩家可以選擇下注、加注、或者蓋牌放棄。經過前面四輪發牌和下注，還剩餘2名以上的玩家時，開始比大小，這時候需要亮牌。</t>
+  </si>
+  <si>
+    <t>轉牌 &amp; 河牌 turn — 發 第四 張牌 小盲注 開始 按照 順時針 依次 表態 river — 發 第五 張牌 小盲注 開始 按照 順時針 方向 依次 表態 玩家 可以 選擇 下注 加注 或者 蓋牌 放棄 經過 前面 四輪 發牌 和 下注 還剩 餘 2 名 以上 玩家 時 開始 比 大小 這時候 需要 亮牌</t>
   </si>
   <si>
     <t>亮牌：剩餘2名以上的玩家開始亮牌比大小，成牌最大的玩家贏取池底。亮牌是用自己的2張底牌和5張公共牌結合在一起，選出5張牌，通過比大小決定勝者。不論手中的牌使用幾張（甚至可以不用手中的底牌），湊成最大的成牌，跟其他玩家比大小。</t>
@@ -384,9 +393,6 @@
     <t>叫注(也叫說話)：･讓牌 - 在無需跟進的情況下選擇把決定「讓」給下一位 ･押注 - 押上籌碼 ･棄牌 - 放棄繼續牌局的機會 ･加注 - 在其他玩家下注後，把現有的注金抬高 ･跟進 - 跟隨眾人押上同等的注額 ･全押 - 一次過把手上的籌碼全押上</t>
   </si>
   <si>
-    <t>叫注 ( 叫 說 話 ) ･ 讓 牌 - 無 需 跟 進 情況 下 選擇 把 決定 讓 給下 一位 ･ 押注 - 押 上 籌碼 ･ 棄牌 - 放棄 繼續 牌局 機會 ･ 加注 - 其他 玩家 下注 後 把 現有 注金 抬高 ･ 跟 進 - 跟 隨眾 人 押 上 同等 注額 ･ 全押 - 一次 過把 手上 籌碼 全押 上</t>
-  </si>
-  <si>
     <t>高牌是指沒有湊成以上任何牌型的情況，只能比單張牌的大小，也是遊戲中相當常見的狀況。</t>
   </si>
   <si>
@@ -396,25 +402,25 @@
     <t>一對是由兩張同一個數字的牌所組成，這是德州撲克中最常見的牌型，出現機率非常高。</t>
   </si>
   <si>
-    <t>一對 由 兩張 同一 個 數字 牌 所 組成 這是 德州撲克 中 最常見 牌型 出現 機率 非常 高</t>
+    <t>一對 兩張 同一 個 數字 牌 所 組成 這是 德州撲克 中 最常見 牌型 出現 機率 非常 高</t>
   </si>
   <si>
     <t>兩對是由兩組不同數字的對子所組成，是遊戲中相當常見的牌型。</t>
   </si>
   <si>
-    <t>兩對 由 兩組 不同 數字 對子 所 組成 遊戲 中相 當常見 牌型</t>
+    <t>兩對 兩組 不同 數字 對子 所 組成 遊戲 中相 當常見 牌型</t>
   </si>
   <si>
     <t>三條是由三張同一個數字的牌所組成，出現的機率稍低。</t>
   </si>
   <si>
-    <t>三條 由 三張 同一 個 數字 牌 所 組成 出現 機率 稍低</t>
+    <t>三條 三張 同一 個 數字 牌 所 組成 出現 機率 稍低</t>
   </si>
   <si>
     <t>順子是由五張數字連續的牌所組成，在遊戲中屬於機率偏低的牌型。</t>
   </si>
   <si>
-    <t>順子 由 五張 數字 連續 牌 所 組成 遊戲 中屬 於 機率 偏低 牌型</t>
+    <t>順子 五張 數字 連續 牌 所 組成 遊戲 中屬 機率 偏低 牌型</t>
   </si>
   <si>
     <t>同花是指五張牌都是同一個花色，雖然強度很高，但出現的機率依然偏低。</t>
@@ -426,31 +432,37 @@
     <t>葫蘆是由一個對子加上一個三條所組成，是一個非常強勢且出現機率較低的牌型。</t>
   </si>
   <si>
-    <t>葫蘆 由 對子 加上 三條 所 組成 非常 強勢 且 出現 機率 較 低 牌型</t>
+    <t>葫蘆 對子 加上 三條 所 組成 非常 強勢 且 出現 機率 較 低 牌型</t>
   </si>
   <si>
     <t>四條是由四張同一個數字的牌所組成，屬於出現機率極低的強大牌型。</t>
   </si>
   <si>
-    <t>四條 由 四張 同一 個 數字 牌 所 組成 屬 於 出現 機率 極低 的強 大牌 型</t>
+    <t>四條 四張 同一 個 數字 牌 所 組成 屬 出現 機率 極低 的強 大牌 型</t>
   </si>
   <si>
     <t>同花順的強度僅次於皇家同花順，是同花色加上順子的組合，出現的機率也是極度罕見。</t>
   </si>
   <si>
-    <t>同花順 強度 僅次 於 皇家同花順 同 花色 加上 順子 組合 出現 機率 極度 罕見</t>
-  </si>
-  <si>
-    <t>皇家同花順是德州撲克中最強的牌型，由十、J、Q、K、A 的同花色組合而成，出現的機率極度罕見。</t>
-  </si>
-  <si>
-    <t>皇家同花順 德州撲克 中 最強 牌型 由十 J Q K A 同 花色 組合 而成 出現 機率 極度 罕見</t>
-  </si>
-  <si>
-    <t>同一個牌型的強弱對比：如果兩個玩家拿到同樣的牌型，則按以下方法確定一手牌的強度。強度為A&gt; K&gt; Q&gt; J&gt; 10&gt; ... &gt; 2。･首先比較手的「主要部分」的大小（一對的話比對子的強度，兩對的話看較大的對子強度，三條的話看數位的強度）。･如果它們相同，則比較其他牌裡數位最大的一張牌的大小（其餘卡）。･如果它們也相同的話，則平分底池。</t>
-  </si>
-  <si>
-    <t>同一 個 牌型 強弱 對 比 如果 兩個 玩家 拿到 同樣 牌型 則 按 以下 方法 確定 一手 牌 強度 強度 為 A K Q J 10 ... 2 ･ 首先 比較 手 主要 部分 大小 一對 話 比 對子 強度 兩對 話 看 較 大 對子 強度 三條 話 看 數位 強度 ･ 如果 它們 相同 則比較 其他 牌裡 數位 最大 一 張牌 大小 其餘卡 ･ 如果 它們 相同 話 則 平分 底池</t>
+    <t>同花順 強度 僅次 皇家同花順 同 花色 加上 順子 組合 出現 機率 極度 罕見</t>
+  </si>
+  <si>
+    <t>皇家同花順是德州撲克中最強的牌型，A_K_Q_J_10 的同花色組合而成，出現的機率極度罕見。</t>
+  </si>
+  <si>
+    <t>皇家同花順 德州撲克 中 最強 牌型 a_k_q_j_10 同 花色 組合 而成 出現 機率 極度 罕見</t>
+  </si>
+  <si>
+    <t>牌型大方向比大小A_K_Q_J_10_9_8_7_6_5_4_3_2，spade黑桃 、heart紅心、diamond方塊、club梅花</t>
+  </si>
+  <si>
+    <t>牌型 大方向 比 大小 a_k_q_j_10_9_8_7_6_5_4_3_2 spade 黑桃 heart 紅心 diamond 方塊 club 梅花</t>
+  </si>
+  <si>
+    <t>兩個玩家拿到同樣的牌型，首先比較主要牌型的大小（一對的話比對子的強度，兩對的話看較大的對子強度，三條的話看數位的強度）。･如果主要牌型相同，則比較其餘的牌。如果其餘的牌也相同的話，則平分底池。</t>
+  </si>
+  <si>
+    <t>兩個 玩家 拿到 同樣 牌型 首先 比較 主要 牌型 大小 一對 話 比 對子 強度 兩對 話 看 較 大 對子 強度 三條 話 看 數位 強度 ･ 如果 主要 牌型 相同 則比較 其餘 牌 如果 其餘 牌 相同 話 則 平分 底池</t>
   </si>
   <si>
     <t>平局情況的底池分配：在平局的情況下，下注的籌碼被平分，並在排名第一的玩家之間平均分配。 但是，如果當時的籌碼總數有除不盡的情況，則一般常見的規則是把除盡後剩下的籌碼分給最先叫注的人（也就是「位置不佳的人」）。</t>
@@ -468,409 +480,409 @@
     <t>SB（小盲位）：位於 BTN 莊家左側的位置。 在這個位置必須下半盲注。 翻牌前可以在 BTN 莊家位行動後進行棄牌，跟注和加注等操作。 翻牌後，必須最先下決定的位置，所以可以說是一個不利的位置。 另外，即使在翻牌前，也要注意在後面的 BB 大盲位置的行動，因此很難採取激進的叫注動作。</t>
   </si>
   <si>
-    <t>SB 小盲位 位 於 BTN 莊家 左側 位置 這個 位置 必須 下 半 盲注 翻牌前 可以 BTN 莊家 位 行動 後 進行 棄牌 跟注 和 加注 等 操作 翻牌後 必須 最先 下 決定 位置 所以 可以 說 不利 位置 另外 即使 翻牌前 要 注意 在後面 BB 大盲位 置 行動 因此 很難 採取 激進 叫注 動作</t>
+    <t>sb 小盲位 位 btn 莊家 左側 位置 這個 位置 必須 下 半 盲注 翻牌前 可以 btn 莊家 位 行動 後 進行 棄牌 跟注 和 加注 等 操作 翻牌後 必須 最先 下 決定 位置 所以 可以 說 不利 位置 另外 即使 翻牌前 要 注意 在後面 bb 大盲位 置 行動 因此 很難 採取 激進 叫注 動作</t>
   </si>
   <si>
     <t>BB（大盲位）：位於 SB 小盲左側的位置。 在這個位置必須下盲注。 翻牌前可以在 SB 小盲位行動後進行棄牌，跟注和加注等操作。 翻牌後，您需要在 SB 小盲位旁邊採取行動。 在翻牌前，您可以在最後階段採取行動，但是如果在翻牌後，除了 SB 小盲位以外，該位置都被認為是不利的，因此它並不是一個好位置。</t>
   </si>
   <si>
-    <t>BB 大盲位 位 於 SB 小盲 左側 位置 這個 位置 必須 下 盲注 翻牌前 可以 SB 小盲位 行動 後 進行 棄牌 跟注 和 加注 等 操作 翻牌後 您 需要 SB 小盲位 旁邊 採取 行動 翻牌前 您 可以 最後階段 採取 行動 但是 如果 翻牌後 除了 SB 小盲位 以外 該 位置 認為 不利 因此 它並 不是 好 位置</t>
+    <t>bb 大盲位 位 sb 小盲 左側 位置 這個 位置 必須 下 盲注 翻牌前 可以 sb 小盲位 行動 後 進行 棄牌 跟注 和 加注 等 操作 翻牌後 您 需要 sb 小盲位 旁邊 採取 行動 翻牌前 您 可以 最後階段 採取 行動 但是 如果 翻牌後 除了 sb 小盲位 以外 該 位置 認為 不利 因此 它並 不是 好 位置</t>
   </si>
   <si>
     <t>UTG（槍口位）：位於 BB 大盲左側的位置。 必須在翻牌前最先採取行動，並且由於翻牌後除了 SB 和 BB 之外，該位置都是不利的，因此從槍口指向的角度來看，這是危險的位置。 由於沒有任何先叫注對手的訊息，因此在游戲中唯一可以利用的訊息就是自己的手牌（底牌）。 因此，該位置如果要採取下注行為的話需要很強的手牌。</t>
   </si>
   <si>
-    <t>UTG 槍口位 位 於 BB 大盲 左側 位置 必須 翻牌前 最先 採取 行動 並且 由 於 翻牌後 除了 SB 和 BB 之外 該 位置 不利 因此 從 槍口 指向 角度 來 看 這是 危險 位置 由 於 沒 有 任何 先 叫注 對手 訊息 因此 游戲 中 唯一 可以 利用 訊息 就是 自己 手牌 底牌 因此 該 位置 如果 要 採取 下注 行為 話 需要 很強 手牌</t>
+    <t>utg 槍口位 位 bb 大盲 左側 位置 必須 翻牌前 最先 採取 行動 並且 翻牌後 除了 sb 和 bb 之外 該 位置 不利 因此 從 槍口 指向 角度 來 看 這是 危險 位置 沒 有 任何 先 叫注 對手 訊息 因此 游戲 中 唯一 可以 利用 訊息 就是 自己 手牌 底牌 因此 該 位置 如果 要 採取 下注 行為 話 需要 很強 手牌</t>
   </si>
   <si>
     <t>EP（早期位）：指需要及早採取行動的位置。 它取決於坐在桌子上的人數。 在10人桌的情況下，UTG 和其左邊的兩個人通常稱為早期位。 對于6人桌，只有UTG 處于早期位。</t>
   </si>
   <si>
-    <t>EP 早期位 指 需要 及早 採取 行動 位置 它 取決 於 坐在 桌子 上 人數 10 人桌 情況 下 UTG 和 其 左邊 兩個 人 通常 稱為 早期位 對于 6 人桌 只有 UTG 處于 早期位</t>
+    <t>ep 早期位 指 需要 及早 採取 行動 位置 它 取決 坐在 桌子 上 人數 10 人桌 情況 下 utg 和 其 左邊 兩個 人 通常 稱為 早期位 對于 6 人桌 只有 utg 處于 早期位</t>
   </si>
   <si>
     <t>MP（中期位）：指每個回合在中間採取行動的位置。 在10人桌的情況下，通常將在翻牌前從第4到第6的這3人位置叫做中期位。 對于6人桌，UTG 的左側2個人屬於中間位。</t>
   </si>
   <si>
-    <t>MP 中期位 指 每個 回合 中間 採取 行動 位置 10 人桌 情況 下 通常 將在 翻牌前 從 第 4 到 第 6 這 3 人 位置 叫做 中期位 對于 6 人桌 UTG 左側 2 個 人屬 於 中間 位</t>
+    <t>mp 中期位 指 每個 回合 中間 採取 行動 位置 10 人桌 情況 下 通常 將在 翻牌前 從 第 4 到 第 6 這 3 人 位置 叫做 中期位 對于 6 人桌 utg 左側 2 個 人屬 中間 位</t>
   </si>
   <si>
     <t>CO（關煞位）：指的是 BTN 莊家位的前一個位置。</t>
   </si>
   <si>
-    <t>CO 關煞位 指 BTN 莊家 位 前 位置</t>
+    <t>co 關煞位 指 btn 莊家 位 前 位置</t>
   </si>
   <si>
     <t>BTN（莊家按鈕位）：指的是每回合可以最後採取行動的位置，被認為是最佳位置。 在許多情況下，這個位置的玩家前面都會放置一枚寫著 DEALER 字樣的圓形按鈕。 不管是線上還是線下，這個位置都會做標記。</t>
   </si>
   <si>
-    <t>BTN 莊家 按鈕位 指 每 回合 可以 最後採取 行動 位置 認為 最佳 位置 在許 多情 況下 這個 位置 玩家 前面 會 放置 一枚 寫著 DEALER 字樣 圓形 按鈕 不管 線 上 還是 線 下 這個 位置 會 做 標記</t>
-  </si>
-  <si>
-    <t>All-in（全下）：全下意味著把自己手上的籌碼全部下注在某牌桌上。 一旦全下，就不能下注或跟注，也不能棄牌，自動過渡到亮牌階段。 其餘玩家將繼續照常進行。</t>
-  </si>
-  <si>
-    <t>All - in 全 下 全 下 意味著 把 自己 手上 籌碼 全部 下注 某牌 桌上 一旦 全 下 不能 下注 或 跟注 不能 棄牌 自動 過渡 到 亮牌 階段 其餘 玩家 將繼續 照常 進行</t>
+    <t>btn 莊家 按鈕位 指 每 回合 可以 最後採取 行動 位置 認為 最佳 位置 在許 多情 況下 這個 位置 玩家 前面 會 放置 一枚 寫著 dealer 字樣 圓形 按鈕 不管 線 上 還是 線 下 這個 位置 會 做 標記</t>
+  </si>
+  <si>
+    <t>all_in（全下）：全下意味著把自己手上的籌碼全部下注在某牌桌上。 一旦全下，就不能下注或跟注，也不能棄牌，自動過渡到亮牌階段。 其餘玩家將繼續照常進行。</t>
+  </si>
+  <si>
+    <t>all_in 全 下 全 下 意味著 把 自己 手上 籌碼 全部 下注 某牌 桌上 一旦 全 下 不能 下注 或 跟注 不能 棄牌 自動 過渡 到 亮牌 階段 其餘 玩家 將繼續 照常 進行</t>
   </si>
   <si>
     <t>Bet（下注）：下注意味著加大籌碼。 如果在前面的玩家尚未進行下注，則下注是該玩家可以採取的行動之一。 一個玩家只有在沒有其他人先進行下注的情況下才能下注。 如果已經有玩家下注，則玩家必須進行跟注動作或者有需要的話可以加注。</t>
   </si>
   <si>
-    <t>Bet 下注 下注 意味著 加大 籌碼 如果 前面 玩家 尚未 進行 下注 則 下注 該 玩家 可以 採取 行動 之一 玩家 只有 沒 有 其他人 先 進行 下注 情況 下 才能 下注 如果 已經 有 玩家 下注 則 玩家 必須 進行 跟注 動作 或者 有 需要 話 可以 加注</t>
-  </si>
-  <si>
-    <t>Buy-in（買入）：參與游戲所需的金額。 對于諸如賭場的現金游戲，最低買入費由表格設定。 對于賽事，分為獎池和支付給主辦方的參與費。</t>
-  </si>
-  <si>
-    <t>Buy - in 買入 參與 游戲 所 需 金額 對于 諸如 賭場 現金游戲 最低 買入費 由 表格 設定 對于 賽事 分為 獎池 和 支付 給主 辦方 參與費</t>
-  </si>
-  <si>
-    <t>Bank roll（總資金）：玩家的資金就是他用來玩撲克的全部金錢。 即准備的資金總額。 在線撲克中，指的是玩家帳戶裡所擁有的資金。</t>
-  </si>
-  <si>
-    <t>Bank roll 總資金 玩家 資金 就是 他用 來 玩 撲克 全部 金錢 即 准備 資金 總額 線 撲克中 指 玩家 帳戶裡 所 擁有 資金</t>
+    <t>bet 下注 下注 意味著 加大 籌碼 如果 前面 玩家 尚未 進行 下注 則 下注 該 玩家 可以 採取 行動 之一 玩家 只有 沒 有 其他人 先 進行 下注 情況 下 才能 下注 如果 已經 有 玩家 下注 則 玩家 必須 進行 跟注 動作 或者 有 需要 話 可以 加注</t>
+  </si>
+  <si>
+    <t>Buy_in（買入）：參與游戲所需的金額。 對于諸如賭場的現金游戲，最低買入費由表格設定。 對于賽事，分為獎池和支付給主辦方的參與費。</t>
+  </si>
+  <si>
+    <t>buy _ in 買入 參與 游戲 所 需 金額 對于 諸如 賭場 現金游戲 最低 買入費 表格 設定 對于 賽事 分為 獎池 和 支付 給主 辦方 參與費</t>
+  </si>
+  <si>
+    <t>Bank_roll（總資金）：玩家的資金就是他用來玩撲克的全部金錢。 即准備的資金總額。 在線撲克中，指的是玩家帳戶裡所擁有的資金。</t>
+  </si>
+  <si>
+    <t>bank_roll 總資金 玩家 資金 就是 他用 來 玩 撲克 全部 金錢 即 准備 資金 總額 線 撲克中 指 玩家 帳戶裡 所 擁有 資金</t>
   </si>
   <si>
     <t>Blind（盲注）：盲注是撲克游戲中強制下注的一種形式。 是必須在發牌前支付的賭注。 每回合由兩名玩家支付，但不是固定玩家支付，每一回合輪流變化。 通常，兩個賭注具有相同的大小，或者一個賭注大於另一個賭注。 後者稱為「大盲注和小盲注」。</t>
   </si>
   <si>
-    <t>Blind 盲注 盲注 撲克游 戲中 強制 下注 一種 形式 必須 發牌 前 支付 賭注 每 回合 由 兩名 玩家 支付 但 不是 固定 玩家 支付 每一 回合 輪流 變化 通常 兩個 賭注 具有 相同 大小 或者 賭 注大 於 另 賭注 後 者 稱 為 大盲注 和 小盲注</t>
+    <t>blind 盲注 盲注 撲克游 戲中 強制 下注 一種 形式 必須 發牌 前 支付 賭注 每 回合 兩名 玩家 支付 但 不是 固定 玩家 支付 每一 回合 輪流 變化 通常 兩個 賭注 具有 相同 大小 或者 賭注 大於 另 賭注 後 者 稱 為 大盲注 和 小盲注</t>
   </si>
   <si>
     <t>Board（公共牌）：在使用公共牌的游戲中，Board一般指的是所有公共牌。 例如，在德州撲克中，由翻牌，轉牌和河牌組成。</t>
   </si>
   <si>
-    <t>Board 公共牌 使用 公共牌 游戲 中 Board 一般 指 所有 公共牌 例如 德州撲克 中 由 翻牌 轉牌 和 河牌 組成</t>
+    <t>board 公共牌 使用 公共牌 游戲 中 board 一般 指 所有 公共牌 例如 德州撲克 中 翻牌 轉牌 和 河牌 組成</t>
   </si>
   <si>
     <t>Button（按鈕）：按鈕，或者莊家按鈕，是一個提示，顯示當前誰是莊家。 莊家坐在的位置也稱為按鈕位。 或者說「莊家即按鈕」。</t>
   </si>
   <si>
-    <t>Button 按鈕 按鈕 或者 莊家 按鈕 提示 顯示 當前 誰 莊家 莊家 坐在 位置 稱 為 按鈕位 或者 說 莊家 即 按鈕</t>
-  </si>
-  <si>
-    <t>Bad beat（小概率失敗）：Bad beat 是指拿到好牌非常有優勢的玩家在不太可能的情況下輸掉。 正常失敗和小概率失敗之間的界限因玩家而異。 通常，如果您以5-10％的勝率輸掉一手牌，或者如果您的對手由於您已經抽出兩張完美的牌而輸了， 則稱為小概率失敗。</t>
-  </si>
-  <si>
-    <t>Bad beat 小 概率 失敗 Bad beat 指 拿到 好牌 非常 有 優勢 玩家 不太可能 情況 下輸 掉 正常 失敗 和 小 概率 失敗 之間 界限 因 玩家 而異 通常 如果 您 以 5 - 10 ％ 勝率 輸掉 一手 牌 或者 如果 您 對手 由 於 您 已經 抽出 兩張 完美 牌 輸 則稱 為 小 概率 失敗</t>
+    <t>button 按鈕 按鈕 或者 莊家 按鈕 提示 顯示 當前 誰 莊家 莊家 坐在 位置 稱 為 按鈕位 或者 說 莊家 即 按鈕</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bad_beat（小概率失敗）：Bad_beat 是指拿到好牌非常有優勢的玩家在不太可能的情況下輸掉。 正常失敗和小概率失敗之間的界限因玩家而異。 </t>
+  </si>
+  <si>
+    <t>bad _ beat 小 概率 失敗 bad _ beat 指 拿到 好牌 非常 有 優勢 玩家 不太可能 情況 下輸 掉 正常 失敗 和 小 概率 失敗 之間 界限 因 玩家 而異</t>
   </si>
   <si>
     <t>Blank（空白）：空白或磚塊指的是不會形成任何牌型的公共牌。 「轉牌是空白」表示轉牌沒有改變游戲狀況。 例如，在3高牌（花色不同的牌）翻牌後，轉牌出現2，表示為空白。</t>
   </si>
   <si>
-    <t>Blank 空白 空白 或 磚塊 指 不會 形成 任何 牌型 公共牌 轉牌 空白 表示 轉牌 沒有 改變 游戲 狀況 例如 3 高牌 花色 不同 牌 翻牌後 轉牌 出現 2 表示 為 空白</t>
-  </si>
-  <si>
-    <t>Bust out（出局）：淘汰或出局意味著失去自己的全部籌碼或輸掉賽事。 淘汰某人意味著把某人從桌子排除或從賽事中擊敗。</t>
-  </si>
-  <si>
-    <t>Bust out 出局 淘汰 或 出局 意味著 失去 自己 全部 籌碼 或 輸掉 賽事 淘汰 某人 意味著 把 某人 從 桌子 排除 或 從 賽事 中擊敗</t>
+    <t>blank 空白 空白 或 磚塊 指 不會 形成 任何 牌型 公共牌 轉牌 空白 表示 轉牌 沒有 改變 游戲 狀況 例如 3 高牌 花色 不同 牌 翻牌後 轉牌 出現 2 表示 為 空白</t>
+  </si>
+  <si>
+    <t>Bust_out（出局）：淘汰或出局意味著失去自己的全部籌碼或輸掉賽事。 淘汰某人意味著把某人從桌子排除或從賽事中擊敗。</t>
+  </si>
+  <si>
+    <t>bust _ out 出局 淘汰 或 出局 意味著 失去 自己 全部 籌碼 或 輸掉 賽事 淘汰 某人 意味著 把 某人 從 桌子 排除 或 從 賽事 中擊敗</t>
   </si>
   <si>
     <t>Call（跟注）：跟上一位玩家投入相同籌碼。 跟注是相對于對手的加注可以采取的行動之一。</t>
   </si>
   <si>
-    <t>Call 跟注 跟上 一位 玩家 投入 相同 籌碼 跟注 相 對 于 對手 加注 可以 采取 行動 之一</t>
+    <t>call 跟注 跟上 一位 玩家 投入 相同 籌碼 跟注 相 對 于 對手 加注 可以 采取 行動 之一</t>
   </si>
   <si>
     <t>Check（看牌）：前面無人下注，自己也不下注，也叫「看牌」或「過牌」。 看牌是玩家可以採取的行動之一。 不進行加注動作的玩家可以選擇看牌動作。</t>
   </si>
   <si>
-    <t>Check 看牌 前面 無人 下注 自己 不 下注 叫 看牌 或 過牌 看牌 玩家 可以 採取 行動 之一 不 進行 加注 動作 玩家 可以 選擇 看牌 動作</t>
-  </si>
-  <si>
-    <t>Cut off（關煞位）：在有規定莊家按鈕位的游戲中，關煞位在按鈕位的右邊。</t>
-  </si>
-  <si>
-    <t>Cut off 關煞位 有 規定 莊家 按鈕位 游戲 中 關煞位 按鈕位 右邊</t>
+    <t>check 看牌 前面 無人 下注 自己 不 下注 叫 看牌 或 過牌 看牌 玩家 可以 採取 行動 之一 不 進行 加注 動作 玩家 可以 選擇 看牌 動作</t>
+  </si>
+  <si>
+    <t>Cut_off（關煞位）：在有規定莊家按鈕位的游戲中，關煞位在按鈕位的右邊。</t>
+  </si>
+  <si>
+    <t>cut_off 關煞位 有 規定 莊家 按鈕位 游戲 中 關煞位 按鈕位 右邊</t>
   </si>
   <si>
     <t>Cap（上限）：上限是您在一局中可以加的最後一次加注，或者是一局中可以下注的最大金額。 通常在一局中限制第三，第四或第五次加注。 最後加注的成為上限。</t>
   </si>
   <si>
-    <t>Cap 上限 上限 您 一局 中 可以 加 最 後 一次 加注 或者 一局 中 可以 下注 最大 金額 通常 一局 中 限制 第三 第四 或 第五次 加注 最 後 加注 成為 上限</t>
-  </si>
-  <si>
-    <t>Community cards（公共牌）：由荷官發出的桌上的玩家共有的牌。</t>
-  </si>
-  <si>
-    <t>Community cards 公共牌 由 荷官 發出 桌上 玩家 共有 牌</t>
-  </si>
-  <si>
-    <t>Check-Raise（看牌加注）：看牌加注是一種打法，指的是「玩家先看牌然後在下一個對手下注時加注」。</t>
-  </si>
-  <si>
-    <t>Check - Raise 看牌 加注 看牌 加注 一種 打法 指 玩家 先看 牌然 後 下 對手 下注 時 加注</t>
+    <t>cap 上限 上限 您 一局 中 可以 加 最 後 一次 加注 或者 一局 中 可以 下注 最大 金額 通常 一局 中 限制 第三 第四 或 第五次 加注 最 後 加注 成為 上限</t>
+  </si>
+  <si>
+    <t>Community_cards（公共牌）：由荷官發出的桌上的玩家共有的牌。</t>
+  </si>
+  <si>
+    <t>community_cards 公共牌 荷官 發出 桌上 玩家 共有 牌</t>
+  </si>
+  <si>
+    <t>Check_Raise（看牌加注）：看牌加注是一種打法，指的是「玩家先看牌然後在下一個對手下注時加注」。</t>
+  </si>
+  <si>
+    <t>check_raise 看牌 加注 看牌 加注 一種 打法 指 玩家 先看 牌然 後 下 對手 下注 時 加注</t>
   </si>
   <si>
     <t>Draw（聽牌）：聽牌是指未完成的組合，還需要1張或1張以上的牌才能組成特定的牌型。</t>
   </si>
   <si>
-    <t>Draw 聽牌 聽牌 指未 完成 組合 還 需要 1 張 或 1 張 以上 牌 才能 組 成特定 牌型</t>
+    <t>draw 聽牌 聽牌 指未 完成 組合 還 需要 1 張 或 1 張 以上 牌 才能 組 成特定 牌型</t>
   </si>
   <si>
     <t>Dealer（荷官）：荷官指的是發牌的人。</t>
   </si>
   <si>
-    <t>Dealer 荷官 荷官 指 發牌 人</t>
-  </si>
-  <si>
-    <t>Drawing dead（聽死牌）：玩家就算發牌之後也沒有勝算的話，就稱作「他在聽死牌」。</t>
-  </si>
-  <si>
-    <t>Drawing dead 聽死牌 玩家 就算 發牌 之 後 沒 有 勝算 話 稱作 他 聽 死牌</t>
+    <t>dealer 荷官 荷官 指 發牌 人</t>
+  </si>
+  <si>
+    <t>Drawing_dead（聽死牌）：玩家就算發牌之後也沒有勝算的話，就稱作「他在聽死牌」。</t>
+  </si>
+  <si>
+    <t>drawing_dead 聽死牌 玩家 就算 發牌 之 後 沒 有 勝算 話 稱作 他 聽 死牌</t>
   </si>
   <si>
     <t>Edge（優勢）：「擁有優勢」意味著比其他玩家更具優勢。 例如，好的手牌比弱的手牌有優勢。 技術水準高或桌上位置好的玩家也有優勢。</t>
   </si>
   <si>
-    <t>Edge 優勢 擁有 優勢 意味著 比 其他 玩家 更具 優勢 例如 好 手牌 比弱 手牌 有 優勢 技術 水準 高 或 桌上 位置 好 玩家 有 優勢</t>
-  </si>
-  <si>
-    <t>Early（早期）：在玩家相對于荷官的相對位置決定游戲順序的游戲中，早期位是必須首先採取行動的玩家。 例如，在德州撲克的全圈桌中，盲注之後的前三個位置是早期位。 它們也稱為UTG（槍口位），UTG + 1，UTG + 2。</t>
-  </si>
-  <si>
-    <t>Early 早期 玩家 相對于 荷官 相 對 位置 決定 游戲 順序 游戲 中 早期位 必須 首先 採取 行動 玩家 例如 德州撲克 全圈 桌中 盲注 之 後 前三個 位置 早期位 它們 稱 為 UTG 槍口位 UTG + 1 UTG + 2</t>
+    <t>edge 優勢 擁有 優勢 意味著 比 其他 玩家 更具 優勢 例如 好 手牌 比弱 手牌 有 優勢 技術 水準 高 或 桌上 位置 好 玩家 有 優勢</t>
+  </si>
+  <si>
+    <t>Early（早期）：在玩家相對于荷官的相對位置決定游戲順序的游戲中，早期位是必須首先採取行動的玩家。 也稱為UTG（槍口位）</t>
+  </si>
+  <si>
+    <t>early 早期 玩家 相對于 荷官 相 對 位置 決定 游戲 順序 游戲 中 早期位 必須 首先 採取 行動 玩家 稱 為 utg 槍口位</t>
   </si>
   <si>
     <t>Flop（翻牌）：在德州撲克和奧馬哈等使用公共牌的撲克游戲中，翻牌指的是前三張公共牌。</t>
   </si>
   <si>
-    <t>Flop 翻牌 德州撲克 和 奧馬哈 等 使用 公共牌 撲克游戲 中 翻牌 指 前三張 公共牌</t>
+    <t>flop 翻牌 德州撲克 和 奧馬哈 等 使用 公共牌 撲克游戲 中 翻牌 指 前三張 公共牌</t>
   </si>
   <si>
     <t>Fold（棄牌）：棄牌的玩家放置其牌，並在本回合中退出該賽事。 該玩家已經下注的籌碼留在底池中，可以從下一輪重新加入游戲。</t>
   </si>
   <si>
-    <t>Fold 棄牌 棄牌 玩家 放置 其牌 並在 本 回合 中 退出 該賽 事 該 玩家 已經 下注 籌碼 留在 底池 中 可以 從下 一輪 重新加入 游戲</t>
+    <t>fold 棄牌 棄牌 玩家 放置 其牌 並在 本 回合 中 退出 該賽 事 該 玩家 已經 下注 籌碼 留在 底池 中 可以 從下 一輪 重新加入 游戲</t>
   </si>
   <si>
     <t xml:space="preserve">Fish（菜鳥）：Fish 指的是菜鳥。  Fish 指沒有策略，甚至還會採取負期望的行動的玩家。  菜鳥用很爛的牌入池，還頻繁下注。 </t>
   </si>
   <si>
-    <t>Fish 菜 鳥 Fish 指 菜 鳥 Fish 指沒有 策略 甚至 還會 採取負 期望 行動 玩家 菜 鳥用 很爛 牌入 池 還頻 繁 下注</t>
+    <t>fish 菜 鳥 fish 指 菜 鳥 fish 指沒有 策略 甚至 還會 採取負 期望 行動 玩家 菜 鳥用 很爛 牌入 池 還頻 繁 下注</t>
   </si>
   <si>
     <t>Freeroll（免費賽）：Freeroll 免費賽是指具有贊助獎品或有贊助商的不需要買入的賽事。 Freeroll 免費賽指2名玩家擁有同等實力的手牌聽牌，其中1名玩家組成牌型的話將拿走全部獎池的情況。 （第二個玩家聽牌沒有擊中）。</t>
   </si>
   <si>
-    <t>Freeroll 免費賽 Freeroll 免費賽 指 具有 贊助 獎品 或 有 贊助商 不 需要 買入 賽事 Freeroll 免費賽 指 2 名 玩家 擁有 同等 實力 手牌 聽牌 其中 1 名 玩家 組成 牌型 話將 拿走 全部 獎池 情況 第二 個 玩家 聽牌 沒有擊 中</t>
+    <t>freeroll 免費賽 freeroll 免費賽 指 具有 贊助 獎品 或 有 贊助商 不 需要 買入 賽事 freeroll 免費賽 指 2 名 玩家 擁有 同等 實力 手牌 聽牌 其中 1 名 玩家 組成 牌型 話將 拿走 全部 獎池 情況 第二 個 玩家 聽牌 沒有擊 中</t>
   </si>
   <si>
     <t>Grind（安全打法）：安全打法指的是不願冒太大風險，根據一定的下注限額持續取得利益的一種打法。 「Grinder」和「Rounder」這兩個術語是指，為了賺取自己的收入一部分或者全額（即使可以採取高風險高回報的打法的 時候）進行的安全打法。</t>
   </si>
   <si>
-    <t>Grind 安全 打法 安全 打法 指 不願 冒 太大風險 一定 下注 限額 持續 取得 利益 一種 打法 Grinder 和 Rounder 這兩個術語 指 為 賺取 自己 收入 一部分 或者 全額 即使 可以 採取 高風險 高 回報 打法 時候 進行 安全 打法</t>
-  </si>
-  <si>
-    <t>Heads-up（單挑）：只有2個玩家玩的撲克游戲稱為「單挑」。 單挑游戲是不規則的撲克形式，將是最激烈的戰鬥。 因為玩家無力等待強牌，所以除了相信自己的打法運氣和發現對手的弱點外，他們別無選擇。</t>
-  </si>
-  <si>
-    <t>Heads - up 單挑 只有 2 個 玩家 玩 撲克游 戲稱 為 單挑 單挑游戲 不 規則 撲克 形式 將是 最 激烈 戰鬥 因為 玩家 無力 等待 強牌 所以 除了 相信 自己 打法 運氣 和 發現 對手 弱點 外 他們 別無選擇</t>
-  </si>
-  <si>
-    <t>Hole cards（手牌）：手牌指的是只有自己可以看見的卡牌。 比如，德州撲克中指的是荷官發給自己的2張牌。</t>
-  </si>
-  <si>
-    <t>Hole cards 手牌 手牌 指 只有 自己 可以 看見 卡牌 比如 德州撲克 中指 荷官 發給 自己 2 張牌</t>
+    <t>grind 安全 打法 安全 打法 指 不願 冒 太大風險 一定 下注 限額 持續 取得 利益 一種 打法 grinder 和 rounder 這兩個術語 指 為 賺取 自己 收入 一部分 或者 全額 即使 可以 採取 高風險 高 回報 打法 時候 進行 安全 打法</t>
+  </si>
+  <si>
+    <t>heads_up（單挑）：只有2個玩家玩的撲克游戲稱為「單挑」。 單挑游戲是不規則的撲克形式，將是最激烈的戰鬥。 因為玩家無力等待強牌，所以除了相信自己的打法運氣和發現對手的弱點外，他們別無選擇。</t>
+  </si>
+  <si>
+    <t>heads_up 單挑 只有 2 個 玩家 玩 撲克游 戲稱 為 單挑 單挑游戲 不 規則 撲克 形式 將是 最 激烈 戰鬥 因為 玩家 無力 等待 強牌 所以 除了 相信 自己 打法 運氣 和 發現 對手 弱點 外 他們 別無選擇</t>
+  </si>
+  <si>
+    <t>hole_cards（手牌）：手牌指的是只有自己可以看見的卡牌。 比如，德州撲克中指的是荷官發給自己的2張牌。</t>
+  </si>
+  <si>
+    <t>hole_cards 手牌 手牌 指 只有 自己 可以 看見 卡牌 比如 德州撲克 中指 荷官 發給 自己 2 張牌</t>
   </si>
   <si>
     <t>Kicker（踢牌）：踢牌者是指組成撲克牌型的5張牌以外的1張牌，但是如果有2手牌具有相等值的牌型組合，則 其作用是確定這2手牌的強弱高下。 因此，少於5張牌型組合的牌才能使用踢牌。 也就是說，僅適用于四條，三條，一對（兩對）和高牌。 如果兩個玩家的手牌相等，則踢牌確定哪個玩家是獲勝者。 最高的踢牌是最強的踢牌。 狹義是有且只有一張踢牌。 也就是說，當兩個玩家的手牌相似時，只有那張踢牌才能決定哪個更強。 如果玩家擁有完全相同的一手牌，則最高的非組合牌將成為踢牌，他們將平分底池。</t>
   </si>
   <si>
-    <t>Kicker 踢牌 踢牌 者 指 組成 撲克 牌型 5 張牌 以外 1 張牌 但是 如果 有 2 手牌 具有 相等值 牌型 組合 則 其 作用 確定 這 2 手牌 強弱 高下 因此 少 於 5 張 牌型 組合 牌 才能 使用 踢牌 就是 說 僅適 用于 四條 三條 一對 兩對 和 高牌 如果 兩個 玩家 手牌 相等 則 踢牌 確定 哪個 玩家 獲勝者 最高 踢牌 最強 踢牌 狹義是 有且 只有 一張 踢牌 就是 說 當兩個 玩家 手牌 相似 時 只有 那張 踢牌 才能 決定 哪個 更強 如果 玩家 擁有 完全相同 一手 牌 則 最高 非 組合牌 將成 為 踢牌 他們將 平分 底池</t>
+    <t>kicker 踢牌 踢牌 者 指 組成 撲克 牌型 5 張牌 以外 1 張牌 但是 如果 有 2 手牌 具有 相等值 牌型 組合 則 其 作用 確定 這 2 手牌 強弱 高下 因此 少 5 張 牌型 組合 牌 才能 使用 踢牌 就是 說 僅適 用于 四條 三條 一對 兩對 和 高牌 如果 兩個 玩家 手牌 相等 則 踢牌 確定 哪個 玩家 獲勝者 最高 踢牌 最強 踢牌 狹義是 有且 只有 一張 踢牌 就是 說 當兩個 玩家 手牌 相似 時 只有 那張 踢牌 才能 決定 哪個 更強 如果 玩家 擁有 完全相同 一手 牌 則 最高 非 組合牌 將成 為 踢牌 他們將 平分 底池</t>
   </si>
   <si>
     <t>Limit（限額）：限額是下注金額或下注額的另一個術語。 例如，NL400是最大買入額為$400的限額以及無限額（NL）的下注結構。</t>
   </si>
   <si>
-    <t>Limit 限額 限額 下注 金額 或 下注 額 另 一個術語 例如 NL400 最大 買入 額為 $ 400 限額 無限額 NL 下注 結構</t>
+    <t>limit 限額 限額 下注 金額 或 下注 額 另 一個術語 例如 nl400 最大 買入 額為 $ 400 限額 無限額 nl 下注 結構</t>
   </si>
   <si>
     <t>Late（後期位）：在游戲中玩家行為順序由莊家的位置決定的情況下，後期位置是指最後兩個位置（關煞位和按鈕位）。 處在這些位置的玩家比其他位置的玩家要有優勢。 因為他們可以在看了其他前面玩家的行動之後自己再採取相應的行動。</t>
   </si>
   <si>
-    <t>Late 後期位 游戲 中 玩家 行為 順序 由 莊家 位置 決定 情況 下 後期位 置 指 最後兩個 位置 關煞位 和 按鈕位 處 這些 位置 玩家 比 其他 位置 玩家 要 有 優勢 因為 他們 可以 看 其他 前面 玩家 行動 之 後 自己 再 採取 相應 行動</t>
+    <t>late 後期位 游戲 中 玩家 行為 順序 莊家 位置 決定 情況 下 後期位 置 指 最後兩個 位置 關煞位 和 按鈕位 處 這些 位置 玩家 比 其他 位置 玩家 要 有 優勢 因為 他們 可以 看 其他 前面 玩家 行動 之 後 自己 再 採取 相應 行動</t>
   </si>
   <si>
     <t>Limp（跟大盲）：在帶有盲注（強制下注）的游戲中，如果玩家將跟大盲注作為第一個動作，則表示玩家想要緩慢進行。 想要跟大盲注，不會選擇加注。</t>
   </si>
   <si>
-    <t>Limp 跟大盲 帶 有 盲注 強制 下注 游戲 中 如果 玩家 將跟 大盲注 作為 第一 個動作 則 表示 玩家 想要 緩慢 進行 想要 跟 大盲注 不會 選擇 加注</t>
-  </si>
-  <si>
-    <t>Middle（中期位）：在游戲中玩家行為順序由莊家的位置決定的情況下，中期位是指從發牌者的角度來看位於桌子中央的人。 例如，在一個德州撲克全額的10人桌中，第6、7和8位稱為中期位，即MP，MP2，MP3。 處于這些位置的玩家對之後的玩家處于劣勢，將與之後的玩家進行戰鬥，但在面對之前的玩家 時處于有利的位置（ 因為可以看到之前的行動）。</t>
-  </si>
-  <si>
-    <t>Middle 中期位 游戲 中 玩家 行為 順序 由 莊家 位置 決定 情況 下 中期位 指 從 發牌 者 角度 來 看位 於 桌子 中央 人 例如 德州撲克 全額 10 人桌 中 第 6 7 和 8 位稱 為 中期位 即 MP MP2 MP3 處于 這些 位置 玩家 對 之 後 玩家 處于 劣勢 將與 之 後 玩家 進行 戰鬥 但 面 對 之前 玩家 時處 于 有利 位置 因為 可以 看到 之前 行動</t>
+    <t>limp 跟大盲 帶 有 盲注 強制 下注 游戲 中 如果 玩家 將跟 大盲注 作為 第一 個動作 則 表示 玩家 想要 緩慢 進行 想要 跟 大盲注 不會 選擇 加注</t>
+  </si>
+  <si>
+    <t>Middle（中期位）：在游戲中玩家行為順序由莊家的位置決定的情況下，中期位是指從發牌者的角度來看位於桌子中央的人。 這些位置的玩家對之後的玩家處于劣勢，面對之前的玩家 時處于有利的位置。</t>
+  </si>
+  <si>
+    <t>middle 中期位 游戲 中 玩家 行為 順序 莊家 位置 決定 情況 下 中期位 指 從 發牌者 角度 來 看位 桌子 中央 人 這些 位置 玩家 對 之 後 玩家 處于 劣勢 面對 之前 玩家 時處 于 有利 位置</t>
   </si>
   <si>
     <t>Muck（棄牌區）：棄牌區指的是撲克桌上所有已使用過的紙牌放置的區域。 它包含所有洗牌卡（在某些時候將最上層的牌去掉）或玩家棄掉的牌。 棄牌區意味著不去看那些牌就放置在那。</t>
   </si>
   <si>
-    <t>Muck 棄牌 區 棄牌 區指 撲克 桌上 所有 已 使用 過的 紙牌 放置 區域 它 包含 所有 洗牌 卡 某些 時 候將 最 上層 牌 去掉 或 玩家 棄掉 牌 棄牌 區 意味著 不去 看 那些 牌 放置 那</t>
-  </si>
-  <si>
-    <t>Nuts（必勝牌）：必勝牌指的是在特定情況下的最強牌。 如果在已發的牌之中，某玩家擁有最好的一手牌，那麼他就是拿到必勝牌。 在某些牌型類別中也使用此術語。 例如必勝同花牌或者必勝順子牌指的是已知牌面中最強的同花或者順子。</t>
-  </si>
-  <si>
-    <t>Nuts 必勝牌 必勝牌 指 特定 情況 下 最 強牌 如果 已發 牌 之中 某 玩家 擁有 最好 一手 牌 那麼 他 就是 拿到 必勝牌 某些 牌型 類別 中 使用 此術語 例如 必勝 同花 牌 或者 必勝 順子 牌指 已知 牌面 中 最強 同花 或者 順子</t>
+    <t>muck 棄牌 區 棄牌 區指 撲克 桌上 所有 已 使用 過的 紙牌 放置 區域 它 包含 所有 洗牌 卡 某些 時 候將 最 上層 牌 去掉 或 玩家 棄掉 牌 棄牌 區 意味著 不去 看 那些 牌 放置 那</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuts（必勝牌）：必勝牌指的是在特定情況下的最強牌。 如果在已發的牌之中，某玩家擁有最好的一手牌，那麼他就是拿到必勝牌。 </t>
+  </si>
+  <si>
+    <t>nuts 必勝牌 必勝牌 指 特定 情況 下 最 強牌 如果 已發 牌 之中 某 玩家 擁有 最好 一手 牌 那麼 他 就是 拿到 必勝牌</t>
   </si>
   <si>
     <t xml:space="preserve">Odds（賠率）：一定數量的聽牌，剩餘1張（可能多於1張）來牌的話就可以形成牌型並使自己的牌型增強 ，發這種牌有一定的概率。 這種概率通常稱為賠率。 </t>
   </si>
   <si>
-    <t>Odds 賠率 一定 數量 聽牌 剩餘 1 張 可能 多 於 1 張 來牌 話 可以 形成 牌型 並使 自己 牌型 增強 發 這種 牌 有 一定 概率 這種 概率 通常 稱為 賠率</t>
-  </si>
-  <si>
-    <t>Outs（出路）：也叫補牌，能夠使玩家在某個階段所有可能獲勝的公共牌。 如口袋對8的玩家需要再獲得一張8，那麼他就有兩個「出路」（兩張不同花色的8）。</t>
-  </si>
-  <si>
-    <t>Outs 出路 叫 補牌 能夠 使 玩家 某個 階段 所有 可能 獲勝 公共牌 如 口袋 對 8 玩家 需要 再 獲得 一張 8 那麼 他 有 兩個 出路 兩張 不同 花色 8</t>
-  </si>
-  <si>
-    <t>Pocket pair（口袋對）：在德州撲克中，口袋對是由兩個玩家的底牌組成的對子牌。 例如，如果玩家有兩個K，便叫做有口袋K。</t>
-  </si>
-  <si>
-    <t>Pocket pair 口袋 對 德州撲克 中 口袋 對 由 兩個 玩家 底牌 組成 對子 牌 例如 如果 玩家 有 兩個 K 便 叫做 有 口袋 K</t>
-  </si>
-  <si>
-    <t>Pot（底池）：底池是一個獎池，包括在成牌過程中進行的所有下注。 如果底池分配在兩個或更多玩家之間，例如，最佳牌型和最差牌型獲勝的高/低局賽事，或者如果兩個或更多玩家拿到相同牌型的話，則稱為平分獎池。</t>
-  </si>
-  <si>
-    <t>Pot 底池 底池 獎池 包括 成牌 過程 中 進行 所有 下注 如果 底池 分配 兩個 或 更 多 玩家 之間 例如 最佳 牌型 和 最差 牌型 獲勝 高 低局 賽事 或者 如果 兩個 或 更 多 玩家 拿到 相同 牌型 話 則稱 為 平分 獎池</t>
-  </si>
-  <si>
-    <t>Pot Limit（底池限注）：底池限制是一種「底池大小必須小於或等於當前底池大小」的下注結構。 下注可以是任何值，但必須小於或等於當前底池大小，但通常大於上次下注或加注的大小。</t>
-  </si>
-  <si>
-    <t>Pot Limit 底池 限注 底池 限制 一種 底池 大小 必須 小 於 或 等 於 當前 底池 大小 下注 結構 下注 可以 任何 值 但 必須 小 於 或 等 於 當前 底池 大小 但 通常 大 於 上次 下注 或 加注 大小</t>
-  </si>
-  <si>
-    <t>Pot Odds（底池賠率）：底池賠率是「可以贏得的獎金」與「獲得獎金的機會所需的成本」之間的比率。 因此，它們是給定賭注的反向成本效益比。</t>
-  </si>
-  <si>
-    <t>Pot Odds 底池 賠率 底池 賠率 可以 贏得 獎金 獲得 獎金 機會 所 需 成本 之間 比率 因此 它們 給定 賭注 反向 成本 效益 比</t>
-  </si>
-  <si>
-    <t>Pre flop（翻牌前）：指的是德州撲克和奧馬哈等游戲中，發出底牌後，公共牌出現以前的第一輪叫注階段。</t>
-  </si>
-  <si>
-    <t>Pre flop 翻牌前 指 德州撲克 和 奧馬哈 等 游戲 中 發出 底牌 後 公共牌 出現 以前 第一 輪 叫注 階段</t>
+    <t>odds 賠率 一定 數量 聽牌 剩餘 1 張 可能 多 1 張 來牌 話 可以 形成 牌型 並使 自己 牌型 增強 發 這種 牌 有 一定 概率 這種 概率 通常 稱為 賠率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outs（出路）：也叫補牌，能夠使玩家在某個階段所有可能獲勝的公共牌。 </t>
+  </si>
+  <si>
+    <t>outs 出路 叫 補牌 能夠 使 玩家 某個 階段 所有 可能 獲勝 公共牌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pocket_pair（口袋對）：在德州撲克中，口袋對是由兩個玩家的底牌組成的對子牌。 </t>
+  </si>
+  <si>
+    <t>pocket_pair 口袋 對 德州撲克 中 口袋 對 兩個 玩家 底牌 組成 對子 牌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pot（底池）：底池是一個獎池，包括在成牌過程中進行的所有下注。 </t>
+  </si>
+  <si>
+    <t>pot 底池 底池 獎池 包括 成牌 過程 中 進行 所有 下注</t>
+  </si>
+  <si>
+    <t>Pot_Limit（底池限注）：底池限制是一種「底池大小必須小於或等於當前底池大小」的下注結構。 下注可以是任何值，但必須小於或等於當前底池大小，但通常大於上次下注或加注的大小。</t>
+  </si>
+  <si>
+    <t>pot_limit 底池 限注 底池 限制 一種 底池 大小 必須 小於 或 等於 當前 底池 大小 下注 結構 下注 可以 任何 值 但 必須 小於 或 等於 當前 底池 大小 但 通常 大於 上次 下注 或 加注 大小</t>
+  </si>
+  <si>
+    <t>pot_odds（底池賠率）：底池賠率是「可以贏得的獎金」與「獲得獎金的機會所需的成本」之間的比率。 因此，它們是給定賭注的反向成本效益比。</t>
+  </si>
+  <si>
+    <t>pot_odds 底池 賠率 底池 賠率 可以 贏得 獎金 獲得 獎金 機會 所 需 成本 之間 比率 因此 它們 給定 賭注 反向 成本 效益 比</t>
+  </si>
+  <si>
+    <t>Pre_flop（翻牌前）：指的是德州撲克和奧馬哈等游戲中，發出底牌後，公共牌出現以前的第一輪叫注階段。</t>
+  </si>
+  <si>
+    <t>pre_flop 翻牌前 指 德州撲克 和 奧馬哈 等 游戲 中 發出 底牌 後 公共牌 出現 以前 第一 輪 叫注 階段</t>
   </si>
   <si>
     <t>Raise（加注）：加注是當一個玩家面對另一位玩家的下注時他可以採取的動作。 加注是超過對手下注金額的下注。 每輪加注的數量和大小可能會根據每個地方的規則而受到不同限制。 通常，每輪下注允許3，4或5次（5次不常見）加注。 再次加注到對手的加注時，該加注稱為再加注。</t>
   </si>
   <si>
-    <t>Raise 加注 加注 當一個 玩家 面對 另 一位 玩家 下注 時 他 可以 採取 動作 加注 超過 對手 下注 金額 下注 每輪 加注 數量 和 大小 可能 會 每個 地方 規則 受到 不同 限制 通常 每輪 下注 允許 3 4 或 5 次 5 次 不常見 加注 再次 加注 到 對手 加注 時 該 加注 稱為 再 加注</t>
-  </si>
-  <si>
-    <t>Re-raise（再加注）：再加注是在另一位玩家已經加注之後加注。 如果一位玩家下注，第二位玩家加注，而第三位玩家在轉牌上加注，則第三位玩家算是再加注。</t>
-  </si>
-  <si>
-    <t>Re - raise 再 加注 再 加注 另 一位 玩家 已經 加注 之 後 加注 如果 一位 玩家 下注 第二位 玩家 加注 第三位 玩家 轉牌 上 加注 則 第三位 玩家 算是 再 加注</t>
+    <t>raise 加注 加注 當一個 玩家 面對 另 一位 玩家 下注 時 他 可以 採取 動作 加注 超過 對手 下注 金額 下注 每輪 加注 數量 和 大小 可能 會 每個 地方 規則 受到 不同 限制 通常 每輪 下注 允許 3 4 或 5 次 5 次 不常見 加注 再次 加注 到 對手 加注 時 該 加注 稱為 再 加注</t>
+  </si>
+  <si>
+    <t>Re_raise（再加注）：再加注是在另一位玩家已經加注之後加注。 如果一位玩家下注，第二位玩家加注，而第三位玩家在轉牌上加注，則第三位玩家算是再加注。</t>
+  </si>
+  <si>
+    <t>re_raise 再 加注 再 加注 另 一位 玩家 已經 加注 之 後 加注 如果 一位 玩家 下注 第二位 玩家 加注 第三位 玩家 轉牌 上 加注 則 第三位 玩家 算是 再 加注</t>
   </si>
   <si>
     <t>River（河牌）：德州撲克和奧馬哈等游戲中，第5張公共牌叫河牌。</t>
   </si>
   <si>
-    <t>River 河牌 德州撲克 和 奧馬哈 等 游戲 中 第 5 張 公共牌 叫 河牌</t>
-  </si>
-  <si>
-    <t>Rag（廢牌）：廢牌指的是沒有價值或很弱的牌。 例如，在德州撲克中，擁有一張A和一張低牌（例如4等）的起手牌被表示為A廢牌。</t>
-  </si>
-  <si>
-    <t>Rag 廢牌 廢牌 指 沒 有 價值 或 很 弱 牌 例如 德州撲克 中 擁有 一張 A 和 一張 低牌 例如 4 等 起 手牌 表示 為 A 廢牌</t>
-  </si>
-  <si>
-    <t>Rake（抽水）：抽水指的是每局要固定從獎池中抽取一定比例給賭場等。 收取抽水的牌型稱作抽水牌。 抽水取決於各種條件。 通常，如果超過某個金額限制，將抽出5％的底池作為抽水。 每手最大抽水也根據特定規則和賭注進行控制。 如果牌局沒有進行到翻牌階段，則不會收取抽水。 這也稱為「不翻牌，不抽水」。</t>
-  </si>
-  <si>
-    <t>Rake 抽水 抽水 指 每局 要 固定 從 獎池 中 抽取 一定 比例 給賭場 等 收取 抽水 牌型 稱作 抽水 牌 抽水 取決 於 各種 條件 通常 如果 超過 某個 金額 限制 將 抽出 5 ％ 底 池作 為 抽水 每手 最大 抽水 特定 規則 和 賭注 進行 控制 如果 牌局 沒有 進行 到 翻牌 階段 則不會 收取 抽水 這也稱 為 不 翻牌 不 抽水</t>
+    <t>river 河牌 德州撲克 和 奧馬哈 等 游戲 中 第 5 張 公共牌 叫 河牌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rag（廢牌）：廢牌指的是沒有價值或很弱的牌。 </t>
+  </si>
+  <si>
+    <t>rag 廢牌 廢牌 指 沒 有 價值 或 很 弱 牌</t>
+  </si>
+  <si>
+    <t>Rake（抽水）：抽水指的是每局要固定從獎池中抽取一定比例給賭場等。 如果牌局沒有進行到翻牌階段，則不會收取抽水。</t>
+  </si>
+  <si>
+    <t>rake 抽水 抽水 指 每局 要 固定 從 獎池 中 抽取 一定 比例 給賭場 等 如果 牌局 沒有 進行 到 翻牌 階段 則不會 收取 抽水</t>
   </si>
   <si>
     <t>Rock（石頭）：石頭指的是持保守態度的玩家，只有在拿到很少的幾手強牌的時候才入池。 他的策略是「只打最強的牌」，但是當拿到期望值很高的強牌時，即使很可能輸掉，也只能保持積極的態度打下去。</t>
   </si>
   <si>
-    <t>Rock 石頭 石頭 指 持 保守 態度 玩家 只有 拿到 很少 幾手 強牌 時候 才 入池 他 策略 只 打 最強 牌 但是 當 拿到 期望值 很 高 強牌 時 即使 很 可能 輸掉 只能 保持 積極 態度 打 下去</t>
-  </si>
-  <si>
-    <t>Ring game（現金桌）：現金桌是在賭場中始終開放的賭桌，您可以在這裡持籌碼坐下並以該賭桌的速度持續 玩游戲。 玩家可以自由進入游戲並站起。 如果您想以較低或較高的速度進行游戲，則必須移動桌子。</t>
-  </si>
-  <si>
-    <t>Ring game 現金桌 現金桌 賭場 中始 終開 放 賭桌 您 可以 這裡持 籌碼 坐下 並以 該 賭桌 速度 持續 玩游 戲 玩家 可以 自由 進入 游戲 並站 起 如果 您 想 以 較 低 或 較 高 速度 進行 游戲 則必須 移動 桌子</t>
+    <t>rock 石頭 石頭 指 持 保守 態度 玩家 只有 拿到 很少 幾手 強牌 時候 才 入池 他 策略 只 打 最強 牌 但是 當 拿到 期望值 很 高 強牌 時 即使 很 可能 輸掉 只能 保持 積極 態度 打 下去</t>
+  </si>
+  <si>
+    <t>Ring_game（現金桌）：現金桌是在賭場中始終開放的賭桌，您可以在這裡持籌碼坐下並以該賭桌的速度持續 玩游戲。 玩家可以自由進入游戲並站起。 如果您想以較低或較高的速度進行游戲，則必須移動桌子。</t>
+  </si>
+  <si>
+    <t>ring_game 現金桌 現金桌 賭場 中始 終開 放 賭桌 您 可以 這裡持 籌碼 坐下 並以 該 賭桌 速度 持續 玩游 戲 玩家 可以 自由 進入 游戲 並站 起 如果 您 想 較 低 或 較 高 速度 進行 游戲 則必須 移動 桌子</t>
   </si>
   <si>
     <t>Shark（鯊魚）：鯊魚指的是桌上的強大且採取積極打法的玩家。 鯊魚攻擊弱小的玩家並從中盈利。</t>
   </si>
   <si>
-    <t>Shark 鯊魚 鯊魚 指 桌上 強大且 採取 積極 打法 玩家 鯊魚 攻擊 弱小 玩家 並從 中 盈利</t>
+    <t>shark 鯊魚 鯊魚 指 桌上 強大且 採取 積極 打法 玩家 鯊魚 攻擊 弱小 玩家 並從 中 盈利</t>
   </si>
   <si>
     <t>Showdown（亮牌）：亮牌是牌型（游戲）的最後部分，剩餘玩家展示自己的牌，並決定誰擁有最好的牌以及誰贏得底池。 亮牌將一樣在最後一輪下注之後進行。</t>
   </si>
   <si>
-    <t>Showdown 亮牌 亮牌 牌型 游戲 最 後 部分 剩餘 玩家 展示 自己 牌 並決定 誰 擁有 最好 牌 誰 贏得 底池 亮牌 將一樣 最後一輪 下注 之後進行</t>
+    <t>showdown 亮牌 亮牌 牌型 游戲 最 後 部分 剩餘 玩家 展示 自己 牌 並決定 誰 擁有 最好 牌 誰 贏得 底池 亮牌 將一樣 最後一輪 下注 之後進行</t>
   </si>
   <si>
     <t>Slowplay（慢打）：慢打指的是「為了使對手消除警惕，拿到強牌的時候也故意採取消極示弱的打法」，「給人以為是弱牌的印象」或「讓對手誤以 為自己拿到的是最強牌」 的戰略戰術。</t>
   </si>
   <si>
-    <t>Slowplay 慢打 慢打 指 為 使 對手 消除 警惕 拿到 強牌 時候 故意 採 取消 極 示弱 打法 給人以 為 弱牌 印象 或 讓 對手 誤以 為 自己 拿到 最 強牌 戰略 戰術</t>
-  </si>
-  <si>
-    <t>Side Pot（邊池）：邊池是指用全押玩家的牌局中放在側面的底池。 牌局的主要底池是指所有活躍玩家都能獲得的底池。 如果一名玩家全押並且至少有兩名對手仍在賽事中並且他們不是全押，則所有隨後的下注都放在邊池中，而不是全押的玩家可以獲得。</t>
-  </si>
-  <si>
-    <t>Side Pot 邊池 邊池 指用 全押 玩家 牌局 中 放在 側面 底池 牌局 主要 底池 指 所有 活躍 玩家 能 獲得 底池 如果 一名 玩家 全押 並且 至少 有 兩名 對手 仍 賽事 中 並且 他們 不是 全押 則 所有 隨後的 下注 放在 邊池 中 不是 全押 玩家 可以 獲得</t>
-  </si>
-  <si>
-    <t>Semi bluff（半詐牌）：半詐牌指的是用目前較弱但有可能發展成強牌的手牌進行虛張聲勢。 半詐牌的目標不一定是淘汰所有對手。 因為如果在亮牌為止完成牌型，仍然有機會獲得底池。 因此，半詐牌的目的之一是在早期下注中將籌碼盡可能收集到底池中，以增加可能獲得的籌碼。 這一舉動是有益的，因為對手很可能棄牌並且自己可能可以贏得一個大底池。 半詐牌適用的典型情況是當自己在聽牌的時候，如果發出了適當的牌，將很可能形成牌型。</t>
-  </si>
-  <si>
-    <t>Semi bluff 半詐牌 半詐牌 指 用 目前 較弱 但 有 可能 發展 成 強牌 手牌 進行 虛張 聲勢 半詐牌 目標 不 一定 淘汰 所有 對手 因為 如果 亮牌 為止 完成 牌型 仍然 有 機會 獲得 底池 因此 半詐牌 目的 之一 早期 下注 中將 籌碼 盡 可能 收集 到底 池中 以 增加 可能 獲得 籌碼 這一 舉動 有益 因為 對手 很 可能 棄牌 並且 自己 可能 可以 贏得 大底 池 半詐牌 適用 典型 情況 是當 自己 聽牌 時候 如果 發出 適當 牌 將 很 可能 形成 牌型</t>
-  </si>
-  <si>
-    <t>Starting hand chat（起始手牌表）：起始手牌表是可以入池的手牌的概率表格歸納，並說明瞭根據這些手要採取的操作。 SHC（起始手牌表）對于初學者在第一輪下注中制定策略特別有用。</t>
-  </si>
-  <si>
-    <t>Starting hand chat 起始 手牌表 起始 手牌 表是 可以 入池 手牌 概率 表格 歸納 並說明 瞭根據 這些 手要 採取 操作 SHC 起始 手牌表 對于 初學者 第一 輪 下注 中 制定 策略 特別 有用</t>
+    <t>slowplay 慢打 慢打 指 為 使 對手 消除 警惕 拿到 強牌 時候 故意 採 取消 極 示弱 打法 給人以 為 弱牌 印象 或 讓 對手 誤以 為 自己 拿到 最 強牌 戰略 戰術</t>
+  </si>
+  <si>
+    <t>side_pot（邊池）：邊池是指用全押玩家的牌局中放在側面的底池。 牌局的主要底池是指所有活躍玩家都能獲得的底池。 如果一名玩家全押並且至少有兩名對手仍在賽事中並且他們不是全押，則所有隨後的下注都放在邊池中，而不是全押的玩家可以獲得。</t>
+  </si>
+  <si>
+    <t>side_pot 邊池 邊池 指用 全押 玩家 牌局 中 放在 側面 底池 牌局 主要 底池 指 所有 活躍 玩家 能 獲得 底池 如果 一名 玩家 全押 並且 至少 有 兩名 對手 仍 賽事 中 並且 他們 不是 全押 則 所有 隨後的 下注 放在 邊池 中 不是 全押 玩家 可以 獲得</t>
+  </si>
+  <si>
+    <t>Semi_bluff（半詐牌）：半詐牌指的是用目前較弱但有可能發展成強牌的手牌進行虛張聲勢。 半詐牌的目標不一定是淘汰所有對手。 因為如果在亮牌為止完成牌型，仍然有機會獲得底池。 因此，半詐牌的目的之一是在早期下注中將籌碼盡可能收集到底池中，以增加可能獲得的籌碼。 這一舉動是有益的，因為對手很可能棄牌並且自己可能可以贏得一個大底池。 半詐牌適用的典型情況是當自己在聽牌的時候，如果發出了適當的牌，將很可能形成牌型。</t>
+  </si>
+  <si>
+    <t>semi_bluff 半詐牌 半詐牌 指 用 目前 較弱 但 有 可能 發展 成 強牌 手牌 進行 虛張 聲勢 半詐牌 目標 不 一定 淘汰 所有 對手 因為 如果 亮牌 為止 完成 牌型 仍然 有 機會 獲得 底池 因此 半詐牌 目的 之一 早期 下注 中將 籌碼 盡 可能 收集 到底 池中 增加 可能 獲得 籌碼 這一 舉動 有益 因為 對手 很 可能 棄牌 並且 自己 可能 可以 贏得 大底 池 半詐牌 適用 典型 情況 是當 自己 聽牌 時候 如果 發出 適當 牌 將 很 可能 形成 牌型</t>
+  </si>
+  <si>
+    <t>Starting_hand_chat（起始手牌表）：起始手牌表是可以入池的手牌的概率表格歸納，並說明瞭根據這些手要採取的操作。 SHC（起始手牌表）對于初學者在第一輪下注中制定策略特別有用。</t>
+  </si>
+  <si>
+    <t>starting_hand_chat 起始 手牌表 起始 手牌 表是 可以 入池 手牌 概率 表格 歸納 並說明 瞭根據 這些 手要 採取 操作 shc 起始 手牌表 對于 初學者 第一 輪 下注 中 制定 策略 特別 有用</t>
   </si>
   <si>
     <t>Streak（連運）：連運指的是牌局中連著幸運贏牌或連著厄運輸牌的情況。</t>
   </si>
   <si>
-    <t>Streak 連運 連運指 牌局 中連著 幸運 贏牌 或 連著 厄 運輸牌 情況</t>
+    <t>streak 連運 連運指 牌局 中連著 幸運 贏牌 或 連著 厄 運輸牌 情況</t>
   </si>
   <si>
     <t>Turn（轉牌）：德州撲克或奧馬哈等有使用公共牌的游戲中，第4張公共牌稱作轉牌。</t>
   </si>
   <si>
-    <t>Turn 轉牌 德州撲克 或 奧馬哈 等 有 使用 公共牌 游戲 中 第 4 張 公共牌 稱作 轉牌</t>
+    <t>turn 轉牌 德州撲克 或 奧馬哈 等 有 使用 公共牌 游戲 中 第 4 張 公共牌 稱作 轉牌</t>
   </si>
   <si>
     <t>Tell（小動作）：小動作是指玩家無意間透露出來的一些下意識的動作，這些動作有可能讓他輸掉。 其中也包括有意識的動作。 比如發現對方正在觀察自己的時候刻意作出一些假動作演技讓對手作出錯誤判斷。</t>
   </si>
   <si>
-    <t>Tell 小動作 小動作 指 玩家 無意間 透露 出來 一些 下意識 動作 這些 動作 有 可能 讓 他 輸掉 其中 包括 有意 識 動作 比如 發現 對 方正 觀察 自己 時候 刻意 作出 一些 假動作 演技 讓 對手 作出 錯誤 判斷</t>
+    <t>tell 小動作 小動作 指 玩家 無意間 透露 出來 一些 下意識 動作 這些 動作 有 可能 讓 他 輸掉 其中 包括 有意 識 動作 比如 發現 對 方正 觀察 自己 時候 刻意 作出 一些 假動作 演技 讓 對手 作出 錯誤 判斷</t>
   </si>
   <si>
     <t xml:space="preserve">Tilt（上頭）：上頭指的是指玩家無法做出合理判斷，出現了一些情緒化的狀態。 </t>
   </si>
   <si>
-    <t>Tilt 上頭 上頭 指 指 玩家 無法 做出 合理 判斷 出現 一些 情緒化 狀態</t>
+    <t>tilt 上頭 上頭 指 指 玩家 無法 做出 合理 判斷 出現 一些 情緒化 狀態</t>
   </si>
   <si>
     <t>Tournament（賽事）：撲克賽事是一種游戲形式，每個玩家都可以通過買入來參加賽事。 每個玩家最初獲得相同數量的籌碼，如果輸掉了手上所有籌碼，就輸掉了賽事。 在可重購的賽事中，玩家可以在初始階段再次買入。 獎金是根據贏得賽事的玩家的排名分配的。 根據特定的支出結構，確定獲得多少獎金。 當然，可以使用金錢以外的獎品。</t>
   </si>
   <si>
-    <t>Tournament 賽事 撲克賽 事 一種 游戲 形式 每個 玩家 可以 通過 買入 來 參加賽 事 每個 玩家 最初 獲得 相同 數量 籌碼 如果 輸掉 手上 所有 籌碼 輸掉 賽事 可 重購 賽事 中 玩家 可以 初始 階段 再次 買入 獎金 贏得賽 事 玩家 排名 分配 特定 支出 結構 確定 獲得 多少 獎金 當然 可以 使用 金錢 以外 獎品</t>
-  </si>
-  <si>
-    <t>UTG(under the gun)（槍口位）：大盲注左手邊第一個為槍口位，翻牌前最先行動，在德州撲克裡位置越靠後越有利，因此坐在槍口位的玩家是最被動的玩家，由於起手牌要求比其他位置都要高，往往會翻牌前棄牌。</t>
-  </si>
-  <si>
-    <t>UTG ( under the gun ) 槍口位 大盲注 左手 邊 第一 個 為 槍口位 翻牌前 最先 行動 德州撲克 裡 位置 越靠後越 有利 因此 坐在 槍口位 玩家 最 動 玩家 由 於 起 手牌 要求 比 其他 位置 要 高 往往 會 翻牌前 棄牌</t>
+    <t>tournament 賽事 撲克賽 事 一種 游戲 形式 每個 玩家 可以 通過 買入 來 參加賽 事 每個 玩家 最初 獲得 相同 數量 籌碼 如果 輸掉 手上 所有 籌碼 輸掉 賽事 可 重購 賽事 中 玩家 可以 初始 階段 再次 買入 獎金 贏得賽 事 玩家 排名 分配 特定 支出 結構 確定 獲得 多少 獎金 當然 可以 使用 金錢 以外 獎品</t>
+  </si>
+  <si>
+    <t>UTG(Under_the_Gun)（槍口位）：大盲注左手邊第一個為槍口位，翻牌前最先行動，在德州撲克裡位置越靠後越有利，因此坐在槍口位的玩家是最被動的玩家，由於起手牌要求比其他位置都要高，往往會翻牌前棄牌。</t>
+  </si>
+  <si>
+    <t>utg under_the_gun 槍口位 大盲注 左手 邊 第一 個 為 槍口位 翻牌前 最先 行動 德州撲克 裡 位置 越靠後越 有利 因此 坐在 槍口位 玩家 最 動 玩家 起 手牌 要求 比 其他 位置 要 高 往往 會 翻牌前 棄牌</t>
   </si>
   <si>
     <t>概率與賠率的基本概念：概率是自己擊中公共牌後能贏的機率；賠率是投入籌碼和贏回籌碼之間的比例。打牌不算概率幾乎是在瞎玩，概率和賠率就是幫你做正確決定的工具。</t>
@@ -879,46 +891,46 @@
     <t>概率 賠率 基本概念 概率 自己 擊中 公共牌 後 能贏 機率 賠率 投入 籌碼 和 贏回 籌碼 之間 比例 打牌 不算 概率 幾乎 瞎 玩 概率 和 賠率 就是 幫 你 做 正確 決定 工具</t>
   </si>
   <si>
-    <t>Outs (出路) 與 42 定律：第一步，數能贏的牌叫做 Outs（出路）。第二步，算概率。簡單算法是「42 定律」：在發出翻牌之後，能贏的概率是用你能贏的牌的張數乘以 4；在轉牌後，用你能贏的數量乘以 2。這是因為未知的牌大約剩 50 張左右（46或47張）所換算出的百分比捷徑。</t>
-  </si>
-  <si>
-    <t>Outs ( 出路 ) 42 定律 第一步 數能贏 牌 叫做 Outs 出路 第二步 算 概率 簡單 算法 42 定律 發出 翻牌 之 後 能贏 概率 用 你 能贏 牌 張數 乘以 4 轉牌 後 用 你 能贏 數量 乘以 2 這是 因為 未知 牌大約 剩 50 張 左右 46 或 47 張 所換 算出 百分比 捷徑</t>
-  </si>
-  <si>
-    <t>賠率計算與決策應用：賠率是你要付出的籌碼和已經在底池裡籌碼的比例。例如底池 100，對手下注 50（底池變 150），你跟注 50 去贏 150，賠率就是 1:3（25%）。拿賠率對比算出來的概率，如果贏的概率高於投入的賠率，數學上就應該跟注；反之則棄牌。</t>
-  </si>
-  <si>
-    <t>賠率 計算 決策 應用 賠率 你 要 付出 籌碼 和 已經 底 池裡 籌碼 比例 例如 底池 100 對手 下注 50 底池 變 150 你 跟注 50 去贏 150 賠率 就是 1 : 3 25% 拿 賠率 對 比算 出來 概率 如果 贏的 概率 高 於 投入 賠率 數學 上 應該 跟注 反之 則 棄牌</t>
-  </si>
-  <si>
-    <t>隱含賠率 (Implied Odds)：當單算賠率不足以跟注時，需考慮對手後手的籌碼。當你確定發出你要的牌（中牌）後，對手會支付他後手還不在底池裡的籌碼時，就可以把這些籌碼預先算入你能贏的底池中來重新計算賠率。這通常適用於對手牌力極強（如 AA）而難以棄牌的情況。</t>
-  </si>
-  <si>
-    <t>隱含 賠率 ( Implied Odds ) 當單 算 賠率 不足以 跟注 時 需考慮 對手 後 手 籌碼 當你 確定 發出 你 要 牌 中牌 後 對手 會 支付 他後手 還不在 底 池裡 籌碼 時 可以 把 這些 籌碼 預先 算入 你 能贏 底池 中來 重新 計算 賠率 這 通常 適用 於 對手 牌力 極強 如 AA 難以 棄牌 情況</t>
-  </si>
-  <si>
-    <t>棄牌率 (Fold Equity)：即使目前牌力落後，但透過再加注等激進打法，讓對手覺得自己牌力不夠大而選擇蓋牌的機率。打棄牌率對於玩家的讀牌能力有一定要求，讀對手牌力範圍越準，就越能找到詐唬（偷雞）的時機。</t>
-  </si>
-  <si>
-    <t>棄牌 率 ( Fold Equity ) 即使 目前 牌力 落 後 但 透過 再 加注 等 激進 打法 讓 對手 覺得 自己 牌力 不夠 大 選擇 蓋牌 機率 打 棄牌 率 對 於 玩家 讀牌 能力 有 一定 要求 讀 對手 牌力 範圍 越準 越 能 找到 詐唬 偷雞 時機</t>
+    <t>Outs (出路) 與2與4法則：數能贏的牌叫做 Outs（出路）。算概率。簡單算法是2與4法則：在發出翻牌之後，能贏的概率是用你能贏的牌的張數乘以 4；在轉牌後，用你能贏的數量乘以 2。這是因為未知的牌大約剩 50 張左右所換算出的百分比捷徑。</t>
+  </si>
+  <si>
+    <t>outs 出路 2與4法則 數能贏 牌 叫做 outs 出路 算 概率 簡單 算法 2與4法則 發出 翻牌 之 後 能贏 概率 用 你 能贏 牌 張數 乘以 4 轉牌 後 用 你 能贏 數量 乘以 2 這是 因為 未知 牌大約 剩 50 張 左右 所換 算出 百分比 捷徑</t>
+  </si>
+  <si>
+    <t>賠率計算與決策應用：賠率是你要付出的籌碼和已經在底池裡籌碼的比例。拿賠率對比算出來的概率，如果贏的概率高於投入的賠率，數學上就應該跟注；反之則棄牌。</t>
+  </si>
+  <si>
+    <t>賠率 計算 決策 應用 賠率 你 要 付出 籌碼 和 已經 底 池裡 籌碼 比例 拿 賠率 對 比算 出來 概率 如果 贏的 概率 高 投入 賠率 數學 上 應該 跟注 反之 則 棄牌</t>
+  </si>
+  <si>
+    <t>隱含賠率 (Implied_Odds)：當單算賠率不足以跟注時，需考慮對手後手的籌碼。當你確定發出你要的牌（中牌）後，對手會支付他後手還不在底池裡的籌碼時，就可以把這些籌碼預先算入你能贏的底池中來重新計算賠率。這通常適用於對手牌力極強而難以棄牌的情況。</t>
+  </si>
+  <si>
+    <t>隱含 賠率 implied_odds 當單 算 賠率 不足以 跟注 時 需考慮 對手 後 手 籌碼 當你 確定 發出 你 要 牌 中牌 後 對手 會 支付 他後手 還不在 底 池裡 籌碼 時 可以 把 這些 籌碼 預先 算入 你 能贏 底池 中來 重新 計算 賠率 這 通常 適用 對手 牌力 極強 難以 棄牌 情況</t>
+  </si>
+  <si>
+    <t>棄牌率 (Fold_Equity)：即使目前牌力落後，但透過再加注等激進打法，讓對手覺得自己牌力不夠大而選擇蓋牌的機率。打棄牌率對於玩家的讀牌能力有一定要求，讀對手牌力範圍越準，就越能找到詐唬（偷雞）的時機。</t>
+  </si>
+  <si>
+    <t>棄牌 率 fold_equity 即使 目前 牌力 落 後 但 透過 再 加注 等 激進 打法 讓 對手 覺得 自己 牌力 不夠 大 選擇 蓋牌 機率 打 棄牌 率 對 玩家 讀牌 能力 有 一定 要求 讀 對手 牌力 範圍 越準 越 能 找到 詐唬 偷雞 時機</t>
   </si>
   <si>
     <t>範圍與範圍優勢：在撲克對抗中，範圍是不可忽略的因素。翻牌前在前位（如槍口位 UTG）加注（Raise）的人，通常會被認為牌力範圍很強（例如範圍內包含最大的同花 A）。玩家可以有效地利用自己的範圍優勢來進行詐唬（偷雞），前提是對手也具備解讀範圍的能力。</t>
   </si>
   <si>
-    <t>範圍 範圍 優勢 撲克 對 抗中 範圍 不可 忽略 因素 翻牌前 前位 如 槍口位 UTG 加注 Raise 人 通常 會 認為 牌力 範圍 很強 例如 範圍 內 包含 最大 同花 A 玩家 可以 有效 地 利用 自己 範圍 優勢 來 進行 詐唬 偷雞 前提 對手 具備 解讀 範圍 能力</t>
+    <t>範圍 範圍 優勢 撲克 對 抗中 範圍 不可 忽略 因素 翻牌前 前位 如 槍口位 utg 加注 raise 人 通常 會 認為 牌力 範圍 很強 例如 範圍 內 包含 最大 同花 a 玩家 可以 有效 地 利用 自己 範圍 優勢 來 進行 詐唬 偷雞 前提 對手 具備 解讀 範圍 能力</t>
   </si>
   <si>
     <t>翻牌前動作與範圍判斷：翻牌前起 Raise 的人，其範圍是「無上限」的（包含 AA、KK 等）。相反地，面對加注卻只是選擇跟注（沒有 3bet）的玩家，通常會被認為排除了最頂級的牌力，範圍主要集中在中等牌力，因為拿大牌通常會選擇 3bet 來避免給後面玩家太好的賠率。</t>
   </si>
   <si>
-    <t>翻牌前 動作 範圍 判斷 翻牌前 起 Raise 人 其範圍 無 上限 包含 AA KK 等 相反 地 面對 加注 卻 只是 選擇 跟注 沒有 3bet 玩家 通常 會 認為 排除 最 頂級 牌力 範圍 主要 集中 中等 牌力 因為 拿 大牌 通常 會選擇 3bet 來 避免 給後面 玩家 太好 賠率</t>
-  </si>
-  <si>
-    <t>3bet 的作用與好處：當拿到一、二等強牌時，面對前位加注強烈建議進行 3bet。好處包含：1. 利用位置優勢搶奪主動權，讓翻牌後更容易打；2. 把自己的範圍擴大並維持在最高範圍；3. 隔離後面牌力較弱的玩家入池。</t>
-  </si>
-  <si>
-    <t>3bet 作用 好 處 當 拿到 一 二等 強牌 時 面對 前位 加注 強烈 建議 進行 3bet 好處 包含 1 . 利用 位置 優勢 搶 奪主動權 讓 翻牌後 更 容易 打 2 . 把 自己 範圍 擴大 並維持 最高 範圍 3 . 隔離後面 牌力 較 弱 玩家 入池</t>
+    <t>翻牌前 動作 範圍 判斷 翻牌前 起 raise 人 其範圍 無 上限 包含 aa kk 等 相反 地 面對 加注 卻 只是 選擇 跟注 沒有 3bet 玩家 通常 會 認為 排除 最 頂級 牌力 範圍 主要 集中 中等 牌力 因為 拿 大牌 通常 會選擇 3bet 來 避免 給後面 玩家 太好 賠率</t>
+  </si>
+  <si>
+    <t>3bet 的作用與好處：當拿到一、二等強牌時，面對前位加注強烈建議進行 3bet。好處包含：利用位置優勢搶奪主動權，讓翻牌後更容易打；把自己的範圍擴大並維持在最高範圍；隔離後面牌力較弱的玩家入池。</t>
+  </si>
+  <si>
+    <t>3bet 作用 好 處 當 拿到 一 二等 強牌 時 面對 前位 加注 強烈 建議 進行 3bet 好處 包含 利用 位置 優勢 搶 奪主動權 讓 翻牌後 更 容易 打 把 自己 範圍 擴大 並維持 最高 範圍 隔離後面 牌力 較 弱 玩家 入池</t>
   </si>
   <si>
     <t>大盲位的底端範圍：當翻牌前已有多人入池，大盲位玩家因為擁有極佳的賠率而選擇最後跟注時，其範圍通常沒有頂端牌力（否則會選擇加注），但包含了極廣的「底端範圍」（各種小牌）。因此，當翻牌發出如 4、5、6 這類小牌面時，大盲位反而是最有可能擊中牌面的人。</t>
@@ -930,7 +942,23 @@
     <t>形象 (Image) 對詐唬的影響：偷雞能否成功，除了合理的範圍建構外，「形象」也是關鍵因素。如果玩家平時打法非常兇且具創造性，對手較容易去抓他的詐唬；但如果是同樣的範圍操作換成形象不同的玩家來打，對手極可能就會選擇棄牌。</t>
   </si>
   <si>
-    <t>形象 ( Image ) 對 詐唬 影響 偷雞 能否 成功 除了 合理 範圍 建構 外 形象 關鍵 因素 如果 玩家 平時 打法 非常 兇且 具創 造性 對手 較 容易 去 抓 他 詐唬 但 如果 同樣 範圍 操作 換成 形象 不同 玩家 來 打 對手 極 可能 就會 選擇 棄牌</t>
+    <t>形象 image 對 詐唬 影響 偷雞 能否 成功 除了 合理 範圍 建構 外 形象 關鍵 因素 如果 玩家 平時 打法 非常 兇且 具創 造性 對手 較 容易 去 抓 他 詐唬 但 如果 同樣 範圍 操作 換成 形象 不同 玩家 來 打 對手 極 可能 就會 選擇 棄牌</t>
+  </si>
+  <si>
+    <t>德州撲克 最常見 三個 變種 為 限注 limit 無限注 no _ limit 和 彩池限注 pot_limit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最佳 五張牌 組合 打公牌 play _ the _ board 玩家 需從 手裡 2 張手牌 加上 桌面 5 張 公共牌 共 7 張牌 中選出 任意 5 張 做出 最大 牌型 組合 這 5 張牌 可以 手裡 2 張加 桌面 3 張 或是 手裡 1 張加 桌面 4 張 若 桌面 5 張 公共牌 已 最大 組合 可以 完全 不 使用 手牌 稱為 打公牌 play _ the _ board</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>翻牌前 後 行動 順序 選項 翻牌前 pre_flop 因為 盲注 已 下注 大盲注 左側 槍口位 utg 第一 個 行動 可選擇 棄牌 fold 跟注 call 或 加注 raise 翻牌後 post _ flop 則由 小盲位 開始 行動 若該 下注圈 尚未 有人 下注 玩家 多出 過牌 check 選擇 若 前方 已經 有人 下注 或 加注 則後方 玩家 不能 選擇 過牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>叫注 叫 說 話 ･ 讓 牌 - 無 需 跟 進 情況 下 選擇 把 決定 讓 給下 一位 ･ 押注 - 押 上 籌碼 ･ 棄牌 - 放棄 繼續 牌局 機會 ･ 加注 - 其他 玩家 下注 後 把 現有 注金 抬高 ･ 跟 進 - 跟 隨眾 人 押 上 同等 注額 ･ 全押 - 一次 過把 手上 籌碼 全押 上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1280,14 +1308,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B151"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B155"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.69921875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="57.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="100.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1295,7 +1322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1303,7 +1330,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1311,7 +1338,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1319,7 +1346,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1327,7 +1354,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1335,7 +1362,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="87" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -1343,7 +1370,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="63" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1351,7 +1378,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -1359,7 +1386,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -1367,7 +1394,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -1375,7 +1402,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -1383,7 +1410,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="58" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="63" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -1391,1108 +1418,1140 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="29" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="1" t="s">
+    </row>
+    <row r="16" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="1" t="s">
+    </row>
+    <row r="17" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="B17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="1" t="s">
+    </row>
+    <row r="18" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="B18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="1" t="s">
+    </row>
+    <row r="19" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="B19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="1" t="s">
+    </row>
+    <row r="20" spans="1:2" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="1" t="s">
+    </row>
+    <row r="21" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="1" t="s">
+    </row>
+    <row r="22" spans="1:2" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="1" t="s">
+    </row>
+    <row r="23" spans="1:2" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="1" t="s">
+    </row>
+    <row r="24" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="1" t="s">
+    </row>
+    <row r="25" spans="1:2" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="1" t="s">
+    </row>
+    <row r="26" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+      <c r="B26" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="1" t="s">
+    </row>
+    <row r="27" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="58" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+      <c r="B27" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="1" t="s">
+    </row>
+    <row r="28" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="1" t="s">
+    </row>
+    <row r="29" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="1" t="s">
+    </row>
+    <row r="30" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" ht="58" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="1" t="s">
+    </row>
+    <row r="31" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" ht="58" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+      <c r="B31" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="1" t="s">
+    </row>
+    <row r="32" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" ht="58" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+      <c r="B32" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="1" t="s">
+    </row>
+    <row r="33" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" ht="58" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
+      <c r="B33" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="1" t="s">
+    </row>
+    <row r="34" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" ht="58" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B34" s="1" t="s">
+    </row>
+    <row r="35" spans="1:2" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+      <c r="B35" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B35" s="1" t="s">
+    </row>
+    <row r="36" spans="1:2" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+      <c r="B36" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="1" t="s">
+    </row>
+    <row r="37" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="1" t="s">
+    </row>
+    <row r="38" spans="1:2" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" ht="116" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="1" t="s">
+    </row>
+    <row r="39" spans="1:2" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B39" s="1" t="s">
+    </row>
+    <row r="40" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
+      <c r="B40" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B40" s="1" t="s">
+    </row>
+    <row r="41" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B41" s="1" t="s">
+    </row>
+    <row r="42" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
+      <c r="B42" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B42" s="1" t="s">
+    </row>
+    <row r="43" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
+      <c r="B43" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B43" s="1" t="s">
+    </row>
+    <row r="44" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
+      <c r="B44" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B44" s="1" t="s">
+    </row>
+    <row r="45" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
+      <c r="B45" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B45" s="1" t="s">
+    </row>
+    <row r="46" spans="1:2" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
+      <c r="B46" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B46" s="1" t="s">
+    </row>
+    <row r="47" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
+      <c r="B47" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B48" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
+    <row r="49" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B49" s="1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
+      <c r="B50" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B49" s="1" t="s">
+    </row>
+    <row r="51" spans="1:2" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A50" s="1" t="s">
+      <c r="B51" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B50" s="1" t="s">
+    </row>
+    <row r="52" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A51" s="1" t="s">
+      <c r="B52" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B51" s="1" t="s">
+    </row>
+    <row r="53" spans="1:2" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A52" s="1" t="s">
+      <c r="B53" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B52" s="1" t="s">
+    </row>
+    <row r="54" spans="1:2" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" ht="58" x14ac:dyDescent="0.3">
-      <c r="A53" s="1" t="s">
+      <c r="B54" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B53" s="1" t="s">
+    </row>
+    <row r="55" spans="1:2" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A54" s="1" t="s">
+      <c r="B55" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B54" s="1" t="s">
+    </row>
+    <row r="56" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A55" s="1" t="s">
+      <c r="B56" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B55" s="1" t="s">
+    </row>
+    <row r="57" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A56" s="1" t="s">
+      <c r="B57" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B56" s="1" t="s">
+    </row>
+    <row r="58" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" ht="58" x14ac:dyDescent="0.3">
-      <c r="A57" s="1" t="s">
+      <c r="B58" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B57" s="1" t="s">
+    </row>
+    <row r="59" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A58" s="1" t="s">
+      <c r="B59" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B58" s="1" t="s">
+    </row>
+    <row r="60" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A59" s="1" t="s">
+      <c r="B60" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B59" s="1" t="s">
+    </row>
+    <row r="61" spans="1:2" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A60" s="1" t="s">
+      <c r="B61" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B60" s="1" t="s">
+    </row>
+    <row r="62" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" ht="29" x14ac:dyDescent="0.3">
-      <c r="A61" s="1" t="s">
+      <c r="B62" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B61" s="1" t="s">
+    </row>
+    <row r="63" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" ht="29" x14ac:dyDescent="0.3">
-      <c r="A62" s="1" t="s">
+      <c r="B63" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B64" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="29" x14ac:dyDescent="0.3">
-      <c r="A63" s="1" t="s">
+    <row r="65" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B65" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="29" x14ac:dyDescent="0.3">
-      <c r="A64" s="1" t="s">
+    <row r="66" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B66" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="29" x14ac:dyDescent="0.3">
-      <c r="A65" s="1" t="s">
+    <row r="67" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="29" x14ac:dyDescent="0.3">
-      <c r="A66" s="1" t="s">
+    <row r="68" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B68" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="29" x14ac:dyDescent="0.3">
-      <c r="A67" s="1" t="s">
+    <row r="69" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B69" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="29" x14ac:dyDescent="0.3">
-      <c r="A68" s="1" t="s">
+    <row r="70" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B70" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="29" x14ac:dyDescent="0.3">
-      <c r="A69" s="1" t="s">
+    <row r="71" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B71" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
-      <c r="A70" s="1" t="s">
+    <row r="72" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B72" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
-      <c r="A71" s="1" t="s">
+    <row r="73" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B73" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A72" s="1" t="s">
+    <row r="74" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B74" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A73" s="1" t="s">
+    <row r="75" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B75" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A74" s="1" t="s">
+    <row r="76" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B76" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
-      <c r="A75" s="1" t="s">
+    <row r="77" spans="1:2" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B77" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
-      <c r="A76" s="1" t="s">
+    <row r="78" spans="1:2" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="58" x14ac:dyDescent="0.3">
-      <c r="A77" s="1" t="s">
+    <row r="79" spans="1:2" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B79" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="58" x14ac:dyDescent="0.3">
-      <c r="A78" s="1" t="s">
+    <row r="80" spans="1:2" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="29" x14ac:dyDescent="0.3">
-      <c r="A79" s="1" t="s">
+    <row r="81" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B81" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A80" s="1" t="s">
+    <row r="82" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B82" s="1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="58" x14ac:dyDescent="0.3">
-      <c r="A81" s="1" t="s">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B83" s="1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A82" s="1" t="s">
+    <row r="84" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B84" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
-      <c r="A83" s="1" t="s">
+    <row r="85" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B85" s="1" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
-      <c r="A84" s="1" t="s">
+    <row r="86" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B86" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A85" s="1" t="s">
+    <row r="87" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B87" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
-      <c r="A86" s="1" t="s">
+    <row r="88" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B88" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
-      <c r="A87" s="1" t="s">
+    <row r="89" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B89" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A88" s="1" t="s">
+    <row r="90" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B90" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="58" x14ac:dyDescent="0.3">
-      <c r="A89" s="1" t="s">
+    <row r="91" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B91" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
-      <c r="A90" s="1" t="s">
+    <row r="92" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B92" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="29" x14ac:dyDescent="0.3">
-      <c r="A91" s="1" t="s">
+    <row r="93" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B93" s="1" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="58" x14ac:dyDescent="0.3">
-      <c r="A92" s="1" t="s">
+    <row r="94" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B94" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="29" x14ac:dyDescent="0.3">
-      <c r="A93" s="1" t="s">
+    <row r="95" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B95" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="58" x14ac:dyDescent="0.3">
-      <c r="A94" s="1" t="s">
+    <row r="96" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B96" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="29" x14ac:dyDescent="0.3">
-      <c r="A95" s="1" t="s">
+    <row r="97" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B97" s="1" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
-      <c r="A96" s="1" t="s">
+    <row r="98" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B98" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="29" x14ac:dyDescent="0.3">
-      <c r="A97" s="1" t="s">
+    <row r="99" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B99" s="1" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A98" s="1" t="s">
+    <row r="100" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B100" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="29" x14ac:dyDescent="0.3">
-      <c r="A99" s="1" t="s">
+    <row r="101" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B101" s="1" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
-      <c r="A100" s="1" t="s">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B102" s="1" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A101" s="1" t="s">
+    <row r="103" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B103" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="29" x14ac:dyDescent="0.3">
-      <c r="A102" s="1" t="s">
+    <row r="104" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B104" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
-      <c r="A103" s="1" t="s">
+    <row r="105" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="B105" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
-      <c r="A104" s="1" t="s">
+    <row r="106" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="B106" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A105" s="1" t="s">
+    <row r="107" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B107" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A106" s="1" t="s">
+    <row r="108" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="B108" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A107" s="1" t="s">
+    <row r="109" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B109" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
-      <c r="A108" s="1" t="s">
+    <row r="110" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="B110" s="1" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="159.5" x14ac:dyDescent="0.3">
-      <c r="A109" s="1" t="s">
+    <row r="111" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="B111" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
-      <c r="A110" s="1" t="s">
+    <row r="112" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="B112" s="1" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A111" s="1" t="s">
+    <row r="113" spans="1:2" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="B113" s="1" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="58" x14ac:dyDescent="0.3">
-      <c r="A112" s="1" t="s">
+    <row r="114" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B114" s="1" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="116" x14ac:dyDescent="0.3">
-      <c r="A113" s="1" t="s">
+    <row r="115" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="B115" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="58" x14ac:dyDescent="0.3">
-      <c r="A114" s="1" t="s">
+    <row r="116" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="B116" s="1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A115" s="1" t="s">
+    <row r="117" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B117" s="1" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="116" spans="1:2" ht="58" x14ac:dyDescent="0.3">
-      <c r="A116" s="1" t="s">
+    <row r="118" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="B118" s="1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="117" spans="1:2" ht="58" x14ac:dyDescent="0.3">
-      <c r="A117" s="1" t="s">
+    <row r="119" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="B119" s="1" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="118" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
-      <c r="A118" s="1" t="s">
+    <row r="120" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="B120" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="119" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A119" s="1" t="s">
+    <row r="121" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B121" s="1" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="120" spans="1:2" ht="58" x14ac:dyDescent="0.3">
-      <c r="A120" s="1" t="s">
+    <row r="122" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="B122" s="1" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="121" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
-      <c r="A121" s="1" t="s">
+    <row r="123" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="B123" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="122" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
-      <c r="A122" s="1" t="s">
+    <row r="124" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="B124" s="1" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="123" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A123" s="1" t="s">
+    <row r="125" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="B125" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="124" spans="1:2" ht="58" x14ac:dyDescent="0.3">
-      <c r="A124" s="1" t="s">
+    <row r="126" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="B126" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="125" spans="1:2" ht="29" x14ac:dyDescent="0.3">
-      <c r="A125" s="1" t="s">
+    <row r="127" spans="1:2" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="B127" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="126" spans="1:2" ht="43.5" x14ac:dyDescent="0.3">
-      <c r="A126" s="1" t="s">
+    <row r="128" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="B128" s="1" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="127" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
-      <c r="A127" s="1" t="s">
+    <row r="129" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="B129" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="128" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A128" s="1" t="s">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="B130" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="129" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A129" s="1" t="s">
+    <row r="131" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="B131" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="130" spans="1:2" ht="29" x14ac:dyDescent="0.3">
-      <c r="A130" s="1" t="s">
+    <row r="132" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="B132" s="1" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="58" x14ac:dyDescent="0.3">
-      <c r="A131" s="1" t="s">
+    <row r="133" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="B133" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="132" spans="1:2" ht="58" x14ac:dyDescent="0.3">
-      <c r="A132" s="1" t="s">
+    <row r="134" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="B134" s="1" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="133" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A133" s="1" t="s">
+    <row r="135" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="B135" s="1" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="134" spans="1:2" ht="130.5" x14ac:dyDescent="0.3">
-      <c r="A134" s="1" t="s">
+    <row r="136" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="B136" s="1" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="135" spans="1:2" ht="58" x14ac:dyDescent="0.3">
-      <c r="A135" s="1" t="s">
+    <row r="137" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="B137" s="1" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="136" spans="1:2" ht="29" x14ac:dyDescent="0.3">
-      <c r="A136" s="1" t="s">
+    <row r="138" spans="1:2" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="B138" s="1" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="137" spans="1:2" ht="29" x14ac:dyDescent="0.3">
-      <c r="A137" s="1" t="s">
+    <row r="139" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="B139" s="1" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="138" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A138" s="1" t="s">
+    <row r="140" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="B140" s="1" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="139" spans="1:2" ht="29" x14ac:dyDescent="0.3">
-      <c r="A139" s="1" t="s">
+    <row r="141" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="B141" s="1" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="140" spans="1:2" ht="101.5" x14ac:dyDescent="0.3">
-      <c r="A140" s="1" t="s">
+    <row r="142" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="B142" s="1" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="141" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A141" s="1" t="s">
+    <row r="143" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="B143" s="1" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="142" spans="1:2" ht="58" x14ac:dyDescent="0.3">
-      <c r="A142" s="1" t="s">
+    <row r="144" spans="1:2" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B142" s="1" t="s">
+      <c r="B144" s="1" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="143" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A143" s="1" t="s">
+    <row r="145" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="B145" s="1" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="144" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A144" s="1" t="s">
+    <row r="146" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B144" s="1" t="s">
+      <c r="B146" s="1" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="145" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A145" s="1" t="s">
+    <row r="147" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B145" s="1" t="s">
+      <c r="B147" s="1" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="146" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A146" s="1" t="s">
+    <row r="148" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="B148" s="1" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="147" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A147" s="1" t="s">
+    <row r="149" spans="1:2" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="B149" s="1" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="148" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A148" s="1" t="s">
+    <row r="150" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="B150" s="1" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="149" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A149" s="1" t="s">
+    <row r="151" spans="1:2" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B149" s="1" t="s">
+      <c r="B151" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="150" spans="1:2" ht="87" x14ac:dyDescent="0.3">
-      <c r="A150" s="1" t="s">
+    <row r="152" spans="1:2" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B150" s="1" t="s">
+      <c r="B152" s="1" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="151" spans="1:2" ht="72.5" x14ac:dyDescent="0.3">
-      <c r="A151" s="1" t="s">
+    <row r="153" spans="1:2" ht="63" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B151" s="1" t="s">
+      <c r="B153" s="1" t="s">
         <v>301</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>305</v>
       </c>
     </row>
   </sheetData>
